--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -425,659 +425,739 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>index</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Expected Answer</t>
+          <t>question</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Agent Answer</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>prediction</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>justification</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Quels modes de paiement acceptez-vous ?</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Nous acceptons les paiements par carte bancaire, prélèvement automatique, virement bancaire et PayPal. Le prélèvement automatique garantit de ne jamais manquer une échéance.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Facile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' est complètement hors sujet et ne contient aucune information sur les modes de paiement acceptés. Elle ne répond pas du tout à la question du client et ne contient aucun élément de la réponse de référence qui mentionne les différentes options de paiement (carte bancaire, prélèvement, virement, PayPal).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Comment puis-je consulter ma facture en ligne ?</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Vous pouvez consulter vos factures en vous connectant à votre espace client sur le site web ou via l'application mobile. Toutes les factures sont disponibles dans la section 'Mes factures' pendant 24 mois.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Facile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>La réponse générée n'a absolument aucun rapport avec la question du client sur la consultation de factures en ligne. Elle ne contient aucune information pertinente sur l'accès à l'espace client, la section des factures ou la durée de conservation des documents. Il s'agit visiblement d'un message de test ou d'erreur qui ne répond en rien à la demande du client.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Puis-je partager mon forfait data avec ma famille ?</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Oui, nous proposons des forfaits famille qui permettent de partager un pool de données entre plusieurs lignes. Contactez le service client pour plus d'informations sur les offres multi-lignes.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Facile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne répond aucunement à la question sur le partage de forfait data avec la famille. Elle ne contient aucune information pertinente sur les forfaits famille, le partage de données ou les offres multi-lignes mentionnés dans la réponse de référence.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Comment activer le roaming international ?</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Le roaming international est généralement activé par défaut. Vous pouvez vérifier son statut dans votre espace client ou en appelant le service client. Pensez à vérifier les tarifs avant de voyager.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Facile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' n'a absolument aucun rapport avec la question sur l'activation du roaming international. Elle ne contient aucune information pertinente présente dans la réponse de référence (activation par défaut, vérification du statut, tarifs). Il s'agit clairement d'un message d'instruction qui n'était pas destiné au client.</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Quels sont les tarifs de roaming en Europe ?</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Dans l'Union Européenne, vous bénéficiez du 'roaming comme à la maison'. Vous pouvez utiliser votre forfait français sans surcoût dans les pays de l'UE, selon les limites de votre contrat.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Facile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>La réponse générée n'a absolument aucun rapport avec la question sur les tarifs de roaming en Europe. Elle ne contient aucune information pertinente sur le sujet, ne mentionne pas le principe du 'roaming comme à la maison' ni les conditions d'utilisation du forfait dans l'UE. Il s'agit visiblement d'un message d'erreur ou d'un placeholder qui n'a pas été remplacé par une réponse réelle.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>J'ai oublié mon mot de passe, que faire ?</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Cliquez sur 'Mot de passe oublié' sur la page de connexion. Vous recevrez un lien de réinitialisation par email ou SMS. Suivez les instructions pour créer un nouveau mot de passe.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Facile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>La réponse générée n'a aucun rapport avec la question posée sur la récupération d'un mot de passe. Elle ne contient aucune information pertinente, ne mentionne pas la procédure de réinitialisation, et semble être un message d'erreur ou un placeholder en anglais. Elle ne répond absolument pas au besoin du client.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Comment configurer mes MMS ?</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Les paramètres MMS sont généralement configurés automatiquement. Si ce n'est pas le cas, rendez-vous dans Réglages &gt; Réseau mobile &gt; Noms des points d'accès et ajoutez la configuration disponible sur notre site.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Facile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' est complètement hors sujet et ne contient aucune information relative à la configuration des MMS. Il s'agit visiblement d'un texte placeholder qui n'a pas été remplacé par une réponse réelle. La réponse ne fournit aucune des instructions techniques présentes dans la réponse de référence concernant les paramètres MMS.</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Quel est le prix de l'iPhone 15 en 256GB ?</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>L'iPhone 15 en 256GB coûte 1099€.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne fournit aucune information sur le prix de l'iPhone 15 en 256GB. Elle ne contient aucun élément de la réponse de référence qui indique clairement que ce modèle coûte 1099€. Il s'agit visiblement d'un message de test ou d'erreur plutôt que d'une réponse à la question du client.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Quel iPhone a été commercialisé en 2023 ?</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>L'iPhone 15 a été commercialisé en 2023.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' n'a absolument aucun rapport avec la question sur l'iPhone commercialisé en 2023. Elle ne contient aucune information pertinente et semble être un message d'instruction plutôt qu'une réponse client. La réponse de référence indique clairement que c'est l'iPhone 15 qui a été commercialisé en 2023, information totalement absente de la réponse générée.</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Quels sont les coloris disponibles pour l'iPhone 16 ?</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>L'iPhone 16 est disponible en Noir, Blanc, Bleu sarcelle, Rose et Outremer.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne fournit aucune information sur les coloris de l'iPhone 16. Elle ne répond pas du tout à la question du client et ne contient aucun élément de la réponse de référence qui liste les couleurs disponibles.</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Quel est l'iPhone le moins cher disponible en 128GB ?</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>L'iPhone 11 est le moins cher en 128GB à 559€.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>La réponse générée ne contient aucune information pertinente concernant la question posée. Elle ne mentionne pas l'iPhone 11, ni son prix de 559€ pour la version 128GB, ni aucun autre modèle d'iPhone. La réponse 'Hello student, edit me please' est complètement hors sujet et semble être un texte générique ou un placeholder qui n'a pas été remplacé par une réponse réelle.</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Quelle est la différence d'autonomie entre l'iPhone 13 et l'iPhone 16 ?</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>L'iPhone 13 offre jusqu'à 19h de lecture vidéo, tandis que l'iPhone 16 offre jusqu'à 22h, soit 3 heures d'autonomie supplémentaires.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>La réponse générée ne contient aucune information pertinente concernant la différence d'autonomie entre l'iPhone 13 et l'iPhone 16. Il s'agit simplement d'un message générique 'Hello student, edit me please' qui ne répond absolument pas à la question posée. La réponse ne contient aucun des éléments factuels présents dans la réponse de référence (19h pour l'iPhone 13, 22h pour l'iPhone 16, différence de 3h).</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Y a-t-il des frais de résiliation si je suis engagé ?</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Si vous êtes encore en période d'engagement, des frais égaux au montant des mensualités restantes peuvent s'appliquer. Si vous êtes hors engagement (après 12 ou 24 mois), la résiliation est gratuite.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>La réponse générée n'a absolument aucun rapport avec la question sur les frais de résiliation. Il s'agit d'un message générique 'Hello student, edit me please' qui ne contient aucune information pertinente sur les conditions de résiliation, les frais applicables pendant ou après la période d'engagement. La réponse ne répond pas du tout à la question du client.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Je m'appelle Jean Bertrand. Quelle est ma consommation data ce mois-ci ?</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Vous avez consommé 3.20GB sur votre forfait de 5GB ce mois-ci.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>La réponse générée est totalement hors sujet et ne contient aucune information pertinente concernant la consommation data du client. Il s'agit d'un message générique 'Hello student, edit me please' qui ne répond absolument pas à la question posée et ne fournit aucune des informations présentes dans la réponse de référence (consommation de 3.20GB sur un forfait de 5GB).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Je m'appelle Jean Bertrand. Combien dois-je payer pour ma prochaine facture ?</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Votre prochaine facture s'élève à 9.99€ et est due le 15/12/2025.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne répond aucunement à la question du client concernant le montant de sa prochaine facture. Elle ne contient aucune des informations essentielles présentes dans la réponse de référence (montant de 9.99€, date d'échéance). Il s'agit visiblement d'un message de test ou d'erreur plutôt que d'une réponse client.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Je m'appelle Pierre Richard. Ai-je un ticket de support en cours ?</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Oui, vous avez 2 tickets en cours : Ticket #3 'Frais de résiliation' (Résiliation), Ticket #4 'Débit très lent' (Problème de réseau).</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>La réponse générée n'a aucun rapport avec la question du client. Elle ne mentionne pas les tickets en cours, ne confirme pas leur existence, et n'apporte aucune information pertinente. Il s'agit d'un message générique en anglais ('Hello student, edit me please') qui semble être un texte d'espace réservé et non une réponse réelle à la demande du client concernant ses tickets de support.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Je m'appelle Jean Bertrand. Combien me coûtera un voyage de 2 semaines aux États-Unis ?</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Hors Europe, nous recommandons un pass international. Selon votre forfait actuel Essentiel 5GB, vous pouvez souscrire à un pass hebdomadaire ou journalier disponible dans votre espace client. Les tarifs dépendent de votre destination.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Difficile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>La réponse générée n'a absolument aucun rapport avec la question du client concernant le coût d'un voyage aux États-Unis. Elle ne contient aucune information sur les pass internationaux, les forfaits, les tarifs ou les options disponibles pour l'itinérance. C'est une phrase générique sans aucune valeur informative qui ne répond pas du tout à la demande du client.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Je m'appelle Alexandre Martin. Puis-je résilier mon abonnement sans frais ?</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Votre contrat a commencé le 20/02/2024 et vous êtes hors période d'engagement depuis le 14/02/2025. La résiliation est gratuite.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Difficile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' n'a aucun rapport avec la question du client sur la résiliation d'abonnement. Elle ne contient aucune des informations essentielles présentes dans la réponse de référence (date de début de contrat, fin de période d'engagement, gratuité de la résiliation). Il s'agit clairement d'un message de placeholder qui n'est pas destiné au client.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Quel iPhone puis-je m'offrir avec mon budget de 1000€ en 256GB ?</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Avec un budget de 1000€ pour un modèle 256GB, vous pouvez choisir l'iPhone 14 (999€). L'iPhone 15 (1099€) dépasse légèrement votre budget.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Difficile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne répond absolument pas à la question sur les iPhone disponibles dans un budget de 1000€ en 256GB. Elle ne contient aucune information pertinente sur les modèles d'iPhone, leurs prix ou leurs capacités de stockage, contrairement à la réponse de référence qui mentionne précisément l'iPhone 14 et l'iPhone 15 avec leurs prix.</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Je m'appelle Jean Bertrand. Je pars en Italie 10 jours, dois-je changer de forfait ou prendre une option ?</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Vous avez actuellement le forfait Essentiel 5GB avec 5GB. En Italie (UE), le roaming est inclus sans surcoût selon la politique 'roaming comme à la maison'. Vous pouvez utiliser votre forfait normalement dans les limites de votre contrat. Aucune option supplémentaire nécessaire.</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Très Difficile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>La réponse générée est totalement hors sujet et ne contient aucune information pertinente. Elle ne répond pas du tout à la question du client concernant son forfait pour l'Italie, ne mentionne pas le roaming inclus dans l'UE, ni les conditions de son forfait actuel. C'est une phrase générique sans rapport avec la demande du client.</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Je veux acheter l'iPhone 16, puis-je avoir une réduction si je rends mon ancien iPhone ?</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>L'iPhone 16 en 128GB coûte 1019€. TelecomPlus propose des offres de reprise pour réduire ce prix. Pour connaître la valeur de reprise de votre ancien iPhone et bénéficier d'une réduction, consultez notre service de reprise sur www.telecomplus.fr ou contactez nos conseillers au 3900.</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Très Difficile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' est complètement hors sujet et ne contient aucune information pertinente concernant la question du client sur la reprise d'un ancien iPhone pour l'achat d'un iPhone 16. Il s'agit visiblement d'un message d'instruction ou d'erreur plutôt que d'une réponse client. Aucun élément de la réponse de référence n'est présent.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Quel iPhone avec au moins 48 Mpx de caméra est disponible pour moins de 1200€ en 256GB ?</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Les iPhone 15 (1099€) et iPhone 16 (1149€) en 256GB ont tous deux une caméra principale de 48 Mpx et sont sous 1200€. L'iPhone 17 a aussi 48 Mpx mais coûte 1299€, dépassant votre budget.</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Très Difficile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' est complètement hors sujet et ne contient aucune information pertinente concernant la question sur les iPhone avec caméra 48 Mpx sous 1200€. Elle ne mentionne ni les modèles disponibles, ni leurs prix, ni leurs caractéristiques techniques, contrairement à la réponse de référence qui détaille précisément les options (iPhone 15 et 16) correspondant aux critères du client.</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Je m'appelle Jean Bertrand. Si je change pour un forfait avec plus de data, combien cela me coûtera-t-il de plus par mois ?</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Vous avez actuellement le forfait Essentiel 5GB à 9.99€/mois avec 5GB. Le forfait supérieur est Confort 20GB à 15.99€/mois avec 20GB, soit 6.00€ de plus par mois. Pour changer de forfait, vous pouvez le modifier dans votre espace client. Le changement sera effectif à la prochaine période de facturation.</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Très Difficile</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>La réponse générée ne contient aucune information pertinente concernant la question du client sur le changement de forfait. Elle ne mentionne ni le forfait actuel, ni le forfait supérieur, ni la différence de prix, ni la procédure de changement. Il s'agit visiblement d'un message d'erreur ou d'un placeholder qui n'a aucun rapport avec la demande du client.</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Quel est le meilleur iPhone pour la photographie ?</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>L'iPhone 17 offre le système photo le plus avancé avec triple caméra 48 Mpx, téléobjectif périscopique 5x et capteur LiDAR. L'iPhone 16 est également excellent avec son système Fusion 48 Mpx. Le choix dépend de votre budget et de vos besoins spécifiques.</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' est complètement hors sujet et ne contient aucune information pertinente sur les iPhones ou la photographie. Elle ne répond absolument pas à la question du client et ne présente aucune similarité avec la réponse de référence qui détaille les modèles d'iPhone et leurs capacités photographiques.</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Puis-je utiliser mon iPhone à l'étranger sans surcoût ?</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Cela dépend de votre destination. Dans l'Union Européenne, vous bénéficiez du roaming sans surcoût ('roaming comme à la maison'). Hors Europe, des frais s'appliquent, et nous recommandons de souscrire à un pass international journalier ou hebdomadaire.</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Hello student, edit me please</t>
-        </is>
-      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Moyen</t>
+          <t>Hello student, edit me please</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne contient aucune information pertinente concernant l'utilisation d'un iPhone à l'étranger. Elle ne mentionne ni le roaming en UE, ni les frais hors Europe, ni les options de pass internationaux présents dans la réponse de référence. Il s'agit visiblement d'un message d'erreur ou d'un texte placeholder qui n'a aucun rapport avec la question du client.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -476,15 +476,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Merci pour votre question concernant les moyens de paiement disponibles chez TelecomPlus.
+**Nous acceptons les modes de paiement suivants :**
+| Mode de paiement | Principales caractéristiques |
+|------------------|------------------------------|
+| **Carte bancaire** (Visa, Mastercard, American Express) | Paiement sécurisé en ligne ou en boutique. |
+| **Prélèvement automatique** | Le montant de votre facture est prélevé chaque mois directement sur votre compte bancaire. Cette option vous garantit de ne jamais manquer une échéance. |
+| **Virement bancaire** | Vous pouvez effectuer un virement depuis votre compte bancaire en indiquant votre référence client. |
+| **PayPal** | Paiement en ligne via votre compte PayPal, pratique si vous préférez ne pas communiquer vos coordonnées bancaires directement. |
+**Comment choisir ou modifier votre moyen de paiement ?**  
+1. Connectez‑vous à votre espace client : [www.telecomplus.fr/mon-compte](https://www.telecomplus.fr/mon-compte).  
+2. Rendez‑vous dans la section **« Gestion des paiements »**.  
+3. Ajoutez, modifiez ou supprimez le mode de paiement souhaité.  
+**Besoin d’assistance ?**  
+- Téléphone : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
+- Chat en ligne : disponible sur notre site web  
+- Email : support@telecomplus.fr  
+Nous restons à votre disposition pour toute question supplémentaire ou pour vous accompagner dans la mise à jour de vos informations de paiement.
+Cordialement,  
+Service Client TelecomPlus</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' est complètement hors sujet et ne contient aucune information sur les modes de paiement acceptés. Elle ne répond pas du tout à la question du client et ne contient aucun élément de la réponse de référence qui mentionne les différentes options de paiement (carte bancaire, prélèvement, virement, PayPal).</t>
+          <t>La réponse générée couvre tous les modes de paiement mentionnés dans la référence, y compris les détails sur le prélèvement automatique, et fournit même des informations supplémentaires sur la façon de gérer les paiements.</t>
         </is>
       </c>
     </row>
@@ -504,15 +523,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Pour consulter votre facture en ligne, il vous suffit de suivre les étapes ci‑dessous :
+1. **Accédez à votre espace client**  
+   Ouvrez votre navigateur et rendez‑vous sur :  
+   &lt;https://www.telecomplus.fr/mon-compte&gt;
+2. **Identifiez‑vous**  
+   - Saisissez votre identifiant (adresse e‑mail ou numéro de client)  
+   - Entrez votre mot de passe.  
+   *Si vous avez oublié votre mot de passe, cliquez sur « Mot de passe oublié » pour recevoir un lien de réinitialisation par e‑mail.*
+3. **Accédez à la section « Factures »**  
+   - Une fois connecté, cliquez sur le menu **« Factures »** (ou l’icône correspondante).  
+   - Vous verrez la liste de toutes vos factures mensuelles.
+4. **Visualisez ou téléchargez votre facture**  
+   - Cliquez sur la facture du mois souhaité pour l’ouvrir en PDF.  
+   - Vous pouvez la **télécharger** ou l’**imprimer** directement depuis votre navigateur.
+5. **Options supplémentaires**  
+   - Vous pouvez activer les **notifications par e‑mail** ou **SMS** afin d’être informé dès qu’une nouvelle facture est disponible.  
+   - Si vous souhaitez régler votre facture en ligne, la même page vous propose les moyens de paiement (carte bancaire, prélèvement automatique, PayPal, etc.).
+---
+### En cas de difficulté
+- **Chat en ligne** : disponible directement sur le site web (icône de chat en bas à droite).  
+- **Téléphone** : appelez le 3900 (appel gratuit, 7 j/7 de 8 h à 20 h).  
+- **E‑mail** : support@telecomplus.fr  
+Nos conseillers sont à votre disposition pour vous aider à récupérer vos identifiants ou à résoudre tout problème d’accès.
+---
+**Rappel important** : votre espace client est sécurisé et vous permet de consulter l’historique complet de vos factures, de vérifier les consommations (data, appels, SMS) et de gérer vos options de paiement.
+N’hésitez pas à nous contacter si vous avez besoin d’une assistance supplémentaire. Nous sommes là pour vous accompagner.  
+Bonne consultation !</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>La réponse générée n'a absolument aucun rapport avec la question du client sur la consultation de factures en ligne. Elle ne contient aucune information pertinente sur l'accès à l'espace client, la section des factures ou la durée de conservation des documents. Il s'agit visiblement d'un message de test ou d'erreur qui ne répond en rien à la demande du client.</t>
+          <t>La réponse fournit les étapes détaillées pour consulter la facture en ligne, ce qui correspond à la réponse de référence, mais elle offre plus d'informations et d'options que la réponse idéale.</t>
         </is>
       </c>
     </row>
@@ -532,15 +578,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Oui, il est tout à fait possible de partager votre forfait data avec les membres de votre famille grâce à nos **forfaits famille**.  
+### Comment cela fonctionne ?
+- **Pool de données commun** : un volume de data (ex. 10 Go, 30 Go, etc.) est mis à disposition de plusieurs lignes que vous choisissez (généralement 2 à 5 lignes, mais le nombre exact dépend du forfait).
+- **Utilisation libre** : chaque ligne consomme les données du pool commun. Vous avez ainsi une visibilité globale sur la consommation totale via votre espace client.
+- **Gestion simplifiée** : vous pouvez ajouter ou retirer des lignes, consulter le solde restant et recevoir des alertes (80 % et 100 % du pool) par SMS.
+### Conditions importantes
+| Point | Détail |
+|-------|--------|
+| **Éligibilité** | Le titulaire du forfait doit être le responsable du compte (abonné principal). |
+| **Nombre de lignes** | Variable selon le forfait choisi (généralement de 2 à 5 lignes). |
+| **Facturation** | Une seule facture mensuelle regroupe l’ensemble des lignes du pool. |
+| **Modification** | Vous pouvez ajouter ou retirer des lignes à tout moment depuis votre espace client ; le changement prend effet à la prochaine période de facturation. |
+| **Dépassement** | Si le pool est épuisé, vous avez deux options : acheter un rechargement de data supplémentaire ou être facturé au Mo supplémentaire selon les conditions de votre contrat (voir Q32). |
+### Démarches concrètes pour souscrire à un forfait famille
+1. **Vérifier votre éligibilité**  
+   - Connectez‑vous à votre espace client : [www.telecomplus.fr/mon-compte](https://www.telecomplus.fr/mon-compte).  
+   - Consultez la rubrique « Forfaits famille » ou « Mes offres » pour voir les options disponibles.
+2. **Choisir le forfait qui vous convient**  
+   - Comparez les volumes de data proposés (ex. 10 Go, 30 Go, 50 Go) et le nombre de lignes maximum.
+3. **Activer le partage**  
+   - Depuis l’espace client, cliquez sur **« Ajouter une ligne famille »** et suivez les instructions (numéro de téléphone, nom du bénéficiaire, etc.).  
+   - Vous pouvez également le faire directement en boutique ou via notre service client.
+4. **Confirmer et suivre la consommation**  
+   - Une fois le forfait activé, vous recevrez un SMS de confirmation.  
+   - Vous pourrez suivre le solde du pool en temps réel dans votre tableau de bord.
+### Besoin d’assistance ?
+- **Par téléphone** : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
+- **Chat en ligne** : disponible sur notre site web  
+- **Email** : support@telecomplus.fr  
+- **En agence** : retrouvez l’agence la plus proche sur [www.telecomplus.fr/agences](https://www.telecomplus.fr/agences)
+N’hésitez pas à nous contacter si vous avez besoin d’aide pour choisir le forfait le plus adapté à votre usage familial ou pour toute autre question. Nous sommes là pour vous accompagner dans la mise en place du partage de data.
+Bonne journée et à très bientôt !  
+*L’équipe Service Client TelecomPlus*</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne répond aucunement à la question sur le partage de forfait data avec la famille. Elle ne contient aucune information pertinente sur les forfaits famille, le partage de données ou les offres multi-lignes mentionnés dans la réponse de référence.</t>
+          <t>La réponse générée fournit une explication détaillée et complète sur les forfaits famille, incluant les conditions, les démarches pour souscrire et les moyens de contacter le service client, répondant ainsi parfaitement à la question du client.</t>
         </is>
       </c>
     </row>
@@ -560,15 +639,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Le roaming international est **généralement activé par défaut** sur votre ligne TelecomPlus.  
+Voici comment vérifier et, le cas échéant, activer le service :
+1. **Connectez‑vous à votre espace client** (www.telecomplus.fr/mon-compte).  
+2. Rendez‑vous dans la rubrique **« Gestion de mon forfait »** → **« Paramètres roaming »**.  
+3. Vérifiez que le bouton **« Roaming international »** est bien positionné sur **« Activé »**.  
+   - Si le bouton indique « Désactivé », cliquez dessus pour le mettre sur « Activé », puis validez.  
+4. **Enregistrez** les modifications. Le changement prend effet immédiatement.
+&gt; **Astuce :** même si le roaming est activé, il est recommandé de vérifier les tarifs applicables à votre forfait avant votre départ, afin d’éviter toute surprise sur votre facture.
+---
+### Si vous ne voyez pas l’option ou avez un doute :
+- **Appelez le service client** au **3900** (appel gratuit, 7 j/7 de 8 h à 20 h).  
+- **Chat en ligne** disponible sur notre site web.  
+- Vous pouvez également vous rendre dans l’une de nos agences.
+Nous restons à votre disposition pour toute aide supplémentaire.
+Cordialement,  
+Service Client TelecomPlus.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' n'a absolument aucun rapport avec la question sur l'activation du roaming international. Elle ne contient aucune information pertinente présente dans la réponse de référence (activation par défaut, vérification du statut, tarifs). Il s'agit clairement d'un message d'instruction qui n'était pas destiné au client.</t>
+          <t>La réponse générée couvre tous les points de la réponse de référence, y compris l'activation par défaut, la vérification dans l'espace client et la recommandation de vérifier les tarifs, avec des détails supplémentaires pour une aide plus complète.</t>
         </is>
       </c>
     </row>
@@ -588,15 +683,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Dans l’Union européenne, **le roaming « comme à la maison » s’applique** à tous les forfaits TelecomPlus. Concrètement :
+| Pays concernés | Tarif appliqué | Conditions |
+|----------------|----------------|------------|
+| Tous les États membres de l’UE (et les pays de l’EEE) | Aucun surcoût : vous utilisez votre forfait français (appels, SMS/MMS et data) aux mêmes tarifs qu’en France | Respect des limites de votre contrat (fair‑use). Au‑delà de ces seuils, des frais supplémentaires peuvent s’appliquer (voir votre espace client). |
+### Ce que cela signifie pour vous
+- **Appels et SMS/MMS** : facturés comme en France, sans frais additionnels.  
+- **Data mobile** : vous pouvez consommer votre quota data habituel. Si vous dépassez le plafond de fair‑use (défini dans votre contrat), des frais de data roaming peuvent être appliqués.  
+- **Activation** : le roaming est généralement activé par défaut. Vous pouvez le vérifier dans votre espace client ou en appelant le 3900.
+### Vérifier vos limites
+1. Connectez‑vous à votre compte sur **www.telecomplus.fr/mon-compte**.  
+2. Consultez la rubrique **« Mon forfait »** → **« Conditions de roaming »** pour connaître le plafond de fair‑use qui vous concerne.  
+3. Si vous avez besoin d’un suivi en temps réel, activez les notifications de consommation data dans l’application mobile.
+### Que faire si vous avez besoin d’un dépassement ou d’un pass supplémentaire
+- **Pass data additionnel** : disponible à l’achat directement depuis votre espace client (option « Pass roaming »).  
+- **Assistance** : si vous avez le moindre doute, notre service client est à votre disposition :  
+  - Téléphone : **3900** (appel gratuit, 7j/7 de 8 h à 20 h)  
+  - Chat en ligne : via le site web  
+  - Email : **support@telecomplus.fr**
+Nous restons à votre écoute pour toute question complémentaire ou pour vous aider à configurer votre roaming avant votre départ.
+Cordialement,  
+L’équipe Service Client TelecomPlus.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>La réponse générée n'a absolument aucun rapport avec la question sur les tarifs de roaming en Europe. Elle ne contient aucune information pertinente sur le sujet, ne mentionne pas le principe du 'roaming comme à la maison' ni les conditions d'utilisation du forfait dans l'UE. Il s'agit visiblement d'un message d'erreur ou d'un placeholder qui n'a pas été remplacé par une réponse réelle.</t>
+          <t>La réponse générée par l'agent fournit les mêmes informations que la réponse de référence, avec plus de détails sur les conditions et les limites du roaming dans l'UE.</t>
         </is>
       </c>
     </row>
@@ -616,15 +732,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Je comprends que vous ayez perdu votre mot de passe, cela arrive à tout le monde. Voici la démarche à suivre pour le réinitialiser :
+1. **Accédez à la page de connexion** de votre espace client :  
+   &lt;https://www.telecomplus.fr/mon-compte&gt;
+2. Cliquez sur le lien **« Mot de passe oublié »** situé sous les champs de connexion.
+3. Vous serez invité à indiquer **votre adresse e‑mail ou votre numéro de téléphone** associé à votre compte.
+4. Un **lien de réinitialisation** vous sera envoyé par e‑mail ou un **code SMS** selon le moyen que vous avez choisi.
+5. Ouvrez le message reçu, cliquez sur le lien (ou saisissez le code) et suivez les instructions pour créer un **nouveau mot de passe**. Veillez à choisir un mot de passe sécurisé (au moins 8 caractères, incluant lettres, chiffres et éventuellement un symbole).
+6. Une fois le nouveau mot de passe enregistré, vous pourrez vous reconnecter immédiatement à votre espace client.
+---
+### Besoin d’assistance supplémentaire ?
+- **Téléphone** : 3900 (appel gratuit, disponible 7 j/7 de 8 h à 20 h)  
+- **Chat en ligne** : depuis le site web, rubrique « Assistance »  
+- **E‑mail** : support@telecomplus.fr  
+- **Agence** : rendez‑vous dans l’une de nos boutiques (voir &lt;www.telecomplus.fr/agences&gt;)
+N’hésitez pas à nous contacter si vous rencontrez la moindre difficulté lors de la réinitialisation. Nous sommes là pour vous aider.
+Bonne journée et à très vite sur votre compte !</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>La réponse générée n'a aucun rapport avec la question posée sur la récupération d'un mot de passe. Elle ne contient aucune information pertinente, ne mentionne pas la procédure de réinitialisation, et semble être un message d'erreur ou un placeholder en anglais. Elle ne répond absolument pas au besoin du client.</t>
+          <t>La réponse générée par l'agent est très détaillée et suit parfaitement les étapes indiquées dans la réponse de référence, avec des explications supplémentaires pour aider le client.</t>
         </is>
       </c>
     </row>
@@ -644,15 +776,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Voici comment configurer les paramètres MMS de votre téléphone :
+1. **Vérifiez la configuration automatique**  
+   Dans la plupart des cas, les paramètres MMS sont configurés automatiquement dès l’activation de votre carte SIM. Essayez d’envoyer un MMS ; si cela fonctionne, aucune action supplémentaire n’est nécessaire.
+2. **Si les MMS ne fonctionnent pas, configurez manuellement le point d’accès (APN)**  
+   a. Ouvrez **Réglages** (ou **Paramètres**) de votre appareil.  
+   b. Sélectionnez **Réseau mobile** (ou **Cellulaire**).  
+   c. Appuyez sur **Noms des points d’accès** (ou **APN**).  
+   d. Ajoutez un nouveau point d’accès en utilisant les informations suivantes (disponibles sur notre site : [www.telecomplus.fr/apn-mms](https://www.telecomplus.fr/apn-mms)) :  
+| Champ | Valeur (exemple) |
+|-------|------------------|
+| **Nom** | TelecomPlus MMS |
+| **APN** | mms.telecomplus.fr |
+| **Nom d’utilisateur** | (laisser vide) |
+| **Mot de passe** | (laisser vide) |
+| **MMSC** | http://mms.telecomplus.fr |
+| **Proxy MMS** | 0.0.0.0 |
+| **Port MMS** | 0 |
+| **Type d’APN** | mms |
+| **Protocole APN** | IPv4/IPv6 |
+| **Portée APN** | default,supl |
+   e. Enregistrez le nouveau point d’accès, puis sélectionnez‑le comme APN actif.  
+   f. Redémarrez votre téléphone pour que les modifications prennent effet.
+3. **Testez l’envoi d’un MMS**  
+   Après le redémarrage, essayez d’envoyer à nouveau un MMS. Si le message part correctement, la configuration est terminée.
+---
+### En cas de difficulté
+- **Vérifiez la connexion réseau** : assurez-vous d’être en 4G/5G ou en 3G, car les MMS ne fonctionnent pas en mode 2G uniquement.  
+- **Mise à jour du système** : assurez‑vous que votre téléphone dispose de la dernière version logicielle disponible.  
+- **Contactez le support** : si le problème persiste malgré ces étapes, n’hésitez pas à nous appeler au **0 800 123 456** ou à ouvrir un chat en direct depuis votre espace client. Nous pourrons vérifier votre ligne et vous guider plus en détail.
+Nous restons à votre disposition pour toute question supplémentaire.  
+Cordialement,  
+Service Client TelecomPlus.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' est complètement hors sujet et ne contient aucune information relative à la configuration des MMS. Il s'agit visiblement d'un texte placeholder qui n'a pas été remplacé par une réponse réelle. La réponse ne fournit aucune des instructions techniques présentes dans la réponse de référence concernant les paramètres MMS.</t>
+          <t>La réponse générée par l'agent est très détaillée et fournit les mêmes informations que la réponse de référence, avec des étapes supplémentaires pour aider le client en cas de difficulté.</t>
         </is>
       </c>
     </row>
@@ -672,7 +836,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Merci pour votre demande concernant le prix de l’iPhone 15 en version 256 Go.
+**Ce que nous savons d’après la documentation fournie :**
+- L’iPhone 15 est présenté dans notre catalogue avec ses caractéristiques (couleurs, autonomie, etc.).
+- Aucun tarif n’est indiqué dans le PDF de la FAQ ni dans les données tabulaires dont nous disposons.
+**Comment obtenir le prix exact ?**
+1. **Site web** – Rendez‑vous sur notre boutique en ligne :  
+   &lt;https://www.telecomplus.fr&gt;  
+   → Sélectionnez « iPhone 15 » → Choisissez la capacité « 256 GB ». Le prix affiché sera le tarif en vigueur, incluant éventuellement les promotions ou les options de financement.
+2. **Appel téléphonique** – Vous pouvez contacter notre service client au **3900 (appel gratuit)**. Nos conseillers vous communiqueront le tarif actuel et pourront vous conseiller sur les offres de paiement échelonné ou les packs accessoires.
+3. **Boutique physique** – Si vous préférez un échange en face à face, nos équipes en boutique sont à votre disposition. Elles pourront vous montrer le produit, vous indiquer le prix et même vous proposer une démonstration.
+4. **Demande par e‑mail** – Envoyez un message à **serviceclient@telecomplus.fr** avec la référence « iPhone 15 256 GB ». Vous recevrez une réponse écrite contenant le prix ainsi que les éventuelles conditions de garantie et de livraison.
+**À retenir :**
+- Le prix peut varier selon les promotions en cours, le mode de paiement choisi (paiement comptant, crédit, abonnement) et la disponibilité du stock.
+- La livraison standard est gratuite pour les commandes en ligne, comme indiqué dans la FAQ.
+Je reste à votre disposition si vous avez besoin d’aide pour finaliser votre achat ou pour toute autre question. N’hésitez pas à me préciser si vous souhaitez être rappelé ou si vous avez besoin d’informations complémentaires (options de financement, assurance, accessoires compatibles, etc.).
+Cordialement,  
+L’équipe TelecomPlus – Service Client.</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -680,7 +861,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne fournit aucune information sur le prix de l'iPhone 15 en 256GB. Elle ne contient aucun élément de la réponse de référence qui indique clairement que ce modèle coûte 1099€. Il s'agit visiblement d'un message de test ou d'erreur plutôt que d'une réponse à la question du client.</t>
+          <t>La réponse générée par l'agent ne fournit pas le prix de l'iPhone 15 en 256GB, contrairement à la réponse de référence qui donne le prix exact.</t>
         </is>
       </c>
     </row>
@@ -700,15 +881,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>**Réponse :**  
+L’iPhone commercialisé en 2023 est l’**iPhone 15**.
+---
+### Pourquoi cet iPhone ?  
+- **Date de sortie officielle** : Apple a présenté l’iPhone 15 en septembre 2023, marquant le lancement de la génération suivante après l’iPhone 14 (2022).  
+- **Disponibilité chez TelecomPlus** : L’iPhone 15 figure dans notre catalogue actuel (voir le tableau des prix) et est disponible en plusieurs capacités de stockage (128 Go, 256 Go, 512 Go).
+---
+### Comment l’obtenir chez TelecomPlus ?  
+| Action | Détails |
+|--------|---------|
+| **En ligne** | Rendez‑vous sur &lt;https://www.telecomplus.fr&gt; → choisissez le modèle iPhone 15, la capacité souhaitée et ajoutez‑le à votre panier. Livraison gratuite à domicile. |
+| **En boutique** | Visitez l’une de nos agences (liste sur &lt;https://www.telecomplus.fr/agences&gt;) pour tester le téléphone en magasin et le retirer immédiatement. |
+| **Par téléphone** | Appelez le **3900** (appel gratuit, 7 j/7 de 8 h à 20 h) ; un conseiller vous guidera dans le choix du stockage et du forfait le plus adapté. |
+| **Échange / reprise** | Si vous avez un ancien smartphone, profitez de notre programme de reprise : vous bénéficiez d’une remise immédiate sur l’achat de l’iPhone 15. |
+---
+### Points à retenir  
+- **Compatibilité** : Tous les iPhone 15 sont compatibles avec nos forfaits mobiles (4G/5G) et les services additionnels (data, roaming, etc.).  
+- **Garantie** : Vous bénéficiez de la garantie légale de conformité (2 ans) ainsi de la garantie constructeur Apple (1 an).  
+- **Assistance** : En cas de question technique ou de configuration, notre service client (téléphone, chat en ligne, email) reste à votre disposition.
+---
+**Besoin d’un accompagnement personnalisé ?**  
+N’hésitez pas à nous contacter par le canal qui vous convient le mieux ; nous serons ravis de vous aider à finaliser votre achat ou à répondre à toute autre interrogation.  
+*Merci de votre confiance, l’équipe TelecomPlus.*</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' n'a absolument aucun rapport avec la question sur l'iPhone commercialisé en 2023. Elle ne contient aucune information pertinente et semble être un message d'instruction plutôt qu'une réponse client. La réponse de référence indique clairement que c'est l'iPhone 15 qui a été commercialisé en 2023, information totalement absente de la réponse générée.</t>
+          <t>La réponse générée par l'agent fournit l'information exacte demandée par le client, à savoir que l'iPhone 15 a été commercialisé en 2023, et offre même des détails supplémentaires sur la disponibilité et les options d'achat.</t>
         </is>
       </c>
     </row>
@@ -728,15 +931,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>**Bonjour,**
+Merci pour votre question concernant les coloris de l’iPhone 16.  
+Dans la documentation que nous avons à disposition, la section dédiée à l’iPhone 16 décrit ses caractéristiques techniques (écran 6,1 pouces Super Retina XDR OLED, puce A18, design tout‑écran, etc.) mais ne précise pas la liste exacte des coloris proposés.
+### Que faire pour connaître les coloris disponibles ?
+1. **Consulter la page produit officielle** – Le site web de TelecomPlus (ou la boutique Apple) indique généralement la gamme de couleurs au moment du lancement.  
+2. **Contacter notre service commercial** – Vous pouvez appeler le +33 1 23 45 67 89 ou nous écrire à **sales@telecomplus.fr** ; nous vous transmettrons la liste exacte et les éventuelles éditions limitées.  
+3. **Passer en magasin** – Nos conseillers en boutique pourront vous présenter les modèles en stock et vous faire découvrir les finitions disponibles.
+### Points à retenir
+- La FAQ ne mentionne pas les coloris de l’iPhone 16, mais les modèles précédents (iPhone 14, iPhone 13, etc.) proposaient des teintes telles que Noir, Blanc, Bleu, Vert, Rouge (PRODUCT)RED, Mauve, etc.  
+- Il est possible que l’iPhone 16 conserve une partie de ces teintes tout en introduisant de nouvelles finitions (par exemple, des variantes « infusées de couleur » mentionnées pour les modèles récents).  
+- Les disponibilités peuvent varier selon les stocks et les régions.
+---
+**Je reste à votre disposition** si vous avez besoin d’aide pour vérifier la disponibilité d’un coloris précis, pour réserver un appareil ou pour toute autre question relative à votre futur iPhone 16.
+Cordialement,  
+*Service Client – TelecomPlus*  
+📞 +33 1 23 45 67 89 | ✉️ support@telecomplus.fr</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne fournit aucune information sur les coloris de l'iPhone 16. Elle ne répond pas du tout à la question du client et ne contient aucun élément de la réponse de référence qui liste les couleurs disponibles.</t>
+          <t>La réponse générée par l'agent ne fournit pas directement les coloris disponibles pour l'iPhone 16, mais propose des méthodes pour obtenir cette information, montrant un manque d'exactitude et de complétude par rapport à la réponse de référence.</t>
         </is>
       </c>
     </row>
@@ -756,15 +974,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>**Réponse à votre demande**
+| Modèle | Stockage 128 GB | Prix indiqué |
+|--------|----------------|--------------|
+| iPhone 11 | 128 GB | **559 €** |
+| iPhone 12 | 128 GB | 729 € |
+| iPhone 13 | 128 GB | 809 € |
+| iPhone 14 | 128 GB | 869 € |
+| iPhone 15 | 128 GB | 969 € |
+| iPhone 16 | 128 GB | 1 019 € |
+&gt; **L’iPhone le moins cher disponible en 128 GB est donc l’iPhone 11, au prix de 559 €.**  
+---
+### Points à retenir
+1. **Disponibilité** – Le catalogue reflète les prix au **04/11/2025**. Selon les stocks, certains modèles peuvent être momentanément en rupture.  
+2. **Compatibilité** – Tous les modèles listés sont compatibles avec les forfaits TelecomPlus.  
+3. **Livraison** – La commande en ligne (www.telecomplus.fr) bénéficie de la livraison gratuite.  
+---
+### Que faire ensuite ?
+- **Commande en ligne** : Rendez‑vous sur notre site, choisissez *iPhone 11 – 128 GB* et finalisez votre achat en quelques clics.  
+- **Assistance téléphonique** : Si vous avez besoin d’aide pour la configuration ou le choix du forfait, appelez le **3900 (appel gratuit)**.  
+- **Boutique physique** : Vous pouvez également vous rendre dans l’une de nos boutiques pour tester le modèle et le retirer immédiatement.  
+Nous restons à votre disposition pour toute question complémentaire ou pour vous accompagner dans votre achat.  
+Cordialement,  
+L’équipe TelecomPlus – Service Client.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>La réponse générée ne contient aucune information pertinente concernant la question posée. Elle ne mentionne pas l'iPhone 11, ni son prix de 559€ pour la version 128GB, ni aucun autre modèle d'iPhone. La réponse 'Hello student, edit me please' est complètement hors sujet et semble être un texte générique ou un placeholder qui n'a pas été remplacé par une réponse réelle.</t>
+          <t>La réponse générée fournit exactement la même information que la référence, avec le même modèle d'iPhone et le même prix, et offre même des détails supplémentaires utiles pour le client.</t>
         </is>
       </c>
     </row>
@@ -784,15 +1024,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>**Bonjour,**
+Merci pour votre question concernant l’autonomie des iPhone 13 et iPhone 16. Voici les informations disponibles dans notre documentation :
+| Modèle | Autonomie annoncée (lecture vidéo) |
+|--------|------------------------------------|
+| **iPhone 13** (2021) | Jusqu’à **17 heures** de lecture vidéo |
+| **iPhone 16** (2024) | *Aucune donnée d’autonomie précise n’est fournie dans le PDF de notre FAQ* |
+### Ce que cela signifie pour vous
+- **iPhone 13** : Vous pouvez profiter d’environ 17 heures de vidéo en continu, ce qui couvre largement une journée d’utilisation intensive sans recharger.
+- **iPhone 16** : Le document que nous possédons ne précise pas la durée exacte de la batterie. Apple a généralement amélioré l’efficacité énergétique avec chaque génération (puce A18, écran Super Retina XDR OLED, etc.), il est donc probable que l’iPhone 16 offre une autonomie au moins équivalente, voire supérieure, à celle de l’iPhone 13.  
+### Que faire si vous avez besoin de plus de précisions ?
+1. **Consulter le site officiel d’Apple** – les fiches techniques détaillent les heures de lecture vidéo, de navigation web, etc.
+2. **Nous contacter directement** – nous pouvons vous transmettre les dernières spécifications techniques ou vous orienter vers un conseiller spécialisé.
+3. **Tester en magasin** – si vous avez la possibilité de passer dans l’un de nos points de vente, vous pourrez comparer les deux modèles en conditions réelles.
+Nous restons à votre disposition pour toute information complémentaire ou pour vous aider à choisir le modèle qui correspond le mieux à vos besoins.
+**Cordialement,**  
+Le service client TelecomPlus  
+📞 0 800 123 456 – disponible du lundi au vendredi, 9 h–18 h.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>La réponse générée ne contient aucune information pertinente concernant la différence d'autonomie entre l'iPhone 13 et l'iPhone 16. Il s'agit simplement d'un message générique 'Hello student, edit me please' qui ne répond absolument pas à la question posée. La réponse ne contient aucun des éléments factuels présents dans la réponse de référence (19h pour l'iPhone 13, 22h pour l'iPhone 16, différence de 3h).</t>
+          <t>La réponse fournit des informations sur l'autonomie des deux modèles, mais les valeurs sont différentes de celles de la référence et l'agent n'a pas pu fournir la différence exacte pour l'iPhone 16 en raison du manque de données.</t>
         </is>
       </c>
     </row>
@@ -812,15 +1068,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Merci pour votre question.
+**Frais de résiliation lorsque vous êtes encore engagé**
+- **Oui, des frais peuvent s’appliquer** si vous résiliez avant la fin de votre période d’engagement (12 ou 24 mois selon votre offre).  
+- Le montant de ces frais correspond généralement **au total des mensualités restantes** jusqu’à la fin du contrat. Par exemple, si vous avez encore 6 mois d’engagement à 30 € / mois, les frais seront d’environ 180 €.
+**Quand la résiliation est gratuite ?**  
+- Si vous avez dépassé la période d’engagement (c’est‑à‑dire que votre contrat a déjà 12 ou 24 mois selon le cas), la résiliation est alors **gratuite**.
+**Comment connaître le montant exact ?**  
+1. **Consultez votre espace client** (www.telecomplus.fr/mon-compte) → « Mon contrat » → détail des engagements restants.  
+2. Vous pouvez également **contacter notre service client** qui vous indiquera le montant précis :  
+   - Téléphone : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
+   - Chat en ligne sur notre site web  
+   - Email : support@telecomplus.fr  
+**Démarches de résiliation**  
+- Si vous décidez de résilier, vous pouvez le faire **en ligne** depuis votre espace client (si vous êtes hors période d’engagement) ou **par lettre recommandée avec accusé de réception**.  
+- La résiliation prend effet **dans les 10 jours** suivant la réception de votre demande.
+---
+**En résumé**  
+- Engagé ? → Des frais égaux aux mensualités restantes peuvent être facturés.  
+- Hors engagement ? → La résiliation est gratuite.
+N’hésitez pas à nous contacter pour obtenir le calcul exact de vos frais ou pour toute assistance supplémentaire. Nous sommes là pour vous accompagner dans votre démarche.
+Cordialement,  
+Service Client TelecomPlus  
+📞 3900 – 📧 support@telecomplus.fr – 💬 Chat en ligne disponible sur notre site.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>La réponse générée n'a absolument aucun rapport avec la question sur les frais de résiliation. Il s'agit d'un message générique 'Hello student, edit me please' qui ne contient aucune information pertinente sur les conditions de résiliation, les frais applicables pendant ou après la période d'engagement. La réponse ne répond pas du tout à la question du client.</t>
+          <t>La réponse générée par l'agent est très complète, précise et alignée avec la réponse de référence, fournissant même des détails supplémentaires sur la façon de connaître le montant exact des frais et les démarches de résiliation.</t>
         </is>
       </c>
     </row>
@@ -840,7 +1119,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour Monsieur Bertrand,
+Je ne peux malheureusement pas accéder à votre espace personnel ni consulter votre consommation data depuis ce canal.  
+**Voici les démarches les plus simples pour connaître votre consommation du mois en cours :**
+1. **Connectez‑vous à votre espace client**  
+   - Rendez‑vous sur : **www.telecomplus.fr/mon-compte**  
+   - Identifiez‑vous avec votre identifiant et votre mot de passe.  
+   - Dans la rubrique **« Consommation data »** ou **« Mon forfait »**, vous trouverez le détail de votre utilisation (en Mo/Go) ainsi que le pourcentage de votre quota utilisé.
+2. **Application mobile TelecomPlus** (si vous l’avez)  
+   - Ouvrez l’application, puis accédez à la section **« Mon forfait »** → **« Data utilisée »**.
+3. **Contact direct avec le service client**  
+   - **Téléphone** : 3900 (appel gratuit, disponible 7 j/7 de 8 h à 20 h).  
+   - **Chat en ligne** : depuis le site web, cliquez sur l’icône de chat.  
+   - **Email** : support@telecomplus.fr.  
+   - Munissez‑vous de votre numéro de client ou de votre identifiant afin que l’agent puisse vous répondre rapidement.
+4. **Alertes SMS**  
+   - Si vous avez activé les alertes, vous recevez un SMS à 80 % et à 100 % de votre quota. Cela peut déjà vous donner une indication sur votre consommation actuelle.
+---
+### En cas de dépassement
+Si vous constatez que vous approchez ou avez dépassé votre forfait, vous avez deux options :
+- **Acheter un rechargement data** directement depuis votre espace client ou l’application.  
+- **Être facturé au Mo supplémentaire** selon les conditions de votre contrat (voir les détails dans votre offre).
+---
+N’hésitez pas à me recontacter si vous avez besoin d’aide pour la navigation dans votre espace client ou pour toute autre question relative à votre forfait.  
+Bonne journée et à très bientôt !</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -848,7 +1150,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>La réponse générée est totalement hors sujet et ne contient aucune information pertinente concernant la consommation data du client. Il s'agit d'un message générique 'Hello student, edit me please' qui ne répond absolument pas à la question posée et ne fournit aucune des informations présentes dans la réponse de référence (consommation de 3.20GB sur un forfait de 5GB).</t>
+          <t>La réponse générée ne fournit pas la consommation data actuelle du client, mais propose des méthodes pour y accéder.</t>
         </is>
       </c>
     </row>
@@ -868,7 +1170,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour Monsieur Bertrand,
+Merci pour votre message.  
+Pour connaître le montant exact de votre prochaine facture, il vous suffit de consulter votre espace client :
+1. Rendez‑vous sur **www.telecomplus.fr/mon-compte**.  
+2. Connectez‑vous avec votre identifiant et votre mot de passe.  
+3. Dans la rubrique **« Factures »**, vous verrez le détail de la facture en cours ainsi que le montant à payer pour le prochain cycle.
+&gt; **À noter** : le montant peut varier en fonction de plusieurs éléments (dépassage de forfait data, appels hors‑forfait, services premium, frais de roaming, etc.). Si vous avez récemment utilisé des services supplémentaires, ils seront détaillés ligne par ligne dans votre facture.
+### Que faire si le montant vous semble inattendu ?
+- **Vérifiez le détail** de chaque poste (data, appels, services optionnels).  
+- **Contactez notre service client** si vous avez besoin d’éclaircissements ou d’une éventuelle régularisation :
+  - **Téléphone** : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
+  - **Chat en ligne** : disponible depuis votre espace client  
+  - **Email** : support@telecomplus.fr  
+Nous restons à votre disposition pour toute aide supplémentaire.
+Cordialement,  
+L’équipe Service Client TelecomPlus.</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -876,7 +1193,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne répond aucunement à la question du client concernant le montant de sa prochaine facture. Elle ne contient aucune des informations essentielles présentes dans la réponse de référence (montant de 9.99€, date d'échéance). Il s'agit visiblement d'un message de test ou d'erreur plutôt que d'une réponse client.</t>
+          <t>La réponse générée par l'agent ne fournit pas le montant exact de la prochaine facture, contrairement à la réponse de référence.</t>
         </is>
       </c>
     </row>
@@ -896,7 +1213,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour Pierre,
+Merci pour votre message.  
+Dans le cadre de notre FAQ, nous n’avons pas accès aux informations personnelles de votre compte ni à l’historique de vos tickets de support. 
+**Voici les démarches les plus rapides pour vérifier si vous avez un ticket en cours :**
+| Canal | Comment faire | Délai moyen |
+|-------|---------------|-------------|
+| **Espace client** | Connectez‑vous à votre compte sur &lt;https://www.telecomplus.fr/mon-compte&gt; → « Mes tickets » ou « Historique du support ». | Immédiat |
+| **Téléphone** | Appelez le 3900 (appel gratuit, 7 j/7 de 8 h à 20 h) et indiquez votre nom et votre numéro de client. | 5‑10 min |
+| **Chat en ligne** | Ouvrez le chat depuis notre site web et identifiez‑vous avec votre compte. | 5 min |
+| **Email** | Envoyez un message à support@telecomplus.fr en précisant votre nom, votre numéro de client et votre demande. | 24‑48 h |
+Si vous ne retrouvez aucun ticket, il se peut que vous n’en ayez pas encore ouvert. Dans ce cas, n’hésitez pas à créer un nouveau ticket via l’un des canaux ci‑dessus ; notre équipe vous répondra dans les plus brefs délais.
+Je reste à votre disposition si vous avez besoin d’aide pour accéder à votre espace client ou pour toute autre question.
+Cordialement,  
+Service Client TelecomPlus.</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -904,7 +1234,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La réponse générée n'a aucun rapport avec la question du client. Elle ne mentionne pas les tickets en cours, ne confirme pas leur existence, et n'apporte aucune information pertinente. Il s'agit d'un message générique en anglais ('Hello student, edit me please') qui semble être un texte d'espace réservé et non une réponse réelle à la demande du client concernant ses tickets de support.</t>
+          <t>La réponse générée ne fournit pas d'information sur les tickets en cours du client, mais propose plutôt des démarches pour vérifier lui-même.</t>
         </is>
       </c>
     </row>
@@ -924,15 +1254,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour Monsieur Bertrand,
+Merci pour votre message.  
+En tant que service client TelecomPlus, nous ne disposons pas d’informations sur le coût global d’un voyage (billet d’avion, hébergement, activités, etc.) aux États-Unis.  
+Toutefois, nous pouvons vous aider à anticiper les frais liés à votre utilisation mobile pendant votre séjour :
+| Option | Description | Tarif indicatif* |
+|--------|-------------|------------------|
+| **Pass roaming international journalier** | 1 GB de data, appels et SMS illimités vers les États-Unis. | 9 € / jour |
+| **Pass roaming international hebdomadaire** | 5 GB de data, appels et SMS illimités vers les États-Unis. | 49 € / semaine |
+| **Tarif à la consommation** | Facturation au Mo supplémentaire (au‑delà de votre forfait) | 0,12 € / Mo (varie selon le contrat) |
+| **Désactivation des données mobiles** | Utilisez uniquement le Wi‑Fi pour éviter tout frais de data. | Gratuit (hors frais d’itinérance éventuels) |
+\*Les tarifs indiqués sont ceux en vigueur au moment de la rédaction de ce message et peuvent varier selon votre offre et votre contrat. Vous trouverez le détail exact dans votre espace client (section « Roaming ») ou en contactant notre service dédié.
+**Que faire maintenant ?**
+1. **Vérifier votre forfait actuel** – Connectez‑vous à votre espace client (www.telecomplus.fr/mon-compte) et consultez la rubrique « Roaming » pour connaître les options compatibles avec votre abonnement.  
+2. **Souscrire un pass** – Si vous prévoyez d’utiliser vos données à l’étranger, vous pouvez activer un pass journalier ou hebdomadaire directement depuis votre espace client, ou en appelant le 3900 (service gratuit, 7j/7 de 8h à 20h).  
+3. **Désactiver les données mobiles** – Avant de partir, pensez à désactiver les données mobiles dans les réglages de votre smartphone et à vous connecter à un réseau Wi‑Fi dès que possible.  
+Si vous avez besoin d’aide pour activer un pass, vérifier votre consommation ou toute autre question relative à votre ligne pendant votre voyage, n’hésitez pas à :
+- **Appeler le 3900** (gratuit, disponible 7 j/7 de 8 h à 20 h)  
+- **Utiliser le chat en ligne** sur www.telecomplus.fr  
+- **Envoyer un e‑mail** à support@telecomplus.fr  
+Nous restons à votre disposition pour toute assistance concernant votre abonnement mobile pendant votre séjour aux États-Unis.
+Cordialement,  
+L’équipe Service Client TelecomPlus  
+☎ 3900 – Chat en ligne – support@telecomplus.fr</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>La réponse générée n'a absolument aucun rapport avec la question du client concernant le coût d'un voyage aux États-Unis. Elle ne contient aucune information sur les pass internationaux, les forfaits, les tarifs ou les options disponibles pour l'itinérance. C'est une phrase générique sans aucune valeur informative qui ne répond pas du tout à la demande du client.</t>
+          <t>La réponse générée fournit des informations détaillées et précises sur les options de pass international et les tarifs, même si elle commence par une remarque sur les limites de leur connaissance concernant le coût global du voyage.</t>
         </is>
       </c>
     </row>
@@ -952,15 +1304,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour Monsieur Martin,
+Merci pour votre message.  
+### Résiliation sans frais : quelles sont les conditions ?
+| Situation | Frais de résiliation |
+|-----------|----------------------|
+| **Hors période d’engagement** (vous avez dépassé les 12 ou 24 mois prévus dans votre contrat) | **Gratuite** |
+| **Encore engagé** (vous êtes toujours dans la période d’engagement) | Des frais peuvent être appliqués, généralement équivalents aux mensualités restantes jusqu’à la fin du contrat. |
+&gt; **En résumé** : vous pouvez résilier sans frais uniquement si votre engagement est déjà terminé.
+### Comment vérifier votre situation ?
+1. **Espace client** – Connectez‑vous à votre compte sur &lt;https://www.telecomplus.fr/mon-compte&gt; et consultez la rubrique « Mon contrat ». Vous y trouverez la date de fin d’engagement.
+2. **Facture** – La dernière facture indique souvent la durée d’engagement restante.
+3. **Contact direct** – Si vous avez un doute, vous pouvez appeler le Service Client au **3900** (appel gratuit, 7 j/7 de 8 h à 20 h) ou utiliser le **chat en ligne** depuis votre espace client. Nos conseillers pourront vous confirmer votre statut en quelques minutes.
+### Démarches pour résilier (si vous êtes hors engagement)
+- **Via l’espace client** :  
+  1. Accédez à la section « Résilier mon abonnement ».  
+  2. Suivez les instructions et confirmez votre demande.  
+  3. La résiliation prendra effet sous **10 jours** à compter de la réception de votre demande.
+- **Par courrier recommandé** (si vous préférez) :  
+  1. Rédigez une lettre de résiliation avec vos coordonnées, numéro de contrat et la mention « Résiliation sans frais – hors période d’engagement ».  
+  2. Envoyez‑la en recommandé avec accusé de réception à l’adresse indiquée sur votre facture.  
+### Si vous êtes encore engagé
+- Les frais seront calculés sur la base des mensualités restantes.  
+- Vous avez la possibilité de **conserver votre numéro** en changeant d’opérateur ; dans ce cas, nous nous occupons de la résiliation et les frais restent les mêmes.
+### Besoin d’une assistance personnalisée ?
+- **Téléphone** : 3900 (gratuit, 7 j/7, 8 h‑20 h)  
+- **Chat en ligne** : depuis votre espace client  
+- **Email** : support@telecomplus.fr  
+- **Agence** : rendez‑vous dans l’agence la plus proche (voir &lt;https://www.telecomplus.fr/agences&gt;)
+N’hésitez pas à nous contacter avec votre numéro de contrat ; nous pourrons alors vous confirmer immédiatement si vous êtes hors engagement et lancer la résiliation sans frais.
+Nous restons à votre disposition pour toute question supplémentaire.
+Cordialement,  
+L’équipe Service Client TelecomPlus.</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' n'a aucun rapport avec la question du client sur la résiliation d'abonnement. Elle ne contient aucune des informations essentielles présentes dans la réponse de référence (date de début de contrat, fin de période d'engagement, gratuité de la résiliation). Il s'agit clairement d'un message de placeholder qui n'est pas destiné au client.</t>
+          <t>La réponse générée ne répond pas directement à la question du client, qui demande si son abonnement peut être résilié sans frais, alors que la réponse de référence fournit une réponse claire et directe basée sur les informations spécifiques du client.</t>
         </is>
       </c>
     </row>
@@ -980,15 +1363,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Merci pour votre question. Avec un budget de **1 000 €** et en souhaitant un stockage de **256 Go**, voici les modèles iPhone disponibles dans notre catalogue :
+| Modèle | Prix 256 GB |
+|--------|-------------|
+| **iPhone 11** | 659 € |
+| **iPhone 12** | 829 € |
+| **iPhone 13** | 929 € |
+| **iPhone 14** | **999 €** |
+| iPhone 15 | 1 099 € (dépasserait votre budget) |
+| iPhone 16 | 1 149 € (dépasserait votre budget) |
+| iPhone 17 | 1 299 € (dépasserait votre budget) |
+### Quelle option choisir ?
+- **iPhone 14 (999 €)** : il reste juste en dessous de votre plafond budgétaire et vous offre les dernières innovations de notre gamme : écran ProMotion 120 Hz, construction en titane, zoom optique 5×, puce A16, compatibilité 5G, Ceramic Shield et USB‑C Thunderbolt. C’est le meilleur compromis entre performance, design et longévité.
+- **iPhone 13 (929 €)** : très proche du prix de l’iPhone 14, il propose toujours un excellent écran Super Retina XDR, la puce A15 Bionic, et toutes les fonctionnalités de sécurité (Face ID, MagSafe). Si vous n’avez pas besoin du titane ou du ProMotion, c’est une option solide et légèrement moins chère.
+- **iPhone 12 (829 €)** : toujours compatible 5G, écran OLED, puce A14 Bionic. Il représente un bon rapport qualité/prix si vous cherchez à économiser davantage.
+- **iPhone 11 (659 €)** : le plus économique, avec des performances suffisantes pour la plupart des usages quotidiens, mais sans les dernières améliorations (5G, ProMotion, etc.).
+### Recommandation
+Si vous souhaitez profiter des dernières avancées technologiques tout en respectant votre budget, **l’iPhone 14 256 GB à 999 €** est le choix le plus adapté. Il vous offre les meilleures performances, une meilleure durabilité (titane, Ceramic Shield) et les fonctionnalités les plus récentes (USB‑C Thunderbolt, Apple Intelligence).
+### Prochaine étape
+1. **Vérifier la disponibilité** : rendez‑vous sur notre site www.telecomplus.fr ou appelez le **3900** (appel gratuit) pour confirmer le stock du modèle choisi.
+2. **Passer la commande** : vous pouvez commander en ligne avec livraison gratuite, ou vous rendre dans l’une de nos boutiques pour le tester en magasin.
+3. **Option reprise** : si vous avez un ancien smartphone, pensez à notre service de reprise ; vous pourriez obtenir une réduction supplémentaire sur votre nouvel iPhone.
+N’hésitez pas à me dire quel modèle vous intéresse le plus, ou si vous avez besoin d’aide pour finaliser votre achat. Je reste à votre disposition pour toute question supplémentaire.
+Cordialement,  
+L’équipe TelecomPlus – Service Client.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne répond absolument pas à la question sur les iPhone disponibles dans un budget de 1000€ en 256GB. Elle ne contient aucune information pertinente sur les modèles d'iPhone, leurs prix ou leurs capacités de stockage, contrairement à la réponse de référence qui mentionne précisément l'iPhone 14 et l'iPhone 15 avec leurs prix.</t>
+          <t>La réponse fournit les informations demandées, inclut l'iPhone 14 comme choix principal dans le budget, mais est plus détaillée et inclut d'autres options, ce qui la rend un peu plus longue et moins directe que la référence.</t>
         </is>
       </c>
     </row>
@@ -1008,15 +1415,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour Monsieur Bertrand,
+Merci pour votre message et pour la confiance que vous accordez à TelecomPlus.  
+Vous partez en Italie pour 10 jours ; voici les solutions les plus simples pour rester connecté sans surprise sur votre facture.
+---
+## 1. Vérifier votre forfait actuel  
+- **Forfait incluant le roaming Europe** : la plupart de nos forfaits « Euro » offrent les appels, SMS/MMS et un quota data utilisable dans l’ensemble de l’Union européenne (Italie incluse) sans frais supplémentaires.  
+- **Si votre forfait ne comporte pas le roaming Europe** : vous risquez d’être facturé au tarif « roaming », ce qui peut entraîner une facture plus élevée (voir FAQ : *« Une facture plus élevée peut résulter… frais de roaming international »*).
+---
+## 2. Options à souscrire pour votre séjour  
+| Option | Ce qu’elle couvre | Prix (exemple) | Comment l’activer |
+|--------|-------------------|----------------|-------------------|
+| **Option Europe** | Appels, SMS/MMS + 1 Go de data en roaming (renouvelable) | 5 €/mois | Depuis votre espace client → *Mon forfait* → *Ajouter une option* |
+| **Option Data Roaming** | Data supplémentaire en itinérance (500 Mo, 1 Go, 5 Go…) | 3‑12 €/mois selon le volume | Même procédure que ci‑dessus |
+| **Pass Voyage** (offre temporaire) | Data illimitée en Europe pendant 10 jours | 9,90 € (offre ponctuelle) | Contactez le service client (3900) ou le chat en ligne pour l’activer immédiatement |
+&gt; **Astuce** : si vous avez déjà un forfait « Euro », il suffit souvent d’ajouter l’option *Data Roaming* pour éviter toute coupure de data.
+---
+## 3. Démarches concrètes
+1. **Connectez‑vous à votre espace client** : www.telecomplus.fr/mon-compte  
+2. Rendez‑vous dans la section **« Mon forfait »** → **« Ajouter une option »**.  
+3. Sélectionnez l’option qui correspond le mieux à votre besoin (ex. : *Option Europe* ou *Pass Voyage*).  
+4. Confirmez l’ajout ; l’option sera active immédiatement ou à la prochaine période de facturation, selon votre choix.  
+&gt; **Si vous préférez être accompagné** : appelez le 3900 (gratuit, 7 j/7 de 8 h à 20 h) ou utilisez le chat en ligne. Nos conseillers pourront activer l’option en temps réel et vérifier que votre forfait actuel est bien compatible avec le roaming.
+---
+## 4. Points à retenir
+- **Aucun changement de forfait n’est obligatoire** ; une simple option suffit dans la plupart des cas.  
+- **Surveillez votre consommation** : vous recevrez une alerte SMS à 80 % et 100 % de votre quota data (voir FAQ : *« Que se passe‑t‑il si je dépasse mon forfait data ? »*).  
+- **Facturation** : la facturation de l’option se fait au prorata du mois ou sous forme d’abonnement mensuel, sans frais cachés.  
+---
+### Besoin d’aide supplémentaire ?
+- **Téléphone** : 3900 (gratuit)  
+- **Chat en ligne** : disponible sur www.telecomplus.fr  
+- **Email** : support@telecomplus.fr  
+Nous restons à votre disposition pour toute question ou pour activer l’option immédiatement. Bon voyage en Italie !
+Cordialement,  
+L’équipe Service Client TelecomPlus.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>La réponse générée est totalement hors sujet et ne contient aucune information pertinente. Elle ne répond pas du tout à la question du client concernant son forfait pour l'Italie, ne mentionne pas le roaming inclus dans l'UE, ni les conditions de son forfait actuel. C'est une phrase générique sans rapport avec la demande du client.</t>
+          <t>La réponse fournit des informations générales sur les options de roaming et les forfaits, mais ne répond pas directement à la question du client concernant son forfait actuel et les besoins spécifiques pour son voyage en Italie.</t>
         </is>
       </c>
     </row>
@@ -1036,15 +1477,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Merci pour votre intérêt pour l’iPhone 16.  
+Oui, chez TelecomPlus vous pouvez bénéficier d’une réduction en échangeant votre ancien téléphone grâce à notre programme **Reprise**.
+### Comment fonctionne la reprise ?
+| Étape | Description |
+|-------|-------------|
+| **1. Estimation** | Vous obtenez une estimation de la valeur de votre ancien appareil (iPhone, Android ou tout autre smartphone) : &lt;br&gt;• En boutique, nos conseillers évaluent votre téléphone sur place.&lt;br&gt;• En ligne, vous remplissez le formulaire de reprise sur www.telecomplus.fr et recevez une offre instantanée. |
+| **2. Conditions du téléphone** | Le dispositif doit être en bon état de fonctionnement (écran, batterie, ports, aucune détérioration majeure). Les modèles très anciens ou très endommagés peuvent être acceptés avec une valeur réduite. |
+| **3. Validation** | Une fois l’offre acceptée, vous pouvez : &lt;br&gt;• **En boutique** : remettre le téléphone à un conseiller qui vous remettra un bon de réduction à appliquer immédiatement sur l’achat de l’iPhone 16.&lt;br&gt;• **En ligne** : envoyer le téléphone via le service de collecte ou le déposer dans un point relais. Après vérification, le montant de la reprise vous sera crédité sous forme de bon d’achat valable sur votre prochaine commande. |
+| **4. Achat de l’iPhone 16** | Le bon de réduction est déduit du prix de l’iPhone 16 (livraison gratuite incluse). Vous pouvez choisir la couleur et la capacité souhaitées directement en boutique ou sur le site. |
+### Points importants à retenir
+- **Montant de la réduction** : il dépend du modèle et de l’état de votre ancien téléphone. Par exemple, un iPhone 13 en bon état peut rapporter entre 150 € et 250 €, tandis qu’un modèle plus ancien donnera une valeur moindre.  
+- **Validité du bon** : le bon de reprise est valable **30 jours** à compter de la date d’émission.  
+- **Livraison** : la commande en ligne bénéficie de la livraison gratuite, même avec le bon de réduction appliqué.  
+- **Pas de frais cachés** : aucune charge supplémentaire n’est appliquée pour le service de reprise.
+### Démarches concrètes pour vous
+1. **En boutique** : Rendez‑vous dans le magasin TelecomPlus le plus proche. Un conseiller évaluera votre ancien téléphone et vous remettra immédiatement le bon de réduction à appliquer sur l’iPhone 16.  
+2. **En ligne** :  
+   - Accédez à la page **Reprise** sur www.telecomplus.fr.  
+   - Sélectionnez le modèle de votre ancien téléphone, indiquez son état et validez.  
+   - Recevez votre offre par email.  
+   - Confirmez l’échange, choisissez le mode d’envoi (collecte à domicile ou dépôt en point relais).  
+   - Une fois le téléphone reçu et vérifié, le bon d’achat vous sera envoyé, à appliquer lors de la commande de l’iPhone 16.  
+### Besoin d’assistance ?
+- **Téléphone** : 3900 (appel gratuit) – nos conseillers sont disponibles pour vous guider pas à pas.  
+- **Chat en ligne** : disponible sur www.telecomplus.fr.  
+- **Boutique** : nos équipes sont à votre disposition pour une évaluation immédiate.
+Nous restons à votre disposition pour toute question supplémentaire ou pour vous accompagner dans votre échange.  
+Bonne journée et au plaisir de vous voir profiter de votre nouveau iPhone 16 !</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' est complètement hors sujet et ne contient aucune information pertinente concernant la question du client sur la reprise d'un ancien iPhone pour l'achat d'un iPhone 16. Il s'agit visiblement d'un message d'instruction ou d'erreur plutôt que d'une réponse client. Aucun élément de la réponse de référence n'est présent.</t>
+          <t>La réponse générée couvre tous les points clés de la réponse de référence, notamment le programme de reprise, les étapes pour obtenir une réduction, et les informations de contact pour une assistance supplémentaire. Cependant, elle fournit plus de détails que la réponse de référence, ce qui pourrait être considéré comme un plus, mais elle ne mentionne pas explicitement le prix de l'iPhone 16 comme dans la réponse de référence.</t>
         </is>
       </c>
     </row>
@@ -1064,15 +1533,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>**iPhone répondant à votre critère : 48 Mpx + 256 Go ≤ 1200 €**
+| Modèle (extrait du FAQ) | Caméra principale | Stockage disponible | Prix indiqué dans le FAQ |
+|--------------------------|-------------------|----------------------|--------------------------|
+| **iPhone 16** (2024)     | 48 Mpx (Fusion)   | 128 GB – 256 GB – 512 GB | *non communiqué* |
+Le seul modèle mentionné dans notre documentation qui possède **une caméra principale de 48 Mpx** et qui est disponible en **256 GB** est l’**iPhone 16**. Aucun tarif n’est indiqué dans la FAQ ; cependant, les iPhone 16 sont généralement positionnés dans la gamme « premium » avec un prix de lancement autour de **1200 €** pour la version 256 GB, ce qui correspond à votre budget.
+---
+### Que faire pour confirmer le prix ?
+1. **Vérifier en ligne**  
+   - Rendez‑vous sur notre boutique en ligne : **www.telecomplus.fr**  
+   - Recherchez « iPhone 16 256 GB ». Le prix affiché sera le tarif le plus à jour (promotions éventuelles incluses).
+2. **Contacter un conseiller**  
+   - **Par téléphone** : 3900 (appel gratuit) – un conseiller pourra vous confirmer le prix exact et la disponibilité en magasin.  
+   - **En boutique** : nos équipes peuvent vous faire une démonstration et vous proposer une offre personnalisée.
+3. **Comparer avec d’autres modèles**  
+   - Si le prix de l’iPhone 16 dépasse légèrement votre budget, nos conseillers peuvent vous proposer des alternatives (ex. : iPhone 15 Pro, qui possède également une caméra de 48 Mpx selon les dernières sorties, mais dont le prix n’est pas présent dans le FAQ).
+---
+### Résumé
+- **Modèle recommandé** : **iPhone 16**, caméra 48 Mpx, stockage 256 GB.  
+- **Prix** : non indiqué dans la FAQ ; il faut le vérifier en ligne ou auprès d’un conseiller.  
+- **Action conseillée** : consultez le site web ou appelez le 3900 pour obtenir le tarif exact et procéder à la commande.
+Nous restons à votre disposition pour toute aide supplémentaire !</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' est complètement hors sujet et ne contient aucune information pertinente concernant la question sur les iPhone avec caméra 48 Mpx sous 1200€. Elle ne mentionne ni les modèles disponibles, ni leurs prix, ni leurs caractéristiques techniques, contrairement à la réponse de référence qui détaille précisément les options (iPhone 15 et 16) correspondant aux critères du client.</t>
+          <t>La réponse fournit le modèle iPhone 16 avec une caméra de 48 Mpx et 256 GB, mais ne donne pas de prix exact et ne mentionne pas l'iPhone 15 comme alternative sous le budget de 1200€.</t>
         </is>
       </c>
     </row>
@@ -1092,15 +1581,48 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour Monsieur Bertrand,
+Merci pour votre demande.  
+### 1. Quel est le coût d’un passage à un forfait avec plus de data ?  
+Notre FAQ ne précise pas de tarif fixe pour l’augmentation de data, car le supplément dépend :
+| Variable | Impact sur le prix |
+|----------|-------------------|
+| **Le forfait actuel** (10 Go, 30 Go, 100 Go, etc.) | Chaque gamme a un prix de base différent. |
+| **Le volume de data supplémentaire souhaité** | Les forfaits « plus de data » sont proposés sous forme de nouvelles offres (ex. : +20 Go, +50 Go, +100 Go) avec un prix mensuel propre à chaque offre. |
+| **Le type d’abonnement** (engagement 12 mois, 24 mois ou sans engagement) | Les tarifs peuvent varier selon la durée d’engagement. |
+| **Promotions en cours** | Des offres promotionnelles (réduction de X % pendant les 3 ou 6 premiers mois) peuvent s’appliquer. |
+En résumé, le supplément mensuel **varie généralement entre 5 € et 25 €** selon le volume de data ajouté et le type d’engagement, mais le montant exact ne peut être déterminé qu’en consultant les offres actualisées.
+### 2. Comment connaître le prix exact qui vous correspond ?  
+1. **Espace client** – Connectez‑vous à votre compte :  
+   &lt;https://www.telecomplus.fr/mon-compte&gt;  
+   → rubrique **« Mes offres »** → **« Changer de forfait »**.  
+   Vous verrez toutes les options de data supplémentaires avec le prix mensuel affiché.
+2. **Site web – Catalogue des forfaits** – Rendez‑vous sur la page **Offres mobile** :  
+   &lt;https://www.telecomplus.fr/offres-mobile&gt;  
+   Chaque pack indique le volume de data et le tarif mensuel.
+3. **Contact direct** – Si vous préférez être conseillé·e en temps réel :  
+   - **Téléphone** : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
+   - **Chat en ligne** : disponible depuis la page d’accueil du site.  
+   - **Email** : support@telecomplus.fr  
+   Nos conseillers pourront vérifier votre contrat actuel, vous proposer les meilleures options et vous indiquer le coût additionnel exact.
+### 3. Points à retenir avant de changer d’offre  
+- **Alerte de consommation** : vous recevrez un SMS à 80 % et 100 % de votre quota.  
+- **Dépassement** : si vous dépassez le nouveau forfait, vous pouvez soit acheter un rechargement de data, soit être facturé au Mo supplémentaire selon les conditions de votre contrat.  
+- **Engagement** : un changement d’offre peut entraîner un nouveau délai d’engagement (12 ou 24 mois) ou, si vous êtes déjà engagé, un éventuel frais de modification (souvent nul, mais à vérifier).  
+---
+**En bref** : le supplément mensuel dépend du forfait que vous choisissez. Pour obtenir le montant précis, je vous invite à consulter votre espace client ou à contacter notre service client qui pourra vous proposer l’offre la plus adaptée à votre usage.
+N’hésitez pas à revenir vers moi si vous avez besoin d’aide pour la navigation sur le site ou pour planifier un appel avec un conseiller.
+Bonne journée,  
+**Service Client TelecomPlus**  
+📞 3900 – 📧 support@telecomplus.fr – 💬 Chat en ligne.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La réponse générée ne contient aucune information pertinente concernant la question du client sur le changement de forfait. Elle ne mentionne ni le forfait actuel, ni le forfait supérieur, ni la différence de prix, ni la procédure de changement. Il s'agit visiblement d'un message d'erreur ou d'un placeholder qui n'a aucun rapport avec la demande du client.</t>
+          <t>La réponse générée fournit des informations générales sur les facteurs influençant le coût d'un forfait avec plus de data, mais ne répond pas directement à la question du client concernant le coût supplémentaire pour son cas spécifique, contrairement à la réponse de référence qui donne un montant précis.</t>
         </is>
       </c>
     </row>
@@ -1120,15 +1642,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>Bonjour,
+Merci pour votre question ! 📸
+### Quel iPhone offre les meilleures performances photographiques ?
+**L’iPhone 15** se distingue actuellement comme le modèle le plus complet pour la photographie :
+| Caractéristique | iPhone 15 |
+|-----------------|-----------|
+| **Système photo** | Double caméra 12 MP (grand‑angle + téléobjectif) avec zoom optique 5× |
+| **Qualité d’image** | Capture d’images exceptionnelles dans toutes les conditions d’éclairage grâce aux capteurs avancés et à l’Apple Intelligence intégrée |
+| **Fonctions supplémentaires** | Mode cinématique, ProMotion 120 Hz, Dynamic Island, USB‑C Thunderbolt |
+| **Autonomie** | Jusqu’à 13 h de lecture vidéo (suffisant pour de longues sessions de prise de vue) |
+| **Sécurité** | Face ID pour une authentification sécurisée |
+| **Couleurs disponibles** | Gris sidéral, Argent (et d’autres teintes selon les stocks) |
+Ces spécifications font de l’iPhone 15 le choix le plus performant pour la photographie, que vous soyez amateur ou professionnel.
+### Alternatives selon votre budget
+| Modèle | Points forts photographiques | Prix généralement plus bas |
+|--------|-----------------------------|----------------------------|
+| **iPhone 14** | Caméra double 12 MP (grand‑angle + ultra grand‑angle), amélioration de l’autonomie (≈ 20 h vidéo) | Oui, souvent en promotion |
+| **iPhone 11** | Caméra simple 12 MP, puce A13 Bionic, bon rapport qualité/prix | Oui, modèle d’entrée de gamme |
+Si vous avez des contraintes budgétaires, l’iPhone 14 reste une excellente option, offrant une très bonne qualité d’image et des fonctionnalités avancées.
+### Que faire ensuite ?
+1. **Vérifier la disponibilité** – Rendez‑vous sur notre site [www.telecomplus.fr](http://www.telecomplus.fr) ou contactez notre service client.
+2. **Comparer les offres** – Nous proposons la livraison gratuite et, selon les promotions en cours, des remises ou des accessoires offerts.
+3. **Essayer en boutique** – Nos conseillers vous accueillent en magasin pour tester les modèles et vous conseiller en fonction de vos besoins spécifiques.
+---
+**Nos contacts**  
+- Téléphone (appel gratuit) : **3900**  
+- En boutique : démonstration de tous les modèles  
+- En ligne : commande sur www.telecomplus.fr (livraison gratuite)
+N’hésitez pas à nous recontacter si vous avez besoin d’aide pour choisir le modèle qui correspond le mieux à votre usage photographique ou pour toute autre question. Nous sommes là pour vous accompagner.
+Cordialement,  
+L’équipe TelecomPlus.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' est complètement hors sujet et ne contient aucune information pertinente sur les iPhones ou la photographie. Elle ne répond absolument pas à la question du client et ne présente aucune similarité avec la réponse de référence qui détaille les modèles d'iPhone et leurs capacités photographiques.</t>
+          <t>La réponse fournie par l'agent ne correspond pas à la référence, mentionnant l'iPhone 15 au lieu de l'iPhone 17 et ne fournissant pas les détails spécifiques sur le système photo avancé comme la triple caméra 48 Mpx et le capteur LiDAR.</t>
         </is>
       </c>
     </row>
@@ -1148,15 +1700,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Hello student, edit me please</t>
+          <t>**Bonjour,**
+Merci pour votre question concernant l’utilisation de votre iPhone à l’étranger.
+### 1. Rappel de la règle générale
+- **Le roaming (itinérance) international** peut entraîner des frais supplémentaires sur votre facture.  
+- Dans la FAQ, il est indiqué que **« une facture plus élevée peut résulter… de frais de roaming international »** (voir Q32).
+### 2. Ce qui dépend de votre situation
+| Situation | Coût éventuel |
+|-----------|----------------|
+| **Forfait incluant le roaming** (ex. : option « Europe », « Monde », etc.) | Aucun surcoût tant que vous restez dans les limites de l’option. |
+| **Forfait sans option roaming** | Facturation au tarif « hors‑forfait » (généralement plus élevé). |
+| **Utilisation de données, appels ou SMS** | Chaque service (data, appels, SMS) est facturé selon les tarifs roaming de votre offre. |
+### 3. Comment vérifier votre éligibilité
+1. **Connectez‑vous à votre espace client** : www.telecomplus.fr/mon-compte  
+   - Consultez la rubrique *Mon forfait* → *Options &amp; services* pour voir si une option roaming est déjà activée.
+2. **Vérifiez le détail de votre dernière facture** : les frais de roaming y sont clairement indiqués lorsqu’ils s’appliquent.
+3. **Contactez le service client** si vous avez besoin d’ajouter ou de modifier une option :
+   - **Téléphone** : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
+   - **Chat en ligne** : disponible sur notre site web  
+   - **Email** : support@telecomplus.fr  
+### 4. Démarches concrètes si vous n’avez pas d’option roaming
+- **Souscrire une option roaming** (ex. : « Roaming Europe », « Roaming Monde ») directement depuis votre espace client ou via un conseiller téléphonique.  
+- **Activer le mode « Data roaming »** uniquement lorsque vous êtes à l’étranger, et pensez à désactiver le data si vous ne souhaitez pas être facturé.
+### 5. En résumé
+- **Oui, vous pouvez utiliser votre iPhone à l’étranger**, mais **seul un forfait incluant une option roaming vous garantit l’absence de surcoût**.  
+- Sans cette option, les appels, SMS et l’utilisation de données seront facturés selon les tarifs roaming, ce qui peut augmenter votre facture (voir la FAQ Q32).
+Nous restons à votre disposition pour vous aider à vérifier ou à ajouter l’option qui vous convient le mieux.
+**Cordialement,**  
+Le service client TelecomPlus  
+📞 3900 – gratuit, 7 j/7 de 8 h à 20 h  
+💬 Chat en ligne – www.telecomplus.fr  
+✉️ support@telecomplus.fr</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La réponse générée 'Hello student, edit me please' est totalement hors sujet et ne contient aucune information pertinente concernant l'utilisation d'un iPhone à l'étranger. Elle ne mentionne ni le roaming en UE, ni les frais hors Europe, ni les options de pass internationaux présents dans la réponse de référence. Il s'agit visiblement d'un message d'erreur ou d'un texte placeholder qui n'a aucun rapport avec la question du client.</t>
+          <t>La réponse fournit des informations détaillées et exactes sur l'utilisation de l'iPhone à l'étranger, mais elle est plus longue et complexe que la réponse de référence, avec des détails supplémentaires qui ne sont pas directement liés à la question.</t>
         </is>
       </c>
     </row>

--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -477,25 +477,8 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>Bonjour,
-Merci pour votre question concernant les moyens de paiement disponibles chez TelecomPlus.
-**Nous acceptons les modes de paiement suivants :**
-| Mode de paiement | Principales caractéristiques |
-|------------------|------------------------------|
-| **Carte bancaire** (Visa, Mastercard, American Express) | Paiement sécurisé en ligne ou en boutique. |
-| **Prélèvement automatique** | Le montant de votre facture est prélevé chaque mois directement sur votre compte bancaire. Cette option vous garantit de ne jamais manquer une échéance. |
-| **Virement bancaire** | Vous pouvez effectuer un virement depuis votre compte bancaire en indiquant votre référence client. |
-| **PayPal** | Paiement en ligne via votre compte PayPal, pratique si vous préférez ne pas communiquer vos coordonnées bancaires directement. |
-**Comment choisir ou modifier votre moyen de paiement ?**  
-1. Connectez‑vous à votre espace client : [www.telecomplus.fr/mon-compte](https://www.telecomplus.fr/mon-compte).  
-2. Rendez‑vous dans la section **« Gestion des paiements »**.  
-3. Ajoutez, modifiez ou supprimez le mode de paiement souhaité.  
-**Besoin d’assistance ?**  
-- Téléphone : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
-- Chat en ligne : disponible sur notre site web  
-- Email : support@telecomplus.fr  
-Nous restons à votre disposition pour toute question supplémentaire ou pour vous accompagner dans la mise à jour de vos informations de paiement.
-Cordialement,  
-Service Client TelecomPlus</t>
+Nous acceptons les paiements par carte bancaire, prélèvement automatique, virement bancaire et PayPal. Le prélèvement automatique vous assure de ne jamais manquer une échéance.
+Vous pouvez choisir ou modifier votre mode de paiement directement depuis votre espace client, ou nous contacter au 3900 si vous avez besoin d’assistance.</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -503,7 +486,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>La réponse générée couvre tous les modes de paiement mentionnés dans la référence, y compris les détails sur le prélèvement automatique, et fournit même des informations supplémentaires sur la façon de gérer les paiements.</t>
+          <t>La réponse générée est quasi identique à la référence, avec les mêmes modes de paiement et les mêmes avantages pour le prélèvement automatique, avec des informations supplémentaires utiles.</t>
         </is>
       </c>
     </row>
@@ -524,41 +507,17 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>Bonjour,
-Pour consulter votre facture en ligne, il vous suffit de suivre les étapes ci‑dessous :
-1. **Accédez à votre espace client**  
-   Ouvrez votre navigateur et rendez‑vous sur :  
-   &lt;https://www.telecomplus.fr/mon-compte&gt;
-2. **Identifiez‑vous**  
-   - Saisissez votre identifiant (adresse e‑mail ou numéro de client)  
-   - Entrez votre mot de passe.  
-   *Si vous avez oublié votre mot de passe, cliquez sur « Mot de passe oublié » pour recevoir un lien de réinitialisation par e‑mail.*
-3. **Accédez à la section « Factures »**  
-   - Une fois connecté, cliquez sur le menu **« Factures »** (ou l’icône correspondante).  
-   - Vous verrez la liste de toutes vos factures mensuelles.
-4. **Visualisez ou téléchargez votre facture**  
-   - Cliquez sur la facture du mois souhaité pour l’ouvrir en PDF.  
-   - Vous pouvez la **télécharger** ou l’**imprimer** directement depuis votre navigateur.
-5. **Options supplémentaires**  
-   - Vous pouvez activer les **notifications par e‑mail** ou **SMS** afin d’être informé dès qu’une nouvelle facture est disponible.  
-   - Si vous souhaitez régler votre facture en ligne, la même page vous propose les moyens de paiement (carte bancaire, prélèvement automatique, PayPal, etc.).
----
-### En cas de difficulté
-- **Chat en ligne** : disponible directement sur le site web (icône de chat en bas à droite).  
-- **Téléphone** : appelez le 3900 (appel gratuit, 7 j/7 de 8 h à 20 h).  
-- **E‑mail** : support@telecomplus.fr  
-Nos conseillers sont à votre disposition pour vous aider à récupérer vos identifiants ou à résoudre tout problème d’accès.
----
-**Rappel important** : votre espace client est sécurisé et vous permet de consulter l’historique complet de vos factures, de vérifier les consommations (data, appels, SMS) et de gérer vos options de paiement.
-N’hésitez pas à nous contacter si vous avez besoin d’une assistance supplémentaire. Nous sommes là pour vous accompagner.  
-Bonne consultation !</t>
+Je n’ai pas votre nom dans le message, pourriez‑vous me le communiquer afin de personnaliser davantage ma réponse ?
+Pour consulter votre facture en ligne, il vous suffit de vous rendre sur le site : **www.telecomplus.fr/mon-compte**. Connectez‑vous avec vos identifiants, puis cliquez sur l’onglet « Factures » où vous trouverez le détail de chaque facture disponible au téléchargement.
+Souhaitez‑vous que je vous aide à réinitialiser votre mot de passe ou à récupérer vos identifiants ?</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>La réponse fournit les étapes détaillées pour consulter la facture en ligne, ce qui correspond à la réponse de référence, mais elle offre plus d'informations et d'options que la réponse idéale.</t>
+          <t>La réponse fournit les informations essentielles pour consulter la facture en ligne, mais manque de détails sur la disponibilité des factures pendant 24 mois et mentionne inutilement la réinitialisation du mot de passe.</t>
         </is>
       </c>
     </row>
@@ -579,47 +538,21 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>Bonjour,
-Oui, il est tout à fait possible de partager votre forfait data avec les membres de votre famille grâce à nos **forfaits famille**.  
-### Comment cela fonctionne ?
-- **Pool de données commun** : un volume de data (ex. 10 Go, 30 Go, etc.) est mis à disposition de plusieurs lignes que vous choisissez (généralement 2 à 5 lignes, mais le nombre exact dépend du forfait).
-- **Utilisation libre** : chaque ligne consomme les données du pool commun. Vous avez ainsi une visibilité globale sur la consommation totale via votre espace client.
-- **Gestion simplifiée** : vous pouvez ajouter ou retirer des lignes, consulter le solde restant et recevoir des alertes (80 % et 100 % du pool) par SMS.
-### Conditions importantes
-| Point | Détail |
-|-------|--------|
-| **Éligibilité** | Le titulaire du forfait doit être le responsable du compte (abonné principal). |
-| **Nombre de lignes** | Variable selon le forfait choisi (généralement de 2 à 5 lignes). |
-| **Facturation** | Une seule facture mensuelle regroupe l’ensemble des lignes du pool. |
-| **Modification** | Vous pouvez ajouter ou retirer des lignes à tout moment depuis votre espace client ; le changement prend effet à la prochaine période de facturation. |
-| **Dépassement** | Si le pool est épuisé, vous avez deux options : acheter un rechargement de data supplémentaire ou être facturé au Mo supplémentaire selon les conditions de votre contrat (voir Q32). |
-### Démarches concrètes pour souscrire à un forfait famille
-1. **Vérifier votre éligibilité**  
-   - Connectez‑vous à votre espace client : [www.telecomplus.fr/mon-compte](https://www.telecomplus.fr/mon-compte).  
-   - Consultez la rubrique « Forfaits famille » ou « Mes offres » pour voir les options disponibles.
-2. **Choisir le forfait qui vous convient**  
-   - Comparez les volumes de data proposés (ex. 10 Go, 30 Go, 50 Go) et le nombre de lignes maximum.
-3. **Activer le partage**  
-   - Depuis l’espace client, cliquez sur **« Ajouter une ligne famille »** et suivez les instructions (numéro de téléphone, nom du bénéficiaire, etc.).  
-   - Vous pouvez également le faire directement en boutique ou via notre service client.
-4. **Confirmer et suivre la consommation**  
-   - Une fois le forfait activé, vous recevrez un SMS de confirmation.  
-   - Vous pourrez suivre le solde du pool en temps réel dans votre tableau de bord.
-### Besoin d’assistance ?
-- **Par téléphone** : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
-- **Chat en ligne** : disponible sur notre site web  
-- **Email** : support@telecomplus.fr  
-- **En agence** : retrouvez l’agence la plus proche sur [www.telecomplus.fr/agences](https://www.telecomplus.fr/agences)
-N’hésitez pas à nous contacter si vous avez besoin d’aide pour choisir le forfait le plus adapté à votre usage familial ou pour toute autre question. Nous sommes là pour vous accompagner dans la mise en place du partage de data.
-Bonne journée et à très bientôt !  
-*L’équipe Service Client TelecomPlus*</t>
+Vous n’avez pas indiqué votre nom ni le numéro de votre ligne, ce qui nous empêche de vous identifier précisément dans notre système.
+Pour savoir si votre forfait actuel peut être transformé en forfait famille et connaître les conditions (nombre de lignes, volume de data partagé, tarif), vous pouvez :
+- appeler le service client au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h) ;
+- discuter en ligne via le chat disponible sur notre site web ;
+- envoyer un e‑mail à support@telecomplus.fr en précisant votre nom et votre numéro de ligne.
+Ces canaux vous permettront d’obtenir les détails exacts et de mettre en place le partage de data avec votre famille.
+Souhaitez‑vous que je vous indique les horaires d’ouverture du chat ou que je vous aide à préparer votre demande ?</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>La réponse générée fournit une explication détaillée et complète sur les forfaits famille, incluant les conditions, les démarches pour souscrire et les moyens de contacter le service client, répondant ainsi parfaitement à la question du client.</t>
+          <t>La réponse fournit les informations nécessaires pour que le client puisse partager son forfait data avec sa famille, mais elle est plus verbale et demande des informations supplémentaires avant de fournir une réponse directe.</t>
         </is>
       </c>
     </row>
@@ -640,30 +573,20 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>Bonjour,
-Le roaming international est **généralement activé par défaut** sur votre ligne TelecomPlus.  
-Voici comment vérifier et, le cas échéant, activer le service :
-1. **Connectez‑vous à votre espace client** (www.telecomplus.fr/mon-compte).  
-2. Rendez‑vous dans la rubrique **« Gestion de mon forfait »** → **« Paramètres roaming »**.  
-3. Vérifiez que le bouton **« Roaming international »** est bien positionné sur **« Activé »**.  
-   - Si le bouton indique « Désactivé », cliquez dessus pour le mettre sur « Activé », puis validez.  
-4. **Enregistrez** les modifications. Le changement prend effet immédiatement.
-&gt; **Astuce :** même si le roaming est activé, il est recommandé de vérifier les tarifs applicables à votre forfait avant votre départ, afin d’éviter toute surprise sur votre facture.
----
-### Si vous ne voyez pas l’option ou avez un doute :
-- **Appelez le service client** au **3900** (appel gratuit, 7 j/7 de 8 h à 20 h).  
-- **Chat en ligne** disponible sur notre site web.  
-- Vous pouvez également vous rendre dans l’une de nos agences.
-Nous restons à votre disposition pour toute aide supplémentaire.
-Cordialement,  
-Service Client TelecomPlus.</t>
+Je n’ai pas de nom ni de numéro de ligne dans votre message, ce qui m’empêche de vérifier directement le statut de votre roaming.  
+Pour activer ou vérifier le roaming international :  
+- Connectez‑vous à votre espace client (www.telecomplus.fr/mon‑compte) et consultez la rubrique « Gestion du roaming ».  
+- Vous pouvez également appeler le service client au 3900 (appel gratuit, disponible 7 j/7 de 8 h à 20 h) ; un conseiller pourra activer le service immédiatement si besoin.  
+En règle générale, le roaming est déjà activé par défaut, il suffit donc de vérifier qu’il est bien actif avant votre départ.  
+Si vous avez besoin d’aide supplémentaire, n’hésitez pas à utiliser le chat en ligne sur notre site ou à vous rendre dans l’une de nos agences.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>La réponse générée couvre tous les points de la réponse de référence, y compris l'activation par défaut, la vérification dans l'espace client et la recommandation de vérifier les tarifs, avec des détails supplémentaires pour une aide plus complète.</t>
+          <t>La réponse générée couvre les points clés de la réponse de référence, notamment l'activation par défaut du roaming international et les moyens de vérifier son statut, mais elle est plus détaillée et inclut des informations supplémentaires sur les canaux de support.</t>
         </is>
       </c>
     </row>
@@ -684,35 +607,17 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>Bonjour,
-Dans l’Union européenne, **le roaming « comme à la maison » s’applique** à tous les forfaits TelecomPlus. Concrètement :
-| Pays concernés | Tarif appliqué | Conditions |
-|----------------|----------------|------------|
-| Tous les États membres de l’UE (et les pays de l’EEE) | Aucun surcoût : vous utilisez votre forfait français (appels, SMS/MMS et data) aux mêmes tarifs qu’en France | Respect des limites de votre contrat (fair‑use). Au‑delà de ces seuils, des frais supplémentaires peuvent s’appliquer (voir votre espace client). |
-### Ce que cela signifie pour vous
-- **Appels et SMS/MMS** : facturés comme en France, sans frais additionnels.  
-- **Data mobile** : vous pouvez consommer votre quota data habituel. Si vous dépassez le plafond de fair‑use (défini dans votre contrat), des frais de data roaming peuvent être appliqués.  
-- **Activation** : le roaming est généralement activé par défaut. Vous pouvez le vérifier dans votre espace client ou en appelant le 3900.
-### Vérifier vos limites
-1. Connectez‑vous à votre compte sur **www.telecomplus.fr/mon-compte**.  
-2. Consultez la rubrique **« Mon forfait »** → **« Conditions de roaming »** pour connaître le plafond de fair‑use qui vous concerne.  
-3. Si vous avez besoin d’un suivi en temps réel, activez les notifications de consommation data dans l’application mobile.
-### Que faire si vous avez besoin d’un dépassement ou d’un pass supplémentaire
-- **Pass data additionnel** : disponible à l’achat directement depuis votre espace client (option « Pass roaming »).  
-- **Assistance** : si vous avez le moindre doute, notre service client est à votre disposition :  
-  - Téléphone : **3900** (appel gratuit, 7j/7 de 8 h à 20 h)  
-  - Chat en ligne : via le site web  
-  - Email : **support@telecomplus.fr**
-Nous restons à votre écoute pour toute question complémentaire ou pour vous aider à configurer votre roaming avant votre départ.
-Cordialement,  
-L’équipe Service Client TelecomPlus.</t>
+Dans l’Union européenne, le roaming fonctionne « comme à la maison » : vous pouvez utiliser votre forfait français sans frais supplémentaires dans tous les pays de l’UE, dans la limite des volumes (appels, SMS, data) prévus par votre contrat.  
+Si vous souhaitez vérifier les plafonds exacts de votre offre ou activer le roaming, il suffit de consulter votre espace client ou de nous appeler au 3900 (appel gratuit).  
+Nous restons à votre disposition pour tout complément d’information.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>La réponse générée par l'agent fournit les mêmes informations que la réponse de référence, avec plus de détails sur les conditions et les limites du roaming dans l'UE.</t>
+          <t>La réponse générée est très proche de la référence, avec les mêmes informations clés sur le roaming dans l'UE, mais contient des détails supplémentaires sur la vérification des plafonds et le contact pour plus d'informations.</t>
         </is>
       </c>
     </row>
@@ -733,30 +638,18 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>Bonjour,
-Je comprends que vous ayez perdu votre mot de passe, cela arrive à tout le monde. Voici la démarche à suivre pour le réinitialiser :
-1. **Accédez à la page de connexion** de votre espace client :  
-   &lt;https://www.telecomplus.fr/mon-compte&gt;
-2. Cliquez sur le lien **« Mot de passe oublié »** situé sous les champs de connexion.
-3. Vous serez invité à indiquer **votre adresse e‑mail ou votre numéro de téléphone** associé à votre compte.
-4. Un **lien de réinitialisation** vous sera envoyé par e‑mail ou un **code SMS** selon le moyen que vous avez choisi.
-5. Ouvrez le message reçu, cliquez sur le lien (ou saisissez le code) et suivez les instructions pour créer un **nouveau mot de passe**. Veillez à choisir un mot de passe sécurisé (au moins 8 caractères, incluant lettres, chiffres et éventuellement un symbole).
-6. Une fois le nouveau mot de passe enregistré, vous pourrez vous reconnecter immédiatement à votre espace client.
----
-### Besoin d’assistance supplémentaire ?
-- **Téléphone** : 3900 (appel gratuit, disponible 7 j/7 de 8 h à 20 h)  
-- **Chat en ligne** : depuis le site web, rubrique « Assistance »  
-- **E‑mail** : support@telecomplus.fr  
-- **Agence** : rendez‑vous dans l’une de nos boutiques (voir &lt;www.telecomplus.fr/agences&gt;)
-N’hésitez pas à nous contacter si vous rencontrez la moindre difficulté lors de la réinitialisation. Nous sommes là pour vous aider.
-Bonne journée et à très vite sur votre compte !</t>
+Pour réinitialiser votre mot de passe, cliquez sur le lien **« Mot de passe oublié »** présent sur la page de connexion de votre espace client. Vous recevrez alors un lien de réinitialisation par email ou SMS ; suivez simplement les instructions pour créer un nouveau mot de passe.
+Si vous ne recevez pas le lien ou rencontrez une difficulté, vous pouvez contacter notre service client au **3900** (appel gratuit, disponible 7 j/7 de 8 h à 20 h) ou via le chat en ligne sur notre site.  
+À très vite,  
+L’équipe Service Client TelecomPlus.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>La réponse générée par l'agent est très détaillée et suit parfaitement les étapes indiquées dans la réponse de référence, avec des explications supplémentaires pour aider le client.</t>
+          <t>La réponse générée couvre les mêmes étapes que la référence, avec des détails supplémentaires sur les options de support, mais reste pertinente et utile.</t>
         </is>
       </c>
     </row>
@@ -777,46 +670,20 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>Bonjour,
-Voici comment configurer les paramètres MMS de votre téléphone :
-1. **Vérifiez la configuration automatique**  
-   Dans la plupart des cas, les paramètres MMS sont configurés automatiquement dès l’activation de votre carte SIM. Essayez d’envoyer un MMS ; si cela fonctionne, aucune action supplémentaire n’est nécessaire.
-2. **Si les MMS ne fonctionnent pas, configurez manuellement le point d’accès (APN)**  
-   a. Ouvrez **Réglages** (ou **Paramètres**) de votre appareil.  
-   b. Sélectionnez **Réseau mobile** (ou **Cellulaire**).  
-   c. Appuyez sur **Noms des points d’accès** (ou **APN**).  
-   d. Ajoutez un nouveau point d’accès en utilisant les informations suivantes (disponibles sur notre site : [www.telecomplus.fr/apn-mms](https://www.telecomplus.fr/apn-mms)) :  
-| Champ | Valeur (exemple) |
-|-------|------------------|
-| **Nom** | TelecomPlus MMS |
-| **APN** | mms.telecomplus.fr |
-| **Nom d’utilisateur** | (laisser vide) |
-| **Mot de passe** | (laisser vide) |
-| **MMSC** | http://mms.telecomplus.fr |
-| **Proxy MMS** | 0.0.0.0 |
-| **Port MMS** | 0 |
-| **Type d’APN** | mms |
-| **Protocole APN** | IPv4/IPv6 |
-| **Portée APN** | default,supl |
-   e. Enregistrez le nouveau point d’accès, puis sélectionnez‑le comme APN actif.  
-   f. Redémarrez votre téléphone pour que les modifications prennent effet.
-3. **Testez l’envoi d’un MMS**  
-   Après le redémarrage, essayez d’envoyer à nouveau un MMS. Si le message part correctement, la configuration est terminée.
----
-### En cas de difficulté
-- **Vérifiez la connexion réseau** : assurez-vous d’être en 4G/5G ou en 3G, car les MMS ne fonctionnent pas en mode 2G uniquement.  
-- **Mise à jour du système** : assurez‑vous que votre téléphone dispose de la dernière version logicielle disponible.  
-- **Contactez le support** : si le problème persiste malgré ces étapes, n’hésitez pas à nous appeler au **0 800 123 456** ou à ouvrir un chat en direct depuis votre espace client. Nous pourrons vérifier votre ligne et vous guider plus en détail.
-Nous restons à votre disposition pour toute question supplémentaire.  
-Cordialement,  
-Service Client TelecomPlus.</t>
+Les paramètres MMS sont normalement configurés automatiquement sur votre téléphone.  
+Si ce n’est pas le cas, suivez ces étapes :
+1. Ouvrez **Réglages** → **Réseau mobile** → **Noms des points d’accès**.  
+2. Ajoutez un nouveau point d’accès en renseignant la configuration MMS que vous trouverez sur notre site : [www.telecomplus.fr/config-mms](https://www.telecomplus.fr/config-mms).
+Une fois le point d’accès enregistré, redémarrez votre appareil et vos MMS devraient fonctionner.  
+Si vous rencontrez encore des difficultés, n’hésitez pas à nous contacter par téléphone ou via le chat en ligne pour une assistance immédiate.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>La réponse générée par l'agent est très détaillée et fournit les mêmes informations que la réponse de référence, avec des étapes supplémentaires pour aider le client en cas de difficulté.</t>
+          <t>La réponse générée est très proche de la référence, avec les mêmes étapes et informations, mais inclut des détails supplémentaires tels que le lien vers le site et des instructions pour le cas où les MMS ne fonctionnent toujours pas.</t>
         </is>
       </c>
     </row>
@@ -837,23 +704,11 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>Bonjour,
-Merci pour votre demande concernant le prix de l’iPhone 15 en version 256 Go.
-**Ce que nous savons d’après la documentation fournie :**
-- L’iPhone 15 est présenté dans notre catalogue avec ses caractéristiques (couleurs, autonomie, etc.).
-- Aucun tarif n’est indiqué dans le PDF de la FAQ ni dans les données tabulaires dont nous disposons.
-**Comment obtenir le prix exact ?**
-1. **Site web** – Rendez‑vous sur notre boutique en ligne :  
-   &lt;https://www.telecomplus.fr&gt;  
-   → Sélectionnez « iPhone 15 » → Choisissez la capacité « 256 GB ». Le prix affiché sera le tarif en vigueur, incluant éventuellement les promotions ou les options de financement.
-2. **Appel téléphonique** – Vous pouvez contacter notre service client au **3900 (appel gratuit)**. Nos conseillers vous communiqueront le tarif actuel et pourront vous conseiller sur les offres de paiement échelonné ou les packs accessoires.
-3. **Boutique physique** – Si vous préférez un échange en face à face, nos équipes en boutique sont à votre disposition. Elles pourront vous montrer le produit, vous indiquer le prix et même vous proposer une démonstration.
-4. **Demande par e‑mail** – Envoyez un message à **serviceclient@telecomplus.fr** avec la référence « iPhone 15 256 GB ». Vous recevrez une réponse écrite contenant le prix ainsi que les éventuelles conditions de garantie et de livraison.
-**À retenir :**
-- Le prix peut varier selon les promotions en cours, le mode de paiement choisi (paiement comptant, crédit, abonnement) et la disponibilité du stock.
-- La livraison standard est gratuite pour les commandes en ligne, comme indiqué dans la FAQ.
-Je reste à votre disposition si vous avez besoin d’aide pour finaliser votre achat ou pour toute autre question. N’hésitez pas à me préciser si vous souhaitez être rappelé ou si vous avez besoin d’informations complémentaires (options de financement, assurance, accessoires compatibles, etc.).
-Cordialement,  
-L’équipe TelecomPlus – Service Client.</t>
+Nous ne disposons pas du tarif exact de l’iPhone 15 256 Go dans notre base de connaissances. Vous pouvez obtenir ce prix en :
+- consultant le catalogue en ligne sur www.telecomplus.fr (livraison gratuite)  
+- appelant notre service client au 3900 (appel gratuit)  
+- vous rendant dans l’une de nos boutiques où les modèles sont exposés.
+Nos conseillers se tiennent également à votre disposition pour vous proposer les meilleures offres et options de financement. N’hésitez pas à les contacter pour plus de détails.</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -861,7 +716,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>La réponse générée par l'agent ne fournit pas le prix de l'iPhone 15 en 256GB, contrairement à la réponse de référence qui donne le prix exact.</t>
+          <t>La réponse générée ne fournit pas le prix de l'iPhone 15 en 256GB, mais propose des alternatives pour obtenir l'information.</t>
         </is>
       </c>
     </row>
@@ -881,37 +736,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>**Réponse :**  
-L’iPhone commercialisé en 2023 est l’**iPhone 15**.
----
-### Pourquoi cet iPhone ?  
-- **Date de sortie officielle** : Apple a présenté l’iPhone 15 en septembre 2023, marquant le lancement de la génération suivante après l’iPhone 14 (2022).  
-- **Disponibilité chez TelecomPlus** : L’iPhone 15 figure dans notre catalogue actuel (voir le tableau des prix) et est disponible en plusieurs capacités de stockage (128 Go, 256 Go, 512 Go).
----
-### Comment l’obtenir chez TelecomPlus ?  
-| Action | Détails |
-|--------|---------|
-| **En ligne** | Rendez‑vous sur &lt;https://www.telecomplus.fr&gt; → choisissez le modèle iPhone 15, la capacité souhaitée et ajoutez‑le à votre panier. Livraison gratuite à domicile. |
-| **En boutique** | Visitez l’une de nos agences (liste sur &lt;https://www.telecomplus.fr/agences&gt;) pour tester le téléphone en magasin et le retirer immédiatement. |
-| **Par téléphone** | Appelez le **3900** (appel gratuit, 7 j/7 de 8 h à 20 h) ; un conseiller vous guidera dans le choix du stockage et du forfait le plus adapté. |
-| **Échange / reprise** | Si vous avez un ancien smartphone, profitez de notre programme de reprise : vous bénéficiez d’une remise immédiate sur l’achat de l’iPhone 15. |
----
-### Points à retenir  
-- **Compatibilité** : Tous les iPhone 15 sont compatibles avec nos forfaits mobiles (4G/5G) et les services additionnels (data, roaming, etc.).  
-- **Garantie** : Vous bénéficiez de la garantie légale de conformité (2 ans) ainsi de la garantie constructeur Apple (1 an).  
-- **Assistance** : En cas de question technique ou de configuration, notre service client (téléphone, chat en ligne, email) reste à votre disposition.
----
-**Besoin d’un accompagnement personnalisé ?**  
-N’hésitez pas à nous contacter par le canal qui vous convient le mieux ; nous serons ravis de vous aider à finaliser votre achat ou à répondre à toute autre interrogation.  
-*Merci de votre confiance, l’équipe TelecomPlus.*</t>
+          <t>Bonjour,
+Aucun des éléments fournis dans la base de connaissances ne précise quel iPhone a été commercialisé en 2023.  
+Pour connaître le modèle sorti cette année, vous pouvez :
+- consulter la page « Catalogue Téléphones » de notre site www.telecomplus.fr, qui indique les dates de sortie de chaque modèle,  
+- appeler notre service client au 3900 (appel gratuit) ou utiliser le chat en ligne disponible sur notre site.
+En attendant, si vous cherchez un modèle récent, notre catalogue propose l’iPhone 15, l’iPhone 16 et l’iPhone 17, tous disponibles avec plusieurs capacités de stockage. N’hésitez pas à nous contacter pour obtenir des conseils personnalisés ou vérifier la date de commercialisation exacte.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>La réponse générée par l'agent fournit l'information exacte demandée par le client, à savoir que l'iPhone 15 a été commercialisé en 2023, et offre même des détails supplémentaires sur la disponibilité et les options d'achat.</t>
+          <t>La réponse fournie par l'agent ne répond pas directement à la question, mais suggère que l'iPhone 15 pourrait être le modèle sorti en 2023, ce qui est correct, mais elle ne le confirme pas explicitement et propose des alternatives pour obtenir l'information exacte.</t>
         </is>
       </c>
     </row>
@@ -931,22 +769,9 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>**Bonjour,**
-Merci pour votre question concernant les coloris de l’iPhone 16.  
-Dans la documentation que nous avons à disposition, la section dédiée à l’iPhone 16 décrit ses caractéristiques techniques (écran 6,1 pouces Super Retina XDR OLED, puce A18, design tout‑écran, etc.) mais ne précise pas la liste exacte des coloris proposés.
-### Que faire pour connaître les coloris disponibles ?
-1. **Consulter la page produit officielle** – Le site web de TelecomPlus (ou la boutique Apple) indique généralement la gamme de couleurs au moment du lancement.  
-2. **Contacter notre service commercial** – Vous pouvez appeler le +33 1 23 45 67 89 ou nous écrire à **sales@telecomplus.fr** ; nous vous transmettrons la liste exacte et les éventuelles éditions limitées.  
-3. **Passer en magasin** – Nos conseillers en boutique pourront vous présenter les modèles en stock et vous faire découvrir les finitions disponibles.
-### Points à retenir
-- La FAQ ne mentionne pas les coloris de l’iPhone 16, mais les modèles précédents (iPhone 14, iPhone 13, etc.) proposaient des teintes telles que Noir, Blanc, Bleu, Vert, Rouge (PRODUCT)RED, Mauve, etc.  
-- Il est possible que l’iPhone 16 conserve une partie de ces teintes tout en introduisant de nouvelles finitions (par exemple, des variantes « infusées de couleur » mentionnées pour les modèles récents).  
-- Les disponibilités peuvent varier selon les stocks et les régions.
----
-**Je reste à votre disposition** si vous avez besoin d’aide pour vérifier la disponibilité d’un coloris précis, pour réserver un appareil ou pour toute autre question relative à votre futur iPhone 16.
-Cordialement,  
-*Service Client – TelecomPlus*  
-📞 +33 1 23 45 67 89 | ✉️ support@telecomplus.fr</t>
+          <t>Bonjour,
+Les coloris disponibles pour l’iPhone 16 sont : stellaire, bleu, rose, rouge (PRODUCT RED) et vert.  
+Si vous avez besoin d’aide pour choisir le modèle ou pour passer commande, n’hésitez pas à me le faire savoir.</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -954,7 +779,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>La réponse générée par l'agent ne fournit pas directement les coloris disponibles pour l'iPhone 16, mais propose des méthodes pour obtenir cette information, montrant un manque d'exactitude et de complétude par rapport à la réponse de référence.</t>
+          <t>Les couleurs mentionnées dans les deux réponses sont différentes, indiquant une discordance significative dans l'information fournie.</t>
         </is>
       </c>
     </row>
@@ -974,29 +799,8 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>**Réponse à votre demande**
-| Modèle | Stockage 128 GB | Prix indiqué |
-|--------|----------------|--------------|
-| iPhone 11 | 128 GB | **559 €** |
-| iPhone 12 | 128 GB | 729 € |
-| iPhone 13 | 128 GB | 809 € |
-| iPhone 14 | 128 GB | 869 € |
-| iPhone 15 | 128 GB | 969 € |
-| iPhone 16 | 128 GB | 1 019 € |
-&gt; **L’iPhone le moins cher disponible en 128 GB est donc l’iPhone 11, au prix de 559 €.**  
----
-### Points à retenir
-1. **Disponibilité** – Le catalogue reflète les prix au **04/11/2025**. Selon les stocks, certains modèles peuvent être momentanément en rupture.  
-2. **Compatibilité** – Tous les modèles listés sont compatibles avec les forfaits TelecomPlus.  
-3. **Livraison** – La commande en ligne (www.telecomplus.fr) bénéficie de la livraison gratuite.  
----
-### Que faire ensuite ?
-- **Commande en ligne** : Rendez‑vous sur notre site, choisissez *iPhone 11 – 128 GB* et finalisez votre achat en quelques clics.  
-- **Assistance téléphonique** : Si vous avez besoin d’aide pour la configuration ou le choix du forfait, appelez le **3900 (appel gratuit)**.  
-- **Boutique physique** : Vous pouvez également vous rendre dans l’une de nos boutiques pour tester le modèle et le retirer immédiatement.  
-Nous restons à votre disposition pour toute question complémentaire ou pour vous accompagner dans votre achat.  
-Cordialement,  
-L’équipe TelecomPlus – Service Client.</t>
+          <t>Bonjour,
+Le modèle iPhone le moins cher proposé avec une capacité de 128 Go est l’**iPhone 11**, au prix de **559 €**.</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1004,7 +808,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>La réponse générée fournit exactement la même information que la référence, avec le même modèle d'iPhone et le même prix, et offre même des détails supplémentaires utiles pour le client.</t>
+          <t>La réponse générée par l'agent fournit exactement la même information que la référence, avec le même modèle d'iPhone et le même prix.</t>
         </is>
       </c>
     </row>
@@ -1024,31 +828,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>**Bonjour,**
-Merci pour votre question concernant l’autonomie des iPhone 13 et iPhone 16. Voici les informations disponibles dans notre documentation :
-| Modèle | Autonomie annoncée (lecture vidéo) |
-|--------|------------------------------------|
-| **iPhone 13** (2021) | Jusqu’à **17 heures** de lecture vidéo |
-| **iPhone 16** (2024) | *Aucune donnée d’autonomie précise n’est fournie dans le PDF de notre FAQ* |
-### Ce que cela signifie pour vous
-- **iPhone 13** : Vous pouvez profiter d’environ 17 heures de vidéo en continu, ce qui couvre largement une journée d’utilisation intensive sans recharger.
-- **iPhone 16** : Le document que nous possédons ne précise pas la durée exacte de la batterie. Apple a généralement amélioré l’efficacité énergétique avec chaque génération (puce A18, écran Super Retina XDR OLED, etc.), il est donc probable que l’iPhone 16 offre une autonomie au moins équivalente, voire supérieure, à celle de l’iPhone 13.  
-### Que faire si vous avez besoin de plus de précisions ?
-1. **Consulter le site officiel d’Apple** – les fiches techniques détaillent les heures de lecture vidéo, de navigation web, etc.
-2. **Nous contacter directement** – nous pouvons vous transmettre les dernières spécifications techniques ou vous orienter vers un conseiller spécialisé.
-3. **Tester en magasin** – si vous avez la possibilité de passer dans l’un de nos points de vente, vous pourrez comparer les deux modèles en conditions réelles.
-Nous restons à votre disposition pour toute information complémentaire ou pour vous aider à choisir le modèle qui correspond le mieux à vos besoins.
-**Cordialement,**  
-Le service client TelecomPlus  
-📞 0 800 123 456 – disponible du lundi au vendredi, 9 h–18 h.</t>
+          <t>Bonjour,
+L’iPhone 13 offre une autonomie allant jusqu’à **17 heures de lecture vidéo**.  
+Pour l’iPhone 16, les informations d’autonomie ne figurent pas dans les données dont je dispose.
+Vous pouvez obtenir ce détail en consultant la fiche produit de l’iPhone 16 sur notre site ou en contactant notre service client, qui pourra vous fournir les spécifications exactes.  
+N’hésitez pas si vous avez besoin d’aide supplémentaire pour choisir le modèle qui correspond le mieux à vos usages.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>La réponse fournit des informations sur l'autonomie des deux modèles, mais les valeurs sont différentes de celles de la référence et l'agent n'a pas pu fournir la différence exacte pour l'iPhone 16 en raison du manque de données.</t>
+          <t>L'agent fournit des informations partielles et incorrectes sur l'iPhone 13 et ne fournit pas d'informations sur l'iPhone 16, ce qui ne permet pas de comparer les autonomies.</t>
         </is>
       </c>
     </row>
@@ -1069,37 +861,20 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>Bonjour,
-Merci pour votre question.
-**Frais de résiliation lorsque vous êtes encore engagé**
-- **Oui, des frais peuvent s’appliquer** si vous résiliez avant la fin de votre période d’engagement (12 ou 24 mois selon votre offre).  
-- Le montant de ces frais correspond généralement **au total des mensualités restantes** jusqu’à la fin du contrat. Par exemple, si vous avez encore 6 mois d’engagement à 30 € / mois, les frais seront d’environ 180 €.
-**Quand la résiliation est gratuite ?**  
-- Si vous avez dépassé la période d’engagement (c’est‑à‑dire que votre contrat a déjà 12 ou 24 mois selon le cas), la résiliation est alors **gratuite**.
-**Comment connaître le montant exact ?**  
-1. **Consultez votre espace client** (www.telecomplus.fr/mon-compte) → « Mon contrat » → détail des engagements restants.  
-2. Vous pouvez également **contacter notre service client** qui vous indiquera le montant précis :  
-   - Téléphone : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
-   - Chat en ligne sur notre site web  
-   - Email : support@telecomplus.fr  
-**Démarches de résiliation**  
-- Si vous décidez de résilier, vous pouvez le faire **en ligne** depuis votre espace client (si vous êtes hors période d’engagement) ou **par lettre recommandée avec accusé de réception**.  
-- La résiliation prend effet **dans les 10 jours** suivant la réception de votre demande.
----
-**En résumé**  
-- Engagé ? → Des frais égaux aux mensualités restantes peuvent être facturés.  
-- Hors engagement ? → La résiliation est gratuite.
-N’hésitez pas à nous contacter pour obtenir le calcul exact de vos frais ou pour toute assistance supplémentaire. Nous sommes là pour vous accompagner dans votre démarche.
-Cordialement,  
-Service Client TelecomPlus  
-📞 3900 – 📧 support@telecomplus.fr – 💬 Chat en ligne disponible sur notre site.</t>
+Oui, des frais de résiliation peuvent s’appliquer lorsque vous êtes encore engagé. Dans ce cas, le montant des frais correspond généralement au total des mensualités restantes de votre engagement (12 ou 24 mois). Si vous avez déjà dépassé la période d’engagement, la résiliation est alors gratuite.
+Pour connaître le montant exact qui vous serait facturé, vous pouvez consulter votre contrat ou nous contacter directement :
+- par téléphone au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
+- via le chat en ligne sur notre site web  
+- par email à support@telecomplus.fr  
+Nous restons à votre disposition pour toute aide supplémentaire.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>La réponse générée par l'agent est très complète, précise et alignée avec la réponse de référence, fournissant même des détails supplémentaires sur la façon de connaître le montant exact des frais et les démarches de résiliation.</t>
+          <t>La réponse générée est très proche de la référence, avec les mêmes informations clés sur les frais de résiliation et les conditions d'engagement, mais inclut des détails supplémentaires sur les moyens de contact pour obtenir des informations spécifiques.</t>
         </is>
       </c>
     </row>
@@ -1119,38 +894,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bonjour Monsieur Bertrand,
-Je ne peux malheureusement pas accéder à votre espace personnel ni consulter votre consommation data depuis ce canal.  
-**Voici les démarches les plus simples pour connaître votre consommation du mois en cours :**
-1. **Connectez‑vous à votre espace client**  
-   - Rendez‑vous sur : **www.telecomplus.fr/mon-compte**  
-   - Identifiez‑vous avec votre identifiant et votre mot de passe.  
-   - Dans la rubrique **« Consommation data »** ou **« Mon forfait »**, vous trouverez le détail de votre utilisation (en Mo/Go) ainsi que le pourcentage de votre quota utilisé.
-2. **Application mobile TelecomPlus** (si vous l’avez)  
-   - Ouvrez l’application, puis accédez à la section **« Mon forfait »** → **« Data utilisée »**.
-3. **Contact direct avec le service client**  
-   - **Téléphone** : 3900 (appel gratuit, disponible 7 j/7 de 8 h à 20 h).  
-   - **Chat en ligne** : depuis le site web, cliquez sur l’icône de chat.  
-   - **Email** : support@telecomplus.fr.  
-   - Munissez‑vous de votre numéro de client ou de votre identifiant afin que l’agent puisse vous répondre rapidement.
-4. **Alertes SMS**  
-   - Si vous avez activé les alertes, vous recevez un SMS à 80 % et à 100 % de votre quota. Cela peut déjà vous donner une indication sur votre consommation actuelle.
----
-### En cas de dépassement
-Si vous constatez que vous approchez ou avez dépassé votre forfait, vous avez deux options :
-- **Acheter un rechargement data** directement depuis votre espace client ou l’application.  
-- **Être facturé au Mo supplémentaire** selon les conditions de votre contrat (voir les détails dans votre offre).
----
-N’hésitez pas à me recontacter si vous avez besoin d’aide pour la navigation dans votre espace client ou pour toute autre question relative à votre forfait.  
-Bonne journée et à très bientôt !</t>
+          <t>Bonjour Jean,
+Ce mois-ci, votre consommation data s’élève à **3,2 Go** (pour le mois de novembre 2025).
+Si vous avez besoin d’ajuster votre forfait ou d’obtenir plus de data, n’hésitez pas à me le dire ; je peux vous proposer les options disponibles.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>La réponse générée ne fournit pas la consommation data actuelle du client, mais propose des méthodes pour y accéder.</t>
+          <t>La réponse fournit la même information de consommation data (3,2 Go) mais inclut des détails supplémentaires sur la période et propose une aide pour ajuster le forfait, ce qui est pertinent mais un peu au-delà de la question.</t>
         </is>
       </c>
     </row>
@@ -1170,30 +924,18 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bonjour Monsieur Bertrand,
-Merci pour votre message.  
-Pour connaître le montant exact de votre prochaine facture, il vous suffit de consulter votre espace client :
-1. Rendez‑vous sur **www.telecomplus.fr/mon-compte**.  
-2. Connectez‑vous avec votre identifiant et votre mot de passe.  
-3. Dans la rubrique **« Factures »**, vous verrez le détail de la facture en cours ainsi que le montant à payer pour le prochain cycle.
-&gt; **À noter** : le montant peut varier en fonction de plusieurs éléments (dépassage de forfait data, appels hors‑forfait, services premium, frais de roaming, etc.). Si vous avez récemment utilisé des services supplémentaires, ils seront détaillés ligne par ligne dans votre facture.
-### Que faire si le montant vous semble inattendu ?
-- **Vérifiez le détail** de chaque poste (data, appels, services optionnels).  
-- **Contactez notre service client** si vous avez besoin d’éclaircissements ou d’une éventuelle régularisation :
-  - **Téléphone** : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
-  - **Chat en ligne** : disponible depuis votre espace client  
-  - **Email** : support@telecomplus.fr  
-Nous restons à votre disposition pour toute aide supplémentaire.
-Cordialement,  
-L’équipe Service Client TelecomPlus.</t>
+          <t>Bonjour Jean Bertrand,
+Votre prochaine facture s’élèvera à **9,99 €** et devra être réglée avant le **15 décembre 2025**.  
+Vous pouvez la payer par virement bancaire, PayPal ou mettre en place le prélèvement automatique pour éviter tout retard.
+Si vous avez besoin d’assistance pour le paiement, n’hésitez pas à nous appeler au 3900 (appel gratuit).</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La réponse générée par l'agent ne fournit pas le montant exact de la prochaine facture, contrairement à la réponse de référence.</t>
+          <t>La réponse générée fournit les mêmes informations essentielles que la référence, notamment le montant et la date d'échéance de la facture, avec des détails supplémentaires sur les méthodes de paiement.</t>
         </is>
       </c>
     </row>
@@ -1214,27 +956,19 @@
       <c r="D17" t="inlineStr">
         <is>
           <t>Bonjour Pierre,
-Merci pour votre message.  
-Dans le cadre de notre FAQ, nous n’avons pas accès aux informations personnelles de votre compte ni à l’historique de vos tickets de support. 
-**Voici les démarches les plus rapides pour vérifier si vous avez un ticket en cours :**
-| Canal | Comment faire | Délai moyen |
-|-------|---------------|-------------|
-| **Espace client** | Connectez‑vous à votre compte sur &lt;https://www.telecomplus.fr/mon-compte&gt; → « Mes tickets » ou « Historique du support ». | Immédiat |
-| **Téléphone** | Appelez le 3900 (appel gratuit, 7 j/7 de 8 h à 20 h) et indiquez votre nom et votre numéro de client. | 5‑10 min |
-| **Chat en ligne** | Ouvrez le chat depuis notre site web et identifiez‑vous avec votre compte. | 5 min |
-| **Email** | Envoyez un message à support@telecomplus.fr en précisant votre nom, votre numéro de client et votre demande. | 24‑48 h |
-Si vous ne retrouvez aucun ticket, il se peut que vous n’en ayez pas encore ouvert. Dans ce cas, n’hésitez pas à créer un nouveau ticket via l’un des canaux ci‑dessus ; notre équipe vous répondra dans les plus brefs délais.
-Je reste à votre disposition si vous avez besoin d’aide pour accéder à votre espace client ou pour toute autre question.
-Cordialement,  
-Service Client TelecomPlus.</t>
+Oui, vous avez actuellement deux tickets de support en cours :
+- Ticket #3 : « Frais de résiliation », catégorie Résiliation, statut En cours.  
+- Ticket #4 : « Débit très lent », catégorie Problème de réseau, statut En cours.
+Si vous avez besoin d’une mise à jour ou de préciser un point, vous pouvez nous joindre au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h), via le chat en ligne sur notre site, ou par email à support@telecomplus.fr.  
+Nous restons à votre disposition pour toute assistance supplémentaire.</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La réponse générée ne fournit pas d'information sur les tickets en cours du client, mais propose plutôt des démarches pour vérifier lui-même.</t>
+          <t>La réponse générée fournit les mêmes informations que la référence, avec les mêmes détails sur les tickets en cours, et ajoute même des informations supplémentaires sur les moyens de contacter le support.</t>
         </is>
       </c>
     </row>
@@ -1254,37 +988,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bonjour Monsieur Bertrand,
-Merci pour votre message.  
-En tant que service client TelecomPlus, nous ne disposons pas d’informations sur le coût global d’un voyage (billet d’avion, hébergement, activités, etc.) aux États-Unis.  
-Toutefois, nous pouvons vous aider à anticiper les frais liés à votre utilisation mobile pendant votre séjour :
-| Option | Description | Tarif indicatif* |
-|--------|-------------|------------------|
-| **Pass roaming international journalier** | 1 GB de data, appels et SMS illimités vers les États-Unis. | 9 € / jour |
-| **Pass roaming international hebdomadaire** | 5 GB de data, appels et SMS illimités vers les États-Unis. | 49 € / semaine |
-| **Tarif à la consommation** | Facturation au Mo supplémentaire (au‑delà de votre forfait) | 0,12 € / Mo (varie selon le contrat) |
-| **Désactivation des données mobiles** | Utilisez uniquement le Wi‑Fi pour éviter tout frais de data. | Gratuit (hors frais d’itinérance éventuels) |
-\*Les tarifs indiqués sont ceux en vigueur au moment de la rédaction de ce message et peuvent varier selon votre offre et votre contrat. Vous trouverez le détail exact dans votre espace client (section « Roaming ») ou en contactant notre service dédié.
-**Que faire maintenant ?**
-1. **Vérifier votre forfait actuel** – Connectez‑vous à votre espace client (www.telecomplus.fr/mon-compte) et consultez la rubrique « Roaming » pour connaître les options compatibles avec votre abonnement.  
-2. **Souscrire un pass** – Si vous prévoyez d’utiliser vos données à l’étranger, vous pouvez activer un pass journalier ou hebdomadaire directement depuis votre espace client, ou en appelant le 3900 (service gratuit, 7j/7 de 8h à 20h).  
-3. **Désactiver les données mobiles** – Avant de partir, pensez à désactiver les données mobiles dans les réglages de votre smartphone et à vous connecter à un réseau Wi‑Fi dès que possible.  
-Si vous avez besoin d’aide pour activer un pass, vérifier votre consommation ou toute autre question relative à votre ligne pendant votre voyage, n’hésitez pas à :
-- **Appeler le 3900** (gratuit, disponible 7 j/7 de 8 h à 20 h)  
-- **Utiliser le chat en ligne** sur www.telecomplus.fr  
-- **Envoyer un e‑mail** à support@telecomplus.fr  
-Nous restons à votre disposition pour toute assistance concernant votre abonnement mobile pendant votre séjour aux États-Unis.
-Cordialement,  
-L’équipe Service Client TelecomPlus  
-☎ 3900 – Chat en ligne – support@telecomplus.fr</t>
+          <t>Bonjour Jean,
+Nous ne disposons pas d’informations pour estimer le coût d’un séjour de deux semaines aux États‑Unis. En ce qui concerne votre utilisation mobile pendant ce voyage, les frais de roaming hors Europe sont calculés en fonction de votre consommation (data, appels, SMS).  
+Pour limiter ces frais, nous vous recommandons :
+- de désactiver les données mobiles et d’utiliser le Wi‑Fi dès que possible ;  
+- de souscrire à un pass international journalier ou hebdomadaire, disponible dans votre espace client, qui vous permet de maîtriser le prix du roaming.  
+Si vous avez besoin d’un devis précis ou d’aide pour activer un pass, n’hésitez pas à contacter notre service client au 3900 (appel gratuit) ou par chat en ligne.</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>La réponse générée fournit des informations détaillées et précises sur les options de pass international et les tarifs, même si elle commence par une remarque sur les limites de leur connaissance concernant le coût global du voyage.</t>
+          <t>La réponse générée fournit des informations utiles sur la manière de limiter les frais de roaming et propose des solutions pour maîtriser les coûts, mais ne fournit pas de détails spécifiques sur les tarifs comme le fait la réponse de référence.</t>
         </is>
       </c>
     </row>
@@ -1304,46 +1021,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bonjour Monsieur Martin,
-Merci pour votre message.  
-### Résiliation sans frais : quelles sont les conditions ?
-| Situation | Frais de résiliation |
-|-----------|----------------------|
-| **Hors période d’engagement** (vous avez dépassé les 12 ou 24 mois prévus dans votre contrat) | **Gratuite** |
-| **Encore engagé** (vous êtes toujours dans la période d’engagement) | Des frais peuvent être appliqués, généralement équivalents aux mensualités restantes jusqu’à la fin du contrat. |
-&gt; **En résumé** : vous pouvez résilier sans frais uniquement si votre engagement est déjà terminé.
-### Comment vérifier votre situation ?
-1. **Espace client** – Connectez‑vous à votre compte sur &lt;https://www.telecomplus.fr/mon-compte&gt; et consultez la rubrique « Mon contrat ». Vous y trouverez la date de fin d’engagement.
-2. **Facture** – La dernière facture indique souvent la durée d’engagement restante.
-3. **Contact direct** – Si vous avez un doute, vous pouvez appeler le Service Client au **3900** (appel gratuit, 7 j/7 de 8 h à 20 h) ou utiliser le **chat en ligne** depuis votre espace client. Nos conseillers pourront vous confirmer votre statut en quelques minutes.
-### Démarches pour résilier (si vous êtes hors engagement)
-- **Via l’espace client** :  
-  1. Accédez à la section « Résilier mon abonnement ».  
-  2. Suivez les instructions et confirmez votre demande.  
-  3. La résiliation prendra effet sous **10 jours** à compter de la réception de votre demande.
-- **Par courrier recommandé** (si vous préférez) :  
-  1. Rédigez une lettre de résiliation avec vos coordonnées, numéro de contrat et la mention « Résiliation sans frais – hors période d’engagement ».  
-  2. Envoyez‑la en recommandé avec accusé de réception à l’adresse indiquée sur votre facture.  
-### Si vous êtes encore engagé
-- Les frais seront calculés sur la base des mensualités restantes.  
-- Vous avez la possibilité de **conserver votre numéro** en changeant d’opérateur ; dans ce cas, nous nous occupons de la résiliation et les frais restent les mêmes.
-### Besoin d’une assistance personnalisée ?
-- **Téléphone** : 3900 (gratuit, 7 j/7, 8 h‑20 h)  
-- **Chat en ligne** : depuis votre espace client  
-- **Email** : support@telecomplus.fr  
-- **Agence** : rendez‑vous dans l’agence la plus proche (voir &lt;https://www.telecomplus.fr/agences&gt;)
-N’hésitez pas à nous contacter avec votre numéro de contrat ; nous pourrons alors vous confirmer immédiatement si vous êtes hors engagement et lancer la résiliation sans frais.
-Nous restons à votre disposition pour toute question supplémentaire.
-Cordialement,  
-L’équipe Service Client TelecomPlus.</t>
+          <t>Bonjour Alexandre,
+Votre abonnement est **actif – hors engagement** (date de début : 20 février 2024, aucune date de fin d’engagement). Selon notre FAQ, la résiliation est donc **gratuite** : aucun frais de résiliation ne s’appliquera.
+Pour mettre fin à votre contrat, vous pouvez :
+- envoyer une lettre recommandée avec accusé de réception à notre service résiliation, ou  
+- nous contacter directement par téléphone (3900, appel gratuit) ou via le chat en ligne afin que nous procédions à la résiliation pour vous.
+Souhaitez‑vous que nous vous guidions dans la rédaction de la lettre ou que nous planifions l’appel ?</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>La réponse générée ne répond pas directement à la question du client, qui demande si son abonnement peut être résilié sans frais, alors que la réponse de référence fournit une réponse claire et directe basée sur les informations spécifiques du client.</t>
+          <t>La réponse générée fournit les mêmes informations clés que la référence, notamment la date de début du contrat, le statut hors engagement et la gratuité de la résiliation, avec des détails supplémentaires sur la procédure de résiliation.</t>
         </is>
       </c>
     </row>
@@ -1364,30 +1055,14 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>Bonjour,
-Merci pour votre question. Avec un budget de **1 000 €** et en souhaitant un stockage de **256 Go**, voici les modèles iPhone disponibles dans notre catalogue :
-| Modèle | Prix 256 GB |
-|--------|-------------|
-| **iPhone 11** | 659 € |
-| **iPhone 12** | 829 € |
-| **iPhone 13** | 929 € |
-| **iPhone 14** | **999 €** |
-| iPhone 15 | 1 099 € (dépasserait votre budget) |
-| iPhone 16 | 1 149 € (dépasserait votre budget) |
-| iPhone 17 | 1 299 € (dépasserait votre budget) |
-### Quelle option choisir ?
-- **iPhone 14 (999 €)** : il reste juste en dessous de votre plafond budgétaire et vous offre les dernières innovations de notre gamme : écran ProMotion 120 Hz, construction en titane, zoom optique 5×, puce A16, compatibilité 5G, Ceramic Shield et USB‑C Thunderbolt. C’est le meilleur compromis entre performance, design et longévité.
-- **iPhone 13 (929 €)** : très proche du prix de l’iPhone 14, il propose toujours un excellent écran Super Retina XDR, la puce A15 Bionic, et toutes les fonctionnalités de sécurité (Face ID, MagSafe). Si vous n’avez pas besoin du titane ou du ProMotion, c’est une option solide et légèrement moins chère.
-- **iPhone 12 (829 €)** : toujours compatible 5G, écran OLED, puce A14 Bionic. Il représente un bon rapport qualité/prix si vous cherchez à économiser davantage.
-- **iPhone 11 (659 €)** : le plus économique, avec des performances suffisantes pour la plupart des usages quotidiens, mais sans les dernières améliorations (5G, ProMotion, etc.).
-### Recommandation
-Si vous souhaitez profiter des dernières avancées technologiques tout en respectant votre budget, **l’iPhone 14 256 GB à 999 €** est le choix le plus adapté. Il vous offre les meilleures performances, une meilleure durabilité (titane, Ceramic Shield) et les fonctionnalités les plus récentes (USB‑C Thunderbolt, Apple Intelligence).
-### Prochaine étape
-1. **Vérifier la disponibilité** : rendez‑vous sur notre site www.telecomplus.fr ou appelez le **3900** (appel gratuit) pour confirmer le stock du modèle choisi.
-2. **Passer la commande** : vous pouvez commander en ligne avec livraison gratuite, ou vous rendre dans l’une de nos boutiques pour le tester en magasin.
-3. **Option reprise** : si vous avez un ancien smartphone, pensez à notre service de reprise ; vous pourriez obtenir une réduction supplémentaire sur votre nouvel iPhone.
-N’hésitez pas à me dire quel modèle vous intéresse le plus, ou si vous avez besoin d’aide pour finaliser votre achat. Je reste à votre disposition pour toute question supplémentaire.
-Cordialement,  
-L’équipe TelecomPlus – Service Client.</t>
+Avec un budget de 1 000 € pour un iPhone en version 256 GB, vous avez plusieurs options disponibles dans notre catalogue :
+- **iPhone 14 256 GB** à 999 € : le modèle le plus récent qui reste dans votre budget, offrant les dernières améliorations en matière de caméra, de performance et de connectivité 5G.  
+- **iPhone 13 256 GB** à 929 € : un excellent compromis entre prix et performances, avec la puce A15 Bionic et un écran Super Retina XDR.  
+- **iPhone 12 256 GB** à 829 € : toujours compatible 5G, doté d’un écran OLED et d’un bon équilibre entre prix et fonctionnalités.  
+- **iPhone 11 256 GB** à 659 € : le plus économique, idéal si vous cherchez un appareil fiable sans les dernières innovations.
+Si vous privilégiez les dernières technologies, l’iPhone 14 à 999 € correspond parfaitement à votre budget. Vous pouvez le commander en ligne sur www.telecomplus.fr avec livraison gratuite, ou le tester directement en boutique.
+N’hésitez pas à nous appeler au 3900 ou à passer en boutique pour voir les modèles en démonstration.  
+Bonne journée !</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1395,7 +1070,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>La réponse fournit les informations demandées, inclut l'iPhone 14 comme choix principal dans le budget, mais est plus détaillée et inclut d'autres options, ce qui la rend un peu plus longue et moins directe que la référence.</t>
+          <t>La réponse générée fournit plus d'informations que la référence, incluant plusieurs options d'iPhone dans le budget, mais reste pertinente et répond à la question.</t>
         </is>
       </c>
     </row>
@@ -1415,49 +1090,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bonjour Monsieur Bertrand,
-Merci pour votre message et pour la confiance que vous accordez à TelecomPlus.  
-Vous partez en Italie pour 10 jours ; voici les solutions les plus simples pour rester connecté sans surprise sur votre facture.
----
-## 1. Vérifier votre forfait actuel  
-- **Forfait incluant le roaming Europe** : la plupart de nos forfaits « Euro » offrent les appels, SMS/MMS et un quota data utilisable dans l’ensemble de l’Union européenne (Italie incluse) sans frais supplémentaires.  
-- **Si votre forfait ne comporte pas le roaming Europe** : vous risquez d’être facturé au tarif « roaming », ce qui peut entraîner une facture plus élevée (voir FAQ : *« Une facture plus élevée peut résulter… frais de roaming international »*).
----
-## 2. Options à souscrire pour votre séjour  
-| Option | Ce qu’elle couvre | Prix (exemple) | Comment l’activer |
-|--------|-------------------|----------------|-------------------|
-| **Option Europe** | Appels, SMS/MMS + 1 Go de data en roaming (renouvelable) | 5 €/mois | Depuis votre espace client → *Mon forfait* → *Ajouter une option* |
-| **Option Data Roaming** | Data supplémentaire en itinérance (500 Mo, 1 Go, 5 Go…) | 3‑12 €/mois selon le volume | Même procédure que ci‑dessus |
-| **Pass Voyage** (offre temporaire) | Data illimitée en Europe pendant 10 jours | 9,90 € (offre ponctuelle) | Contactez le service client (3900) ou le chat en ligne pour l’activer immédiatement |
-&gt; **Astuce** : si vous avez déjà un forfait « Euro », il suffit souvent d’ajouter l’option *Data Roaming* pour éviter toute coupure de data.
----
-## 3. Démarches concrètes
-1. **Connectez‑vous à votre espace client** : www.telecomplus.fr/mon-compte  
-2. Rendez‑vous dans la section **« Mon forfait »** → **« Ajouter une option »**.  
-3. Sélectionnez l’option qui correspond le mieux à votre besoin (ex. : *Option Europe* ou *Pass Voyage*).  
-4. Confirmez l’ajout ; l’option sera active immédiatement ou à la prochaine période de facturation, selon votre choix.  
-&gt; **Si vous préférez être accompagné** : appelez le 3900 (gratuit, 7 j/7 de 8 h à 20 h) ou utilisez le chat en ligne. Nos conseillers pourront activer l’option en temps réel et vérifier que votre forfait actuel est bien compatible avec le roaming.
----
-## 4. Points à retenir
-- **Aucun changement de forfait n’est obligatoire** ; une simple option suffit dans la plupart des cas.  
-- **Surveillez votre consommation** : vous recevrez une alerte SMS à 80 % et 100 % de votre quota data (voir FAQ : *« Que se passe‑t‑il si je dépasse mon forfait data ? »*).  
-- **Facturation** : la facturation de l’option se fait au prorata du mois ou sous forme d’abonnement mensuel, sans frais cachés.  
----
-### Besoin d’aide supplémentaire ?
-- **Téléphone** : 3900 (gratuit)  
-- **Chat en ligne** : disponible sur www.telecomplus.fr  
-- **Email** : support@telecomplus.fr  
-Nous restons à votre disposition pour toute question ou pour activer l’option immédiatement. Bon voyage en Italie !
-Cordialement,  
-L’équipe Service Client TelecomPlus.</t>
+          <t>Bonjour Jean Bertrand,
+Je constate que votre abonnement actuel n’est pas renseigné (forfait, prix, data, appels, SMS). Sans ces informations, il m’est impossible de déterminer si votre offre actuelle couvre déjà le roaming en Italie ou si une option supplémentaire serait plus avantageuse.
+**Ce qu’il vous faut :**
+- Le nom exact de votre forfait (ex. : « Forfait 5G », « Forfait 10 Go », etc.) ainsi son volume de data, appels et SMS inclus.
+- Vous pouvez obtenir ces détails en appelant le service client au 3900 ou en vous connectant à votre espace client.
+**En attendant, voici les solutions habituelles pour un séjour de 10 jours en Italie :**
+- **Option Roaming Europe** : activation d’une option dédiée qui vous garantit un tarif forfaitaire (ex. : 5 €/semaine) pour les appels, SMS et data en Europe, évitant les dépassements.
+- **Forfait Europe** : si votre consommation actuelle (3,2 Go de data, 1087 min d’appels, 270 SMS) est élevée, passer à un forfait incluant le roaming (ex. : 15 €/mois avec 10 Go data, appels et SMS illimités en Europe) peut être plus économique.
+Je vous propose de nous appeler au **3900** (appel gratuit, 7 j/7 de 8 h à 20 h) avec votre numéro de ligne afin que nous puissions vérifier votre offre actuelle et activer immédiatement l’option la plus adaptée à votre voyage.  
+À très vite,  
+Service Client TelecomPlus.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>La réponse fournit des informations générales sur les options de roaming et les forfaits, mais ne répond pas directement à la question du client concernant son forfait actuel et les besoins spécifiques pour son voyage en Italie.</t>
+          <t>La réponse de l'agent ne fournit pas d'information précise sur le forfait actuel du client et ne répond pas directement à la question, mais propose des solutions générales pour le roaming en Italie.</t>
         </is>
       </c>
     </row>
@@ -1477,35 +1128,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bonjour,
-Merci pour votre intérêt pour l’iPhone 16.  
-Oui, chez TelecomPlus vous pouvez bénéficier d’une réduction en échangeant votre ancien téléphone grâce à notre programme **Reprise**.
-### Comment fonctionne la reprise ?
-| Étape | Description |
-|-------|-------------|
-| **1. Estimation** | Vous obtenez une estimation de la valeur de votre ancien appareil (iPhone, Android ou tout autre smartphone) : &lt;br&gt;• En boutique, nos conseillers évaluent votre téléphone sur place.&lt;br&gt;• En ligne, vous remplissez le formulaire de reprise sur www.telecomplus.fr et recevez une offre instantanée. |
-| **2. Conditions du téléphone** | Le dispositif doit être en bon état de fonctionnement (écran, batterie, ports, aucune détérioration majeure). Les modèles très anciens ou très endommagés peuvent être acceptés avec une valeur réduite. |
-| **3. Validation** | Une fois l’offre acceptée, vous pouvez : &lt;br&gt;• **En boutique** : remettre le téléphone à un conseiller qui vous remettra un bon de réduction à appliquer immédiatement sur l’achat de l’iPhone 16.&lt;br&gt;• **En ligne** : envoyer le téléphone via le service de collecte ou le déposer dans un point relais. Après vérification, le montant de la reprise vous sera crédité sous forme de bon d’achat valable sur votre prochaine commande. |
-| **4. Achat de l’iPhone 16** | Le bon de réduction est déduit du prix de l’iPhone 16 (livraison gratuite incluse). Vous pouvez choisir la couleur et la capacité souhaitées directement en boutique ou sur le site. |
-### Points importants à retenir
-- **Montant de la réduction** : il dépend du modèle et de l’état de votre ancien téléphone. Par exemple, un iPhone 13 en bon état peut rapporter entre 150 € et 250 €, tandis qu’un modèle plus ancien donnera une valeur moindre.  
-- **Validité du bon** : le bon de reprise est valable **30 jours** à compter de la date d’émission.  
-- **Livraison** : la commande en ligne bénéficie de la livraison gratuite, même avec le bon de réduction appliqué.  
-- **Pas de frais cachés** : aucune charge supplémentaire n’est appliquée pour le service de reprise.
-### Démarches concrètes pour vous
-1. **En boutique** : Rendez‑vous dans le magasin TelecomPlus le plus proche. Un conseiller évaluera votre ancien téléphone et vous remettra immédiatement le bon de réduction à appliquer sur l’iPhone 16.  
-2. **En ligne** :  
-   - Accédez à la page **Reprise** sur www.telecomplus.fr.  
-   - Sélectionnez le modèle de votre ancien téléphone, indiquez son état et validez.  
-   - Recevez votre offre par email.  
-   - Confirmez l’échange, choisissez le mode d’envoi (collecte à domicile ou dépôt en point relais).  
-   - Une fois le téléphone reçu et vérifié, le bon d’achat vous sera envoyé, à appliquer lors de la commande de l’iPhone 16.  
-### Besoin d’assistance ?
-- **Téléphone** : 3900 (appel gratuit) – nos conseillers sont disponibles pour vous guider pas à pas.  
-- **Chat en ligne** : disponible sur www.telecomplus.fr.  
-- **Boutique** : nos équipes sont à votre disposition pour une évaluation immédiate.
-Nous restons à votre disposition pour toute question supplémentaire ou pour vous accompagner dans votre échange.  
-Bonne journée et au plaisir de vous voir profiter de votre nouveau iPhone 16 !</t>
+          <t>Bonjour, il manque votre nom pour personnaliser davantage ma réponse.
+Vous pouvez effectivement bénéficier d’une réduction en échangeant votre ancien iPhone contre le nouvel iPhone 16 :  
+- **En boutique** : apportez votre téléphone actuel à l’un de nos magasins, nous l’évaluerons sur place et vous appliquons la remise immédiatement.  
+- **En ligne** : lors de la commande sur www.telecomplus.fr, choisissez l’option « Reprise », indiquez le modèle de votre ancien iPhone, suivez les instructions d’envoi et la réduction sera déduite du prix final.
+Si vous avez besoin d’assistance pour estimer la valeur de reprise ou pour lancer la procédure, n’hésitez pas à appeler le 3900 (appel gratuit) ou à vous rendre dans la boutique la plus proche.</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1513,7 +1140,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>La réponse générée couvre tous les points clés de la réponse de référence, notamment le programme de reprise, les étapes pour obtenir une réduction, et les informations de contact pour une assistance supplémentaire. Cependant, elle fournit plus de détails que la réponse de référence, ce qui pourrait être considéré comme un plus, mais elle ne mentionne pas explicitement le prix de l'iPhone 16 comme dans la réponse de référence.</t>
+          <t>La réponse générée fournit les mêmes informations essentielles que la référence, notamment les options de reprise en boutique et en ligne, ainsi que le numéro de téléphone pour assistance, mais omet le prix de l'iPhone 16.</t>
         </is>
       </c>
     </row>
@@ -1533,35 +1160,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>**iPhone répondant à votre critère : 48 Mpx + 256 Go ≤ 1200 €**
-| Modèle (extrait du FAQ) | Caméra principale | Stockage disponible | Prix indiqué dans le FAQ |
-|--------------------------|-------------------|----------------------|--------------------------|
-| **iPhone 16** (2024)     | 48 Mpx (Fusion)   | 128 GB – 256 GB – 512 GB | *non communiqué* |
-Le seul modèle mentionné dans notre documentation qui possède **une caméra principale de 48 Mpx** et qui est disponible en **256 GB** est l’**iPhone 16**. Aucun tarif n’est indiqué dans la FAQ ; cependant, les iPhone 16 sont généralement positionnés dans la gamme « premium » avec un prix de lancement autour de **1200 €** pour la version 256 GB, ce qui correspond à votre budget.
----
-### Que faire pour confirmer le prix ?
-1. **Vérifier en ligne**  
-   - Rendez‑vous sur notre boutique en ligne : **www.telecomplus.fr**  
-   - Recherchez « iPhone 16 256 GB ». Le prix affiché sera le tarif le plus à jour (promotions éventuelles incluses).
-2. **Contacter un conseiller**  
-   - **Par téléphone** : 3900 (appel gratuit) – un conseiller pourra vous confirmer le prix exact et la disponibilité en magasin.  
-   - **En boutique** : nos équipes peuvent vous faire une démonstration et vous proposer une offre personnalisée.
-3. **Comparer avec d’autres modèles**  
-   - Si le prix de l’iPhone 16 dépasse légèrement votre budget, nos conseillers peuvent vous proposer des alternatives (ex. : iPhone 15 Pro, qui possède également une caméra de 48 Mpx selon les dernières sorties, mais dont le prix n’est pas présent dans le FAQ).
----
-### Résumé
-- **Modèle recommandé** : **iPhone 16**, caméra 48 Mpx, stockage 256 GB.  
-- **Prix** : non indiqué dans la FAQ ; il faut le vérifier en ligne ou auprès d’un conseiller.  
-- **Action conseillée** : consultez le site web ou appelez le 3900 pour obtenir le tarif exact et procéder à la commande.
-Nous restons à votre disposition pour toute aide supplémentaire !</t>
+          <t>Bonjour,
+D’après notre FAQ, les iPhone équipés d’une caméra d’au moins 48 Mpx et disponibles en version 256 Go sont :
+- **iPhone 16** (2024) : caméra principale 48 Mpx, stockage 256 Go disponible.  
+- Un modèle « Système de caméra Fusion 48 Mpx » (description sans nom de gamme) : stockage 256 Go disponible.
+Cependant, les tarifs ne sont pas indiqués dans la base de connaissances que nous utilisons. Nous ne pouvons donc pas confirmer qu’ils sont proposés à moins de 1 200 €.
+**Comment obtenir le prix ?**  
+- Consultez le catalogue en ligne sur www.telecomplus.fr ; le prix s’affiche directement pour chaque configuration.  
+- Appelez notre service commercial au 3900 (appel gratuit) ou rendez‑vous en boutique pour obtenir un devis précis.
+**Alternatives**  
+Si le budget de 1 200 € est strict, vous pouvez également envisager les modèles précédents disposant d’une caméra 48 Mpx (par exemple l’iPhone 15 Pro) qui sont souvent proposés à des tarifs plus avantageux tout en conservant le stockage 256 Go.
+N’hésitez pas à nous recontacter pour toute aide supplémentaire dans votre choix.</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>La réponse fournit le modèle iPhone 16 avec une caméra de 48 Mpx et 256 GB, mais ne donne pas de prix exact et ne mentionne pas l'iPhone 15 comme alternative sous le budget de 1200€.</t>
+          <t>La réponse fournit des informations partiellement correctes sur les modèles d'iPhone avec caméra 48 Mpx et stockage 256GB, mais ne fournit pas les prix exacts et ne répond pas directement à la question du client concernant les modèles disponibles pour moins de 1200€.</t>
         </is>
       </c>
     </row>
@@ -1581,48 +1198,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bonjour Monsieur Bertrand,
-Merci pour votre demande.  
-### 1. Quel est le coût d’un passage à un forfait avec plus de data ?  
-Notre FAQ ne précise pas de tarif fixe pour l’augmentation de data, car le supplément dépend :
-| Variable | Impact sur le prix |
-|----------|-------------------|
-| **Le forfait actuel** (10 Go, 30 Go, 100 Go, etc.) | Chaque gamme a un prix de base différent. |
-| **Le volume de data supplémentaire souhaité** | Les forfaits « plus de data » sont proposés sous forme de nouvelles offres (ex. : +20 Go, +50 Go, +100 Go) avec un prix mensuel propre à chaque offre. |
-| **Le type d’abonnement** (engagement 12 mois, 24 mois ou sans engagement) | Les tarifs peuvent varier selon la durée d’engagement. |
-| **Promotions en cours** | Des offres promotionnelles (réduction de X % pendant les 3 ou 6 premiers mois) peuvent s’appliquer. |
-En résumé, le supplément mensuel **varie généralement entre 5 € et 25 €** selon le volume de data ajouté et le type d’engagement, mais le montant exact ne peut être déterminé qu’en consultant les offres actualisées.
-### 2. Comment connaître le prix exact qui vous correspond ?  
-1. **Espace client** – Connectez‑vous à votre compte :  
-   &lt;https://www.telecomplus.fr/mon-compte&gt;  
-   → rubrique **« Mes offres »** → **« Changer de forfait »**.  
-   Vous verrez toutes les options de data supplémentaires avec le prix mensuel affiché.
-2. **Site web – Catalogue des forfaits** – Rendez‑vous sur la page **Offres mobile** :  
-   &lt;https://www.telecomplus.fr/offres-mobile&gt;  
-   Chaque pack indique le volume de data et le tarif mensuel.
-3. **Contact direct** – Si vous préférez être conseillé·e en temps réel :  
-   - **Téléphone** : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
-   - **Chat en ligne** : disponible depuis la page d’accueil du site.  
-   - **Email** : support@telecomplus.fr  
-   Nos conseillers pourront vérifier votre contrat actuel, vous proposer les meilleures options et vous indiquer le coût additionnel exact.
-### 3. Points à retenir avant de changer d’offre  
-- **Alerte de consommation** : vous recevrez un SMS à 80 % et 100 % de votre quota.  
-- **Dépassement** : si vous dépassez le nouveau forfait, vous pouvez soit acheter un rechargement de data, soit être facturé au Mo supplémentaire selon les conditions de votre contrat.  
-- **Engagement** : un changement d’offre peut entraîner un nouveau délai d’engagement (12 ou 24 mois) ou, si vous êtes déjà engagé, un éventuel frais de modification (souvent nul, mais à vérifier).  
----
-**En bref** : le supplément mensuel dépend du forfait que vous choisissez. Pour obtenir le montant précis, je vous invite à consulter votre espace client ou à contacter notre service client qui pourra vous proposer l’offre la plus adaptée à votre usage.
-N’hésitez pas à revenir vers moi si vous avez besoin d’aide pour la navigation sur le site ou pour planifier un appel avec un conseiller.
-Bonne journée,  
-**Service Client TelecomPlus**  
-📞 3900 – 📧 support@telecomplus.fr – 💬 Chat en ligne.</t>
+          <t>Bonjour Jean Bertrand,
+Je constate que votre dossier ne précise pas le forfait que vous avez actuellement (type de forfait, prix mensuel et volume de data inclus). Sans ces informations, il m’est impossible de calculer précisément l’augmentation de tarif que représenterait le passage à un forfait avec plus de data.
+**Ce qui manque :**  
+- Le nom ou le code de votre forfait actuel  
+- Le prix mensuel et le volume de data inclus dans ce forfait  
+**Comment obtenir ces informations :**  
+Vous pouvez les retrouver dans votre dernier contrat ou sur votre facture détaillée. Si vous avez besoin d’aide pour les localiser, n’hésitez pas à appeler notre service client au **3900** (appel gratuit, disponible 7 j/7 de 8 h à 20 h) ou à nous écrire à **support@telecomplus.fr**.
+**Prochaine étape :**  
+Une fois que vous connaîtrez votre forfait actuel, nous pourrons vous proposer les offres « plus de data » disponibles et vous indiquer exactement le supplément mensuel (par exemple + 2 €, + 5 €, etc.) en fonction du volume supplémentaire souhaité.
+Je reste à votre disposition pour toute question supplémentaire.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La réponse générée fournit des informations générales sur les facteurs influençant le coût d'un forfait avec plus de data, mais ne répond pas directement à la question du client concernant le coût supplémentaire pour son cas spécifique, contrairement à la réponse de référence qui donne un montant précis.</t>
+          <t>La réponse générée ne fournit pas de réponse directe à la question du client, mais demande des informations supplémentaires pour calculer le coût, ce qui indique un manque d'information ou d'accès aux données du client.</t>
         </is>
       </c>
     </row>
@@ -1643,44 +1236,17 @@
       <c r="D25" t="inlineStr">
         <is>
           <t>Bonjour,
-Merci pour votre question ! 📸
-### Quel iPhone offre les meilleures performances photographiques ?
-**L’iPhone 15** se distingue actuellement comme le modèle le plus complet pour la photographie :
-| Caractéristique | iPhone 15 |
-|-----------------|-----------|
-| **Système photo** | Double caméra 12 MP (grand‑angle + téléobjectif) avec zoom optique 5× |
-| **Qualité d’image** | Capture d’images exceptionnelles dans toutes les conditions d’éclairage grâce aux capteurs avancés et à l’Apple Intelligence intégrée |
-| **Fonctions supplémentaires** | Mode cinématique, ProMotion 120 Hz, Dynamic Island, USB‑C Thunderbolt |
-| **Autonomie** | Jusqu’à 13 h de lecture vidéo (suffisant pour de longues sessions de prise de vue) |
-| **Sécurité** | Face ID pour une authentification sécurisée |
-| **Couleurs disponibles** | Gris sidéral, Argent (et d’autres teintes selon les stocks) |
-Ces spécifications font de l’iPhone 15 le choix le plus performant pour la photographie, que vous soyez amateur ou professionnel.
-### Alternatives selon votre budget
-| Modèle | Points forts photographiques | Prix généralement plus bas |
-|--------|-----------------------------|----------------------------|
-| **iPhone 14** | Caméra double 12 MP (grand‑angle + ultra grand‑angle), amélioration de l’autonomie (≈ 20 h vidéo) | Oui, souvent en promotion |
-| **iPhone 11** | Caméra simple 12 MP, puce A13 Bionic, bon rapport qualité/prix | Oui, modèle d’entrée de gamme |
-Si vous avez des contraintes budgétaires, l’iPhone 14 reste une excellente option, offrant une très bonne qualité d’image et des fonctionnalités avancées.
-### Que faire ensuite ?
-1. **Vérifier la disponibilité** – Rendez‑vous sur notre site [www.telecomplus.fr](http://www.telecomplus.fr) ou contactez notre service client.
-2. **Comparer les offres** – Nous proposons la livraison gratuite et, selon les promotions en cours, des remises ou des accessoires offerts.
-3. **Essayer en boutique** – Nos conseillers vous accueillent en magasin pour tester les modèles et vous conseiller en fonction de vos besoins spécifiques.
----
-**Nos contacts**  
-- Téléphone (appel gratuit) : **3900**  
-- En boutique : démonstration de tous les modèles  
-- En ligne : commande sur www.telecomplus.fr (livraison gratuite)
-N’hésitez pas à nous recontacter si vous avez besoin d’aide pour choisir le modèle qui correspond le mieux à votre usage photographique ou pour toute autre question. Nous sommes là pour vous accompagner.
-Cordialement,  
-L’équipe TelecomPlus.</t>
+Pour la photographie, le modèle le plus performant de notre gamme est l’**iPhone 15 Pro** (et son grand frère l’iPhone 15 Pro Max). Il dispose d’un système à double caméra de 12 Mpx (grand‑angle et téléobjectif) avec un zoom optique 5×, d’un écran ProMotion 120 Hz et de la puce Apple Intelligence qui optimise le traitement des images. Ces caractéristiques offrent une qualité exceptionnelle dans toutes les conditions d’éclairage, ainsi qu’un rendu très détaillé et des couleurs fidèles.
+Si vous cherchez une option légèrement moins chère tout en conservant d’excellentes capacités photo, l’**iPhone 14** propose également une double caméra 12 Mpx (grand‑angle et ultra‑grand‑angle) avec le mode Cinematic pour la vidéo, ce qui reste très performant pour la plupart des usages.
+Vous pouvez tester les deux modèles en boutique ou les commander en ligne sur www.telecomplus.fr avec livraison gratuite. Si vous avez besoin d’un conseil plus personnalisé (par exemple, selon votre budget ou vos besoins spécifiques), n’hésitez pas à appeler notre service gratuit au 3900.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La réponse fournie par l'agent ne correspond pas à la référence, mentionnant l'iPhone 15 au lieu de l'iPhone 17 et ne fournissant pas les détails spécifiques sur le système photo avancé comme la triple caméra 48 Mpx et le capteur LiDAR.</t>
+          <t>La réponse fournit des informations sur les modèles d'iPhone performants pour la photographie, mais les modèles mentionnés (iPhone 15 Pro, iPhone 14) ne correspondent pas à ceux de la référence (iPhone 17, iPhone 16), et les caractéristiques techniques diffèrent.</t>
         </is>
       </c>
     </row>
@@ -1700,45 +1266,21 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>**Bonjour,**
-Merci pour votre question concernant l’utilisation de votre iPhone à l’étranger.
-### 1. Rappel de la règle générale
-- **Le roaming (itinérance) international** peut entraîner des frais supplémentaires sur votre facture.  
-- Dans la FAQ, il est indiqué que **« une facture plus élevée peut résulter… de frais de roaming international »** (voir Q32).
-### 2. Ce qui dépend de votre situation
-| Situation | Coût éventuel |
-|-----------|----------------|
-| **Forfait incluant le roaming** (ex. : option « Europe », « Monde », etc.) | Aucun surcoût tant que vous restez dans les limites de l’option. |
-| **Forfait sans option roaming** | Facturation au tarif « hors‑forfait » (généralement plus élevé). |
-| **Utilisation de données, appels ou SMS** | Chaque service (data, appels, SMS) est facturé selon les tarifs roaming de votre offre. |
-### 3. Comment vérifier votre éligibilité
-1. **Connectez‑vous à votre espace client** : www.telecomplus.fr/mon-compte  
-   - Consultez la rubrique *Mon forfait* → *Options &amp; services* pour voir si une option roaming est déjà activée.
-2. **Vérifiez le détail de votre dernière facture** : les frais de roaming y sont clairement indiqués lorsqu’ils s’appliquent.
-3. **Contactez le service client** si vous avez besoin d’ajouter ou de modifier une option :
-   - **Téléphone** : 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
-   - **Chat en ligne** : disponible sur notre site web  
-   - **Email** : support@telecomplus.fr  
-### 4. Démarches concrètes si vous n’avez pas d’option roaming
-- **Souscrire une option roaming** (ex. : « Roaming Europe », « Roaming Monde ») directement depuis votre espace client ou via un conseiller téléphonique.  
-- **Activer le mode « Data roaming »** uniquement lorsque vous êtes à l’étranger, et pensez à désactiver le data si vous ne souhaitez pas être facturé.
-### 5. En résumé
-- **Oui, vous pouvez utiliser votre iPhone à l’étranger**, mais **seul un forfait incluant une option roaming vous garantit l’absence de surcoût**.  
-- Sans cette option, les appels, SMS et l’utilisation de données seront facturés selon les tarifs roaming, ce qui peut augmenter votre facture (voir la FAQ Q32).
-Nous restons à votre disposition pour vous aider à vérifier ou à ajouter l’option qui vous convient le mieux.
-**Cordialement,**  
-Le service client TelecomPlus  
-📞 3900 – gratuit, 7 j/7 de 8 h à 20 h  
-💬 Chat en ligne – www.telecomplus.fr  
-✉️ support@telecomplus.fr</t>
+          <t>Bonjour,
+Votre question porte sur l’utilisation de votre iPhone à l’étranger sans frais supplémentaires.  
+Dans les informations dont je dispose, il n’y a pas de détail précis sur les conditions de roaming pour les iPhone. Les frais éventuels dépendent du forfait que vous avez souscrit (par exemple, un forfait incluant le roaming ou des options « roaming » à ajouter).
+**Ce que vous pouvez faire :**  
+- Vérifier les options roaming disponibles dans votre espace client ou en appelant le Service Client au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h).  
+- Vous pouvez également consulter le chat en ligne sur notre site web ou envoyer un email à support@telecomplus.fr pour obtenir une réponse personnalisée en fonction de votre abonnement.
+Si vous avez besoin d’aide pour activer une option roaming ou pour connaître les tarifs appliqués à votre forfait, n’hésitez pas à nous contacter via l’un de ces canaux. Nous sommes à votre disposition pour vous assurer une utilisation sereine de votre iPhone à l’étranger.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La réponse fournit des informations détaillées et exactes sur l'utilisation de l'iPhone à l'étranger, mais elle est plus longue et complexe que la réponse de référence, avec des détails supplémentaires qui ne sont pas directement liés à la question.</t>
+          <t>La réponse fournit des informations générales sur la façon d'obtenir des informations sur le roaming, mais ne répond pas directement à la question et ne fournit pas les détails spécifiques sur les conditions de roaming comme à la maison dans l'UE ou les frais hors Europe.</t>
         </is>
       </c>
     </row>

--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -478,7 +478,7 @@
         <is>
           <t>Bonjour,
 Nous acceptons les paiements par carte bancaire, prélèvement automatique, virement bancaire et PayPal. Le prélèvement automatique vous assure de ne jamais manquer une échéance.
-Vous pouvez choisir ou modifier votre mode de paiement directement depuis votre espace client, ou nous contacter au 3900 si vous avez besoin d’assistance.</t>
+Vous pouvez choisir ou modifier votre mode de paiement directement dans la section « Mes paiements » de votre espace client, ou en contactant notre service client au 3900 (appel gratuit).</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>La réponse générée est quasi identique à la référence, avec les mêmes modes de paiement et les mêmes avantages pour le prélèvement automatique, avec des informations supplémentaires utiles.</t>
+          <t>La réponse générée contient les mêmes informations que la référence et fournit même des détails supplémentaires sur la façon de gérer les modes de paiement.</t>
         </is>
       </c>
     </row>
@@ -507,17 +507,21 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>Bonjour,
-Je n’ai pas votre nom dans le message, pourriez‑vous me le communiquer afin de personnaliser davantage ma réponse ?
-Pour consulter votre facture en ligne, il vous suffit de vous rendre sur le site : **www.telecomplus.fr/mon-compte**. Connectez‑vous avec vos identifiants, puis cliquez sur l’onglet « Factures » où vous trouverez le détail de chaque facture disponible au téléchargement.
-Souhaitez‑vous que je vous aide à réinitialiser votre mot de passe ou à récupérer vos identifiants ?</t>
+Je n’ai pas votre nom dans les informations que vous avez fournies, ce qui m’empêche de vous adresser une réponse personnalisée.  
+Pour consulter votre facture en ligne, il vous suffit de :
+1. Vous rendre sur le site : **www.telecomplus.fr/mon-compte**  
+2. Vous identifier avec votre identifiant et votre mot de passe.  
+3. Une fois connecté, cliquer sur l’onglet **« Factures »** où vous trouverez le détail de toutes vos factures récentes et la possibilité de les télécharger au format PDF.
+Si vous avez oublié vos identifiants ou rencontrez un problème de connexion, vous pouvez réinitialiser votre mot de passe depuis la même page ou contacter notre service client au **3900** (appel gratuit, 7 j/7 de 8 h à 20 h).
+Souhaitez‑vous que je vous aide à réinitialiser votre accès ou à vérifier un point précis de votre facture ?</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>La réponse fournit les informations essentielles pour consulter la facture en ligne, mais manque de détails sur la disponibilité des factures pendant 24 mois et mentionne inutilement la réinitialisation du mot de passe.</t>
+          <t>La réponse fournie par l'agent contient les informations essentielles pour consulter la facture en ligne, mais elle inclut des détails supplémentaires non présents dans la réponse de référence, comme les étapes détaillées pour se connecter et la possibilité de réinitialiser le mot de passe.</t>
         </is>
       </c>
     </row>
@@ -538,21 +542,17 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>Bonjour,
-Vous n’avez pas indiqué votre nom ni le numéro de votre ligne, ce qui nous empêche de vous identifier précisément dans notre système.
-Pour savoir si votre forfait actuel peut être transformé en forfait famille et connaître les conditions (nombre de lignes, volume de data partagé, tarif), vous pouvez :
-- appeler le service client au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h) ;
-- discuter en ligne via le chat disponible sur notre site web ;
-- envoyer un e‑mail à support@telecomplus.fr en précisant votre nom et votre numéro de ligne.
-Ces canaux vous permettront d’obtenir les détails exacts et de mettre en place le partage de data avec votre famille.
-Souhaitez‑vous que je vous indique les horaires d’ouverture du chat ou que je vous aide à préparer votre demande ?</t>
+Oui, nous proposons des forfaits famille qui permettent de partager un pool de données entre plusieurs lignes. Pour connaître les options disponibles (nombre de lignes, volume de data partagé, tarifs), il vous suffit de contacter notre service client.
+Vous pouvez les joindre gratuitement au 3900 (7 j/7, de 8 h à 20 h), par chat en ligne sur notre site, ou par email à support@telecomplus.fr.
+Souhaitez‑vous que je vous mette en relation avec un conseiller dès maintenant ?</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>La réponse fournit les informations nécessaires pour que le client puisse partager son forfait data avec sa famille, mais elle est plus verbale et demande des informations supplémentaires avant de fournir une réponse directe.</t>
+          <t>La réponse générée par l'agent contient les mêmes informations clés que la réponse de référence et fournit même plus de détails sur les moyens de contacter le service client.</t>
         </is>
       </c>
     </row>
@@ -573,20 +573,20 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>Bonjour,
-Je n’ai pas de nom ni de numéro de ligne dans votre message, ce qui m’empêche de vérifier directement le statut de votre roaming.  
-Pour activer ou vérifier le roaming international :  
-- Connectez‑vous à votre espace client (www.telecomplus.fr/mon‑compte) et consultez la rubrique « Gestion du roaming ».  
-- Vous pouvez également appeler le service client au 3900 (appel gratuit, disponible 7 j/7 de 8 h à 20 h) ; un conseiller pourra activer le service immédiatement si besoin.  
-En règle générale, le roaming est déjà activé par défaut, il suffit donc de vérifier qu’il est bien actif avant votre départ.  
-Si vous avez besoin d’aide supplémentaire, n’hésitez pas à utiliser le chat en ligne sur notre site ou à vous rendre dans l’une de nos agences.</t>
+Le roaming international est généralement activé par défaut sur votre ligne.  
+Pour vous en assurer, vous pouvez :
+- vous connecter à votre espace client (www.telecomplus.fr/mon‑compte) et vérifier le statut du roaming dans la rubrique « Gestion du mobile » ;  
+- appeler le service client au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h) qui pourra le confirmer ou l’activer immédiatement si besoin.
+N’oubliez pas de consulter les tarifs applicables à votre destination ; dans l’Union européenne vous bénéficiez du « roaming comme à la maison », tandis qu’en dehors de l’UE il est conseillé de désactiver les données mobiles ou de souscrire à un pass international journalier/hebdomadaire disponible dans votre espace client.
+Si vous avez besoin d’une assistance en direct, n’hésitez pas à appeler le 3900 ou à utiliser le chat en ligne sur notre site.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>La réponse générée couvre les points clés de la réponse de référence, notamment l'activation par défaut du roaming international et les moyens de vérifier son statut, mais elle est plus détaillée et inclut des informations supplémentaires sur les canaux de support.</t>
+          <t>La réponse générée par l'agent fournit les mêmes informations que la réponse de référence, avec des détails supplémentaires sur la façon de vérifier et d'activer le roaming international, ainsi que des conseils sur les tarifs.</t>
         </is>
       </c>
     </row>
@@ -607,9 +607,9 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>Bonjour,
-Dans l’Union européenne, le roaming fonctionne « comme à la maison » : vous pouvez utiliser votre forfait français sans frais supplémentaires dans tous les pays de l’UE, dans la limite des volumes (appels, SMS, data) prévus par votre contrat.  
-Si vous souhaitez vérifier les plafonds exacts de votre offre ou activer le roaming, il suffit de consulter votre espace client ou de nous appeler au 3900 (appel gratuit).  
-Nous restons à votre disposition pour tout complément d’information.</t>
+Dans l’Union européenne, le roaming fonctionne selon le principe du « roaming comme à la maison ». Vous pouvez donc utiliser votre forfait français (appels, SMS et data) sans frais supplémentaires, tant que vous restez dans les limites prévues par votre contrat (quota data, minutes, etc.).
+Si vous souhaitez connaître précisément les plafonds applicables à votre offre, vous pouvez les vérifier dans votre espace client ou en appelant le 3900 (appel gratuit).  
+Besoin d’un complément d’information ou d’une aide pour ajuster votre forfait ? Nous sommes à votre disposition.</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -617,7 +617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>La réponse générée est très proche de la référence, avec les mêmes informations clés sur le roaming dans l'UE, mais contient des détails supplémentaires sur la vérification des plafonds et le contact pour plus d'informations.</t>
+          <t>La réponse générée est très similaire à la référence, elle fournit les mêmes informations clés sur le roaming dans l'UE, mais ajoute des détails supplémentaires sur la vérification des plafonds et propose une aide supplémentaire.</t>
         </is>
       </c>
     </row>
@@ -638,18 +638,16 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>Bonjour,
-Pour réinitialiser votre mot de passe, cliquez sur le lien **« Mot de passe oublié »** présent sur la page de connexion de votre espace client. Vous recevrez alors un lien de réinitialisation par email ou SMS ; suivez simplement les instructions pour créer un nouveau mot de passe.
-Si vous ne recevez pas le lien ou rencontrez une difficulté, vous pouvez contacter notre service client au **3900** (appel gratuit, disponible 7 j/7 de 8 h à 20 h) ou via le chat en ligne sur notre site.  
-À très vite,  
-L’équipe Service Client TelecomPlus.</t>
+Cliquez sur le lien **« Mot de passe oublié »** sur la page de connexion de votre espace client. Vous recevrez alors un lien de réinitialisation par email ou SMS. Suivez les instructions contenues dans ce message pour créer un nouveau mot de passe.
+Si vous ne recevez pas le lien ou rencontrez un problème, vous pouvez contacter notre service client au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h) ou via le chat en ligne sur notre site.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>La réponse générée couvre les mêmes étapes que la référence, avec des détails supplémentaires sur les options de support, mais reste pertinente et utile.</t>
+          <t>La réponse générée est très proche de la référence, avec les mêmes étapes pour réinitialiser le mot de passe. Elle apporte même des informations supplémentaires utiles en cas de problème.</t>
         </is>
       </c>
     </row>
@@ -670,12 +668,12 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>Bonjour,
-Les paramètres MMS sont normalement configurés automatiquement sur votre téléphone.  
+Les paramètres MMS sont normalement configurés automatiquement par le réseau.  
 Si ce n’est pas le cas, suivez ces étapes :
-1. Ouvrez **Réglages** → **Réseau mobile** → **Noms des points d’accès**.  
-2. Ajoutez un nouveau point d’accès en renseignant la configuration MMS que vous trouverez sur notre site : [www.telecomplus.fr/config-mms](https://www.telecomplus.fr/config-mms).
-Une fois le point d’accès enregistré, redémarrez votre appareil et vos MMS devraient fonctionner.  
-Si vous rencontrez encore des difficultés, n’hésitez pas à nous contacter par téléphone ou via le chat en ligne pour une assistance immédiate.</t>
+1. Ouvrez **Réglages** → **Réseau mobile** → **Noms des points d’accès (APN)**.  
+2. Ajoutez un nouveau point d’accès en renseignant la configuration MMS disponible sur le site de TelecomPlus (section « Paramètres APN »).
+Une fois enregistré, redémarrez votre téléphone pour que les paramètres soient pris en compte.  
+Si vous rencontrez encore des difficultés, n’hésitez pas à contacter notre support par téléphone ou live‑chat pour une assistance immédiate.</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -683,7 +681,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>La réponse générée est très proche de la référence, avec les mêmes étapes et informations, mais inclut des détails supplémentaires tels que le lien vers le site et des instructions pour le cas où les MMS ne fonctionnent toujours pas.</t>
+          <t>La réponse générée par l'agent est très proche de la réponse de référence, avec les mêmes étapes et informations. Les seules différences sont des détails mineurs tels que l'ajout d'une salutation et d'une offre d'assistance supplémentaire.</t>
         </is>
       </c>
     </row>
@@ -704,11 +702,8 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>Bonjour,
-Nous ne disposons pas du tarif exact de l’iPhone 15 256 Go dans notre base de connaissances. Vous pouvez obtenir ce prix en :
-- consultant le catalogue en ligne sur www.telecomplus.fr (livraison gratuite)  
-- appelant notre service client au 3900 (appel gratuit)  
-- vous rendant dans l’une de nos boutiques où les modèles sont exposés.
-Nos conseillers se tiennent également à votre disposition pour vous proposer les meilleures offres et options de financement. N’hésitez pas à les contacter pour plus de détails.</t>
+Le prix de l’iPhone 15 en version 256 Go est d’environ **1 279 €** (hors promotions et options).  
+Vous pouvez le commander directement sur notre site www.telecomplus.fr avec la livraison gratuite, ou appeler le 3900 (appel gratuit) pour être mis en relation avec un conseiller qui pourra vous proposer d’éventuelles offres ou facilités de paiement.</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -716,7 +711,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>La réponse générée ne fournit pas le prix de l'iPhone 15 en 256GB, mais propose des alternatives pour obtenir l'information.</t>
+          <t>La réponse générée par l'agent fournit un prix différent de celui de la réponse de référence, ce qui rend la réponse incorrecte.</t>
         </is>
       </c>
     </row>
@@ -737,19 +732,16 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>Bonjour,
-Aucun des éléments fournis dans la base de connaissances ne précise quel iPhone a été commercialisé en 2023.  
-Pour connaître le modèle sorti cette année, vous pouvez :
-- consulter la page « Catalogue Téléphones » de notre site www.telecomplus.fr, qui indique les dates de sortie de chaque modèle,  
-- appeler notre service client au 3900 (appel gratuit) ou utiliser le chat en ligne disponible sur notre site.
-En attendant, si vous cherchez un modèle récent, notre catalogue propose l’iPhone 15, l’iPhone 16 et l’iPhone 17, tous disponibles avec plusieurs capacités de stockage. N’hésitez pas à nous contacter pour obtenir des conseils personnalisés ou vérifier la date de commercialisation exacte.</t>
+L’iPhone commercialisé en 2023 est la gamme **iPhone 15** (iPhone 15, iPhone 15 Plus, iPhone 15 Pro et iPhone 15 Pro Max), lancée en septembre 2023.
+Vous pouvez les découvrir en boutique ou les commander en ligne sur www.telecomplus.fr avec livraison gratuite. Si vous avez besoin d’un échange ou d’une remise grâce à la reprise de votre ancien téléphone, n’hésitez pas à nous appeler au 3900.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>La réponse fournie par l'agent ne répond pas directement à la question, mais suggère que l'iPhone 15 pourrait être le modèle sorti en 2023, ce qui est correct, mais elle ne le confirme pas explicitement et propose des alternatives pour obtenir l'information exacte.</t>
+          <t>La réponse de l'agent fournit l'information exacte sur l'iPhone commercialisé en 2023, en mentionnant spécifiquement la gamme iPhone 15.</t>
         </is>
       </c>
     </row>
@@ -770,8 +762,7 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>Bonjour,
-Les coloris disponibles pour l’iPhone 16 sont : stellaire, bleu, rose, rouge (PRODUCT RED) et vert.  
-Si vous avez besoin d’aide pour choisir le modèle ou pour passer commande, n’hésitez pas à me le faire savoir.</t>
+Les coloris disponibles pour l’iPhone 16 sont : stellaire, bleu, rose, rouge (PRODUCT RED) et vert.</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -779,7 +770,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Les couleurs mentionnées dans les deux réponses sont différentes, indiquant une discordance significative dans l'information fournie.</t>
+          <t>Les coloris mentionnés dans la réponse générée sont différents de ceux de la réponse de référence, indiquant une faible similarité sémantique.</t>
         </is>
       </c>
     </row>
@@ -800,7 +791,8 @@
       <c r="D12" t="inlineStr">
         <is>
           <t>Bonjour,
-Le modèle iPhone le moins cher proposé avec une capacité de 128 Go est l’**iPhone 11**, au prix de **559 €**.</t>
+L’iPhone le moins cher proposé avec une capacité de 128 Go est l’iPhone 11, au prix de **559 €**.
+Vous pouvez le commander dès maintenant sur notre site www.telecomplus.fr avec livraison gratuite, ou appeler le 3900 (appel gratuit) pour être accompagné dans votre achat.</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -808,7 +800,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>La réponse générée par l'agent fournit exactement la même information que la référence, avec le même modèle d'iPhone et le même prix.</t>
+          <t>La réponse générée par l'agent contient la même information que la référence, avec le même modèle d'iPhone et le même prix, ce qui indique une similarité sémantique et une pertinence parfaite.</t>
         </is>
       </c>
     </row>
@@ -829,10 +821,10 @@
       <c r="D13" t="inlineStr">
         <is>
           <t>Bonjour,
-L’iPhone 13 offre une autonomie allant jusqu’à **17 heures de lecture vidéo**.  
-Pour l’iPhone 16, les informations d’autonomie ne figurent pas dans les données dont je dispose.
-Vous pouvez obtenir ce détail en consultant la fiche produit de l’iPhone 16 sur notre site ou en contactant notre service client, qui pourra vous fournir les spécifications exactes.  
-N’hésitez pas si vous avez besoin d’aide supplémentaire pour choisir le modèle qui correspond le mieux à vos usages.</t>
+L’iPhone 13 offre une autonomie allant jusqu’à **17 heures de lecture vidéo** selon notre FAQ.  
+Pour l’iPhone 16, les informations d’autonomie ne sont pas détaillées dans la FAQ fournie.
+Vous pouvez obtenir ces précisions en consultant la fiche produit de l’iPhone 16 sur le site de TelecomPlus ou en contactant notre service client, qui pourra vous communiquer les performances de batterie officielles d’Apple.  
+Si vous avez besoin d’un comparatif complet ou d’un conseil sur le modèle le plus adapté à votre usage, n’hésitez pas à nous le faire savoir. Nous sommes à votre disposition pour vous aider.</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -840,7 +832,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>L'agent fournit des informations partielles et incorrectes sur l'iPhone 13 et ne fournit pas d'informations sur l'iPhone 16, ce qui ne permet pas de comparer les autonomies.</t>
+          <t>La réponse fournie ne donne pas la différence d'autonomie entre les deux modèles et contient des informations incorrectes ou incomplètes sur l'iPhone 13 et l'iPhone 16.</t>
         </is>
       </c>
     </row>
@@ -861,20 +853,16 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>Bonjour,
-Oui, des frais de résiliation peuvent s’appliquer lorsque vous êtes encore engagé. Dans ce cas, le montant des frais correspond généralement au total des mensualités restantes de votre engagement (12 ou 24 mois). Si vous avez déjà dépassé la période d’engagement, la résiliation est alors gratuite.
-Pour connaître le montant exact qui vous serait facturé, vous pouvez consulter votre contrat ou nous contacter directement :
-- par téléphone au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h)  
-- via le chat en ligne sur notre site web  
-- par email à support@telecomplus.fr  
-Nous restons à votre disposition pour toute aide supplémentaire.</t>
+Oui, des frais de résiliation peuvent s’appliquer si vous êtes encore engagé : ils correspondent au montant des mensualités restantes de votre contrat. En revanche, si vous avez déjà dépassé la période d’engagement (12 ou 24 mois selon votre offre), la résiliation est gratuite.
+Si vous souhaitez connaître le montant exact qui vous serait facturé, vous pouvez contacter notre service client au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h) ou via le chat en ligne sur notre site. Nous nous ferons un plaisir de vous accompagner dans votre démarche.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>La réponse générée est très proche de la référence, avec les mêmes informations clés sur les frais de résiliation et les conditions d'engagement, mais inclut des détails supplémentaires sur les moyens de contact pour obtenir des informations spécifiques.</t>
+          <t>La réponse générée par l'agent est presque identique à la réponse de référence, avec les mêmes informations et la même exactitude.</t>
         </is>
       </c>
     </row>
@@ -895,16 +883,16 @@
       <c r="D15" t="inlineStr">
         <is>
           <t>Bonjour Jean,
-Ce mois-ci, votre consommation data s’élève à **3,2 Go** (pour le mois de novembre 2025).
-Si vous avez besoin d’ajuster votre forfait ou d’obtenir plus de data, n’hésitez pas à me le dire ; je peux vous proposer les options disponibles.</t>
+Ce mois‑ci (novembre 2025), vous avez consommé **3,2 Go** de data sur votre forfait Essentiel 5 GB. Il vous reste donc **1,8 Go** disponibles avant d’atteindre votre quota.
+Si vous avez besoin d’un rechargement ou d’un suivi plus précis, n’hésitez pas à nous appeler au **3900** (gratuit, 7 j/7 de 8 h à 20 h) ou à utiliser le chat en ligne sur notre site.</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>La réponse fournit la même information de consommation data (3,2 Go) mais inclut des détails supplémentaires sur la période et propose une aide pour ajuster le forfait, ce qui est pertinent mais un peu au-delà de la question.</t>
+          <t>La réponse fournie par l'agent contient les informations demandées de manière précise, incluant la consommation data et le forfait, avec des détails supplémentaires utiles.</t>
         </is>
       </c>
     </row>
@@ -924,10 +912,10 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bonjour Jean Bertrand,
-Votre prochaine facture s’élèvera à **9,99 €** et devra être réglée avant le **15 décembre 2025**.  
-Vous pouvez la payer par virement bancaire, PayPal ou mettre en place le prélèvement automatique pour éviter tout retard.
-Si vous avez besoin d’assistance pour le paiement, n’hésitez pas à nous appeler au 3900 (appel gratuit).</t>
+          <t>Bonjour Jean,
+Votre prochaine facture s’élèvera à **9,99 €**, correspondant à votre forfait Essentiel 5 GB. Aucun dépassement n’a été constaté (3,2 GB consommés sur les 5 GB prévus), donc aucun frais supplémentaire n’est appliqué. La date d’échéance de cette facture est le **15 /12 /2025**.
+Vous pouvez régler ce montant dès maintenant par prélèvement automatique, virement bancaire ou PayPal pour éviter tout retard.  
+N’hésitez pas à me dire si vous avez besoin d’aide pour le paiement ou pour toute autre question.</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -935,7 +923,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>La réponse générée fournit les mêmes informations essentielles que la référence, notamment le montant et la date d'échéance de la facture, avec des détails supplémentaires sur les méthodes de paiement.</t>
+          <t>La réponse générée contient les mêmes informations essentielles que la référence, notamment le montant de la facture et la date d'échéance.</t>
         </is>
       </c>
     </row>
@@ -957,10 +945,10 @@
         <is>
           <t>Bonjour Pierre,
 Oui, vous avez actuellement deux tickets de support en cours :
-- Ticket #3 : « Frais de résiliation », catégorie Résiliation, statut En cours.  
-- Ticket #4 : « Débit très lent », catégorie Problème de réseau, statut En cours.
-Si vous avez besoin d’une mise à jour ou de préciser un point, vous pouvez nous joindre au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h), via le chat en ligne sur notre site, ou par email à support@telecomplus.fr.  
-Nous restons à votre disposition pour toute assistance supplémentaire.</t>
+- Ticket #3 : « Frais de résiliation », catégorie Résiliation, statut **En cours**.  
+- Ticket #4 : « Débit très lent », catégorie Problème de réseau, statut **En cours**.
+Si vous avez besoin de précisions supplémentaires ou de faire évoluer l’un de ces dossiers, vous pouvez nous joindre au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h), via le chat en ligne ou par email à support@telecomplus.fr.  
+Nous restons à votre disposition pour toute autre demande.</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -968,7 +956,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>La réponse générée fournit les mêmes informations que la référence, avec les mêmes détails sur les tickets en cours, et ajoute même des informations supplémentaires sur les moyens de contacter le support.</t>
+          <t>La réponse générée par l'agent contient les mêmes informations que la référence, avec les détails des tickets de support en cours, et fournit des informations supplémentaires sur les moyens de contacter le support.</t>
         </is>
       </c>
     </row>
@@ -989,19 +977,23 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>Bonjour Jean,
-Nous ne disposons pas d’informations pour estimer le coût d’un séjour de deux semaines aux États‑Unis. En ce qui concerne votre utilisation mobile pendant ce voyage, les frais de roaming hors Europe sont calculés en fonction de votre consommation (data, appels, SMS).  
-Pour limiter ces frais, nous vous recommandons :
-- de désactiver les données mobiles et d’utiliser le Wi‑Fi dès que possible ;  
-- de souscrire à un pass international journalier ou hebdomadaire, disponible dans votre espace client, qui vous permet de maîtriser le prix du roaming.  
-Si vous avez besoin d’un devis précis ou d’aide pour activer un pass, n’hésitez pas à contacter notre service client au 3900 (appel gratuit) ou par chat en ligne.</t>
+Je n’ai pas d’informations sur le prix d’un voyage (billet d’avion, hébergement, etc.) aux États-Unis, donc je ne peux pas vous donner de coût global pour les deux semaines.
+En ce qui concerne votre utilisation mobile pendant ce séjour, votre forfait **Essentiel 5 GB** (9,99 €/mois) ne comprend pas le roaming hors Europe. Vous pouvez éviter des frais de data à l’étranger en :
+* désactivant les données mobiles et en vous connectant au Wi‑Fi, ou  
+* souscrivant à un **pass international** (journalier ou hebdomadaire) disponible dans votre espace client.
+Pour connaître le tarif exact de ces passes et choisir la durée qui convient à votre voyage, vous pouvez :
+* appeler le service client au **3900** (appel gratuit, 7 j/7 de 8 h à 20 h),  
+* discuter en ligne via le **chat** sur notre site, ou  
+* envoyer un **email** à **support@telecomplus.fr**.
+N’hésitez pas à nous contacter si vous avez besoin d’aide pour activer un pass ou pour toute autre question. Bonne préparation de votre séjour !</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>La réponse générée fournit des informations utiles sur la manière de limiter les frais de roaming et propose des solutions pour maîtriser les coûts, mais ne fournit pas de détails spécifiques sur les tarifs comme le fait la réponse de référence.</t>
+          <t>La réponse générée aborde correctement les aspects liés au forfait mobile et aux options de pass international pour le roaming hors Europe, mais elle inclut également des informations non demandées sur les moyens de contact pour obtenir de l'aide, ce qui la rend légèrement moins pertinente que la réponse de référence.</t>
         </is>
       </c>
     </row>
@@ -1022,11 +1014,12 @@
       <c r="D19" t="inlineStr">
         <is>
           <t>Bonjour Alexandre,
-Votre abonnement est **actif – hors engagement** (date de début : 20 février 2024, aucune date de fin d’engagement). Selon notre FAQ, la résiliation est donc **gratuite** : aucun frais de résiliation ne s’appliquera.
-Pour mettre fin à votre contrat, vous pouvez :
+Vous êtes actuellement **hors période d’engagement** (date de fin d’engagement : 14 février 2025). Selon notre FAQ, la résiliation est donc **gratuite** et aucun frais ne vous sera facturé.
+Pour procéder, vous pouvez :
 - envoyer une lettre recommandée avec accusé de réception à notre service résiliation, ou  
-- nous contacter directement par téléphone (3900, appel gratuit) ou via le chat en ligne afin que nous procédions à la résiliation pour vous.
-Souhaitez‑vous que nous vous guidions dans la rédaction de la lettre ou que nous planifions l’appel ?</t>
+- nous contacter directement par téléphone (3900, appel gratuit) afin que nous enclenchions la démarche pour vous.
+La résiliation prendra effet sous **10 jours** à compter de la réception de votre demande.
+Souhaitez‑vous que je vous envoie le modèle de lettre recommandée ou que je vous mette en relation avec un conseiller ?</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1034,7 +1027,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>La réponse générée fournit les mêmes informations clés que la référence, notamment la date de début du contrat, le statut hors engagement et la gratuité de la résiliation, avec des détails supplémentaires sur la procédure de résiliation.</t>
+          <t>La réponse générée fournit les mêmes informations clés que la référence, notamment la gratuité de la résiliation et le fait d'être hors période d'engagement, avec des détails supplémentaires sur la procédure de résiliation.</t>
         </is>
       </c>
     </row>
@@ -1055,13 +1048,13 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>Bonjour,
-Avec un budget de 1 000 € pour un iPhone en version 256 GB, vous avez plusieurs options disponibles dans notre catalogue :
-- **iPhone 14 256 GB** à 999 € : le modèle le plus récent qui reste dans votre budget, offrant les dernières améliorations en matière de caméra, de performance et de connectivité 5G.  
-- **iPhone 13 256 GB** à 929 € : un excellent compromis entre prix et performances, avec la puce A15 Bionic et un écran Super Retina XDR.  
-- **iPhone 12 256 GB** à 829 € : toujours compatible 5G, doté d’un écran OLED et d’un bon équilibre entre prix et fonctionnalités.  
-- **iPhone 11 256 GB** à 659 € : le plus économique, idéal si vous cherchez un appareil fiable sans les dernières innovations.
-Si vous privilégiez les dernières technologies, l’iPhone 14 à 999 € correspond parfaitement à votre budget. Vous pouvez le commander en ligne sur www.telecomplus.fr avec livraison gratuite, ou le tester directement en boutique.
-N’hésitez pas à nous appeler au 3900 ou à passer en boutique pour voir les modèles en démonstration.  
+Avec un budget de 1 000 € pour un iPhone en version 256 GB, vous avez plusieurs possibilités dans notre catalogue :
+- **iPhone 14 – 256 GB** : 999 € (juste en dessous de votre budget et le modèle le plus récent que vous pouvez acquérir à ce prix).  
+- iPhone 13 – 256 GB : 929 €  
+- iPhone 12 – 256 GB : 829 €  
+- iPhone 11 – 256 GB : 659 €
+Le **iPhone 14 256 GB** vous offre les dernières innovations (écran ProMotion 120 Hz, construction en titane, zoom optique 5×, USB‑C Thunderbolt, etc.) tout en respectant votre plafond de dépense.
+Vous pouvez le commander dès maintenant sur **www.telecomplus.fr** avec la livraison gratuite, ou le tester en boutique où nos conseillers se tiennent à votre disposition.
 Bonne journée !</t>
         </is>
       </c>
@@ -1070,7 +1063,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>La réponse générée fournit plus d'informations que la référence, incluant plusieurs options d'iPhone dans le budget, mais reste pertinente et répond à la question.</t>
+          <t>La réponse fournit les informations demandées et propose même plusieurs options, mais elle inclut des détails supplémentaires non demandés et ne mentionne pas explicitement que l'iPhone 15 dépasse le budget.</t>
         </is>
       </c>
     </row>
@@ -1090,25 +1083,21 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bonjour Jean Bertrand,
-Je constate que votre abonnement actuel n’est pas renseigné (forfait, prix, data, appels, SMS). Sans ces informations, il m’est impossible de déterminer si votre offre actuelle couvre déjà le roaming en Italie ou si une option supplémentaire serait plus avantageuse.
-**Ce qu’il vous faut :**
-- Le nom exact de votre forfait (ex. : « Forfait 5G », « Forfait 10 Go », etc.) ainsi son volume de data, appels et SMS inclus.
-- Vous pouvez obtenir ces détails en appelant le service client au 3900 ou en vous connectant à votre espace client.
-**En attendant, voici les solutions habituelles pour un séjour de 10 jours en Italie :**
-- **Option Roaming Europe** : activation d’une option dédiée qui vous garantit un tarif forfaitaire (ex. : 5 €/semaine) pour les appels, SMS et data en Europe, évitant les dépassements.
-- **Forfait Europe** : si votre consommation actuelle (3,2 Go de data, 1087 min d’appels, 270 SMS) est élevée, passer à un forfait incluant le roaming (ex. : 15 €/mois avec 10 Go data, appels et SMS illimités en Europe) peut être plus économique.
-Je vous propose de nous appeler au **3900** (appel gratuit, 7 j/7 de 8 h à 20 h) avec votre numéro de ligne afin que nous puissions vérifier votre offre actuelle et activer immédiatement l’option la plus adaptée à votre voyage.  
-À très vite,  
-Service Client TelecomPlus.</t>
+          <t>Bonjour Jean,
+Avec votre forfait **Essentiel 5 GB** (9,99 €/mois, appels et SMS illimités) vous avez déjà consommé **3,2 GB** ce mois‑ci, il vous reste donc **1,8 GB** de data disponible. Le roaming dans les pays de l’UE, dont l’Italie, est inclus dans votre quota ; vous pourrez donc utiliser ces 1,8 GB pendant votre séjour de 10 jours sans frais supplémentaires.
+Si vous pensez dépasser ce restant (streaming, navigation intensive, etc.), deux solutions simples s’offrent à vous :
+* **Option Europe** : +5 GB de data en roaming pour 5 € supplémentaires, activable immédiatement et valable pendant toute la durée de votre voyage.  
+* **Passer au forfait Confort 10 GB** : 14,99 €/mois, 10 GB de data (incluant le roaming) si vous souhaitez un forfait plus généreux à long terme.
+Vous pouvez souscrire à l’Option Europe ou changer de forfait en appelant le **3900** (appel gratuit) ou via le chat en ligne. La modification sera effective dès la prochaine facturation.
+Bonne préparation de votre voyage en Italie !</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>La réponse de l'agent ne fournit pas d'information précise sur le forfait actuel du client et ne répond pas directement à la question, mais propose des solutions générales pour le roaming en Italie.</t>
+          <t>La réponse générée par l'agent est complète, exacte et pertinente, elle fournit les informations nécessaires sur l'utilisation du forfait à l'étranger et propose des solutions en cas de dépassement de la limite de données, mais elle inclut des détails supplémentaires sur la consommation actuelle et les options de modification de forfait qui ne sont pas présents dans la réponse de référence.</t>
         </is>
       </c>
     </row>
@@ -1128,11 +1117,10 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bonjour, il manque votre nom pour personnaliser davantage ma réponse.
-Vous pouvez effectivement bénéficier d’une réduction en échangeant votre ancien iPhone contre le nouvel iPhone 16 :  
-- **En boutique** : apportez votre téléphone actuel à l’un de nos magasins, nous l’évaluerons sur place et vous appliquons la remise immédiatement.  
-- **En ligne** : lors de la commande sur www.telecomplus.fr, choisissez l’option « Reprise », indiquez le modèle de votre ancien iPhone, suivez les instructions d’envoi et la réduction sera déduite du prix final.
-Si vous avez besoin d’assistance pour estimer la valeur de reprise ou pour lancer la procédure, n’hésitez pas à appeler le 3900 (appel gratuit) ou à vous rendre dans la boutique la plus proche.</t>
+          <t>Bonjour,
+Oui, vous pouvez bénéficier d’une réduction en échangeant votre ancien iPhone contre le nouvel iPhone 16. La reprise est disponible en boutique et en ligne ; le montant de la remise dépend du modèle et de l’état de votre appareil actuel.  
+Pour profiter de cette offre, rendez‑vous dans l’une de nos boutiques ou lancez la procédure de reprise sur www.telecomplus.fr, où la réduction sera appliquée directement à votre commande.  
+N’hésitez pas à nous appeler au 3900 si vous avez besoin d’assistance pour estimer la valeur de votre ancien téléphone.</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1140,7 +1128,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>La réponse générée fournit les mêmes informations essentielles que la référence, notamment les options de reprise en boutique et en ligne, ainsi que le numéro de téléphone pour assistance, mais omet le prix de l'iPhone 16.</t>
+          <t>La réponse générée couvre les points clés de la réponse de référence, notamment la possibilité d'une réduction en échangeant l'ancien iPhone, la méthode pour connaître la valeur de reprise et les moyens de contact pour plus d'informations. Les différences mineures concernent la formulation et l'ordre des informations.</t>
         </is>
       </c>
     </row>
@@ -1161,24 +1149,19 @@
       <c r="D23" t="inlineStr">
         <is>
           <t>Bonjour,
-D’après notre FAQ, les iPhone équipés d’une caméra d’au moins 48 Mpx et disponibles en version 256 Go sont :
-- **iPhone 16** (2024) : caméra principale 48 Mpx, stockage 256 Go disponible.  
-- Un modèle « Système de caméra Fusion 48 Mpx » (description sans nom de gamme) : stockage 256 Go disponible.
-Cependant, les tarifs ne sont pas indiqués dans la base de connaissances que nous utilisons. Nous ne pouvons donc pas confirmer qu’ils sont proposés à moins de 1 200 €.
-**Comment obtenir le prix ?**  
-- Consultez le catalogue en ligne sur www.telecomplus.fr ; le prix s’affiche directement pour chaque configuration.  
-- Appelez notre service commercial au 3900 (appel gratuit) ou rendez‑vous en boutique pour obtenir un devis précis.
-**Alternatives**  
-Si le budget de 1 200 € est strict, vous pouvez également envisager les modèles précédents disposant d’une caméra 48 Mpx (par exemple l’iPhone 15 Pro) qui sont souvent proposés à des tarifs plus avantageux tout en conservant le stockage 256 Go.
-N’hésitez pas à nous recontacter pour toute aide supplémentaire dans votre choix.</t>
+Le seul modèle mentionné dans notre base de connaissances qui possède une caméra principale de **48 Mpx** et une capacité de **256 Go** est l’**iPhone 16** (commercialisé en 2024).  
+Le prix exact de cette configuration n’est pas indiqué dans les informations dont je dispose. Pour savoir s’il est proposé à moins de 1200 €, je vous recommande :
+- de consulter la fiche produit sur notre site www.telecomplus.fr, où les tarifs sont affichés en temps réel,
+- ou de contacter directement notre service commercial au **3900** (appel gratuit) pour obtenir le prix actuel et vérifier la disponibilité en magasin.
+Je reste à votre disposition si vous avez besoin d’aide pour la commande ou pour comparer d’autres modèles.</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>La réponse fournit des informations partiellement correctes sur les modèles d'iPhone avec caméra 48 Mpx et stockage 256GB, mais ne fournit pas les prix exacts et ne répond pas directement à la question du client concernant les modèles disponibles pour moins de 1200€.</t>
+          <t>La réponse fournit une partie des informations demandées, mais manque de précision sur le prix et ne mentionne qu'un seul modèle, alors que la référence en cite deux.</t>
         </is>
       </c>
     </row>
@@ -1198,24 +1181,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bonjour Jean Bertrand,
-Je constate que votre dossier ne précise pas le forfait que vous avez actuellement (type de forfait, prix mensuel et volume de data inclus). Sans ces informations, il m’est impossible de calculer précisément l’augmentation de tarif que représenterait le passage à un forfait avec plus de data.
-**Ce qui manque :**  
-- Le nom ou le code de votre forfait actuel  
-- Le prix mensuel et le volume de data inclus dans ce forfait  
-**Comment obtenir ces informations :**  
-Vous pouvez les retrouver dans votre dernier contrat ou sur votre facture détaillée. Si vous avez besoin d’aide pour les localiser, n’hésitez pas à appeler notre service client au **3900** (appel gratuit, disponible 7 j/7 de 8 h à 20 h) ou à nous écrire à **support@telecomplus.fr**.
-**Prochaine étape :**  
-Une fois que vous connaîtrez votre forfait actuel, nous pourrons vous proposer les offres « plus de data » disponibles et vous indiquer exactement le supplément mensuel (par exemple + 2 €, + 5 €, etc.) en fonction du volume supplémentaire souhaité.
-Je reste à votre disposition pour toute question supplémentaire.</t>
+          <t>Bonjour Jean,
+Vous êtes actuellement sur le forfait **Essentiel 5 GB** au prix de **9,99 €/mois**.  
+Pour connaître l’augmentation de tarif qu’entraînerait le passage à un forfait offrant davantage de data, il me faut savoir quel niveau de data vous envisagez (par exemple 10 GB, 20 GB, 50 GB, etc.).  
+Dès que vous me préciserez le forfait souhaité, je pourrai vous indiquer exactement la différence de prix mensuel par rapport à votre abonnement actuel.
+Vous pouvez également me demander la liste complète de nos forfaits « plus de data », et je vous fournirai les tarifs correspondants.  
+À très vite pour finaliser votre changement !</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>La réponse générée ne fournit pas de réponse directe à la question du client, mais demande des informations supplémentaires pour calculer le coût, ce qui indique un manque d'information ou d'accès aux données du client.</t>
+          <t>La réponse générée par l'agent demande des précisions supplémentaires au client pour fournir une réponse exacte, au lieu de proposer directement les options de forfaits supérieurs et leurs coûts comme dans la réponse de référence.</t>
         </is>
       </c>
     </row>
@@ -1236,9 +1215,10 @@
       <c r="D25" t="inlineStr">
         <is>
           <t>Bonjour,
-Pour la photographie, le modèle le plus performant de notre gamme est l’**iPhone 15 Pro** (et son grand frère l’iPhone 15 Pro Max). Il dispose d’un système à double caméra de 12 Mpx (grand‑angle et téléobjectif) avec un zoom optique 5×, d’un écran ProMotion 120 Hz et de la puce Apple Intelligence qui optimise le traitement des images. Ces caractéristiques offrent une qualité exceptionnelle dans toutes les conditions d’éclairage, ainsi qu’un rendu très détaillé et des couleurs fidèles.
-Si vous cherchez une option légèrement moins chère tout en conservant d’excellentes capacités photo, l’**iPhone 14** propose également une double caméra 12 Mpx (grand‑angle et ultra‑grand‑angle) avec le mode Cinematic pour la vidéo, ce qui reste très performant pour la plupart des usages.
-Vous pouvez tester les deux modèles en boutique ou les commander en ligne sur www.telecomplus.fr avec livraison gratuite. Si vous avez besoin d’un conseil plus personnalisé (par exemple, selon votre budget ou vos besoins spécifiques), n’hésitez pas à appeler notre service gratuit au 3900.</t>
+Pour la photographie, le modèle le plus performant proposé par TelecomPlus est l’**iPhone 15 Pro**.  
+Il intègre un système photographique très complet : double caméra 12 Mpx (grand‑angle et téléobjectif) avec un **zoom optique 5×**, un écran ProMotion 120 Hz et la puce Apple Intelligence qui optimise le traitement d’image. Ces caractéristiques permettent de capturer des photos d’une qualité exceptionnelle, même en conditions de faible éclairage.
+Si vous cherchez un excellent compromis entre prix et performances, l’**iPhone 15** (double caméra 12 Mpx grand‑angle/téléobjectif) reste également très performant pour la photo.
+N’hésitez pas à nous appeler au **3900** (appel gratuit) ou à vous rendre en boutique pour tester les modèles en démonstration. Vous pouvez également commander en ligne sur **www.telecomplus.fr** avec livraison gratuite.</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1246,7 +1226,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>La réponse fournit des informations sur les modèles d'iPhone performants pour la photographie, mais les modèles mentionnés (iPhone 15 Pro, iPhone 14) ne correspondent pas à ceux de la référence (iPhone 17, iPhone 16), et les caractéristiques techniques diffèrent.</t>
+          <t>La réponse fournit des informations sur les modèles d'iPhone pour la photographie, mais ne correspond pas exactement aux spécifications et modèles mentionnés dans la référence, notamment en ce qui concerne l'iPhone 17 et l'iPhone 16.</t>
         </is>
       </c>
     </row>
@@ -1267,20 +1247,20 @@
       <c r="D26" t="inlineStr">
         <is>
           <t>Bonjour,
-Votre question porte sur l’utilisation de votre iPhone à l’étranger sans frais supplémentaires.  
-Dans les informations dont je dispose, il n’y a pas de détail précis sur les conditions de roaming pour les iPhone. Les frais éventuels dépendent du forfait que vous avez souscrit (par exemple, un forfait incluant le roaming ou des options « roaming » à ajouter).
-**Ce que vous pouvez faire :**  
-- Vérifier les options roaming disponibles dans votre espace client ou en appelant le Service Client au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h).  
-- Vous pouvez également consulter le chat en ligne sur notre site web ou envoyer un email à support@telecomplus.fr pour obtenir une réponse personnalisée en fonction de votre abonnement.
-Si vous avez besoin d’aide pour activer une option roaming ou pour connaître les tarifs appliqués à votre forfait, n’hésitez pas à nous contacter via l’un de ces canaux. Nous sommes à votre disposition pour vous assurer une utilisation sereine de votre iPhone à l’étranger.</t>
+Je ne dispose pas des informations précises sur votre forfait actuel, il m’est donc impossible de confirmer si votre iPhone pourra être utilisé à l’étranger sans frais supplémentaires.
+En général, l’utilisation à l’étranger peut entraîner des frais de roaming : appels, SMS ou data hors‑forfait sont facturés selon les tarifs internationaux. Pour éviter tout surcoût, vous pouvez :
+- Vérifier les conditions de votre abonnement dans votre espace client ou sur votre facture (les dépassements de forfait ou les services de roaming sont souvent indiqués).
+- Souscrire à une option roaming ou à un forfait « Euro‑Roam » qui inclut les communications et la data à l’étranger sans frais additionnels.
+- Contacter notre service client au 3900 (appel gratuit, 7 j/7 de 8 h à 20 h) ou via le chat en ligne pour obtenir une confirmation adaptée à votre ligne.
+N’hésitez pas à nous appeler ou à vous connecter à votre compte pour connaître les options disponibles et éviter toute surprise sur votre prochaine facture.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La réponse fournit des informations générales sur la façon d'obtenir des informations sur le roaming, mais ne répond pas directement à la question et ne fournit pas les détails spécifiques sur les conditions de roaming comme à la maison dans l'UE ou les frais hors Europe.</t>
+          <t>La réponse fournit des informations générales utiles sur l'utilisation à l'étranger et propose des solutions pour éviter les surcoûts, mais ne répond pas directement à la question concernant l'Union Européenne et les frais de roaming.</t>
         </is>
       </c>
     </row>
